--- a/Rekap Absen dan Nilai 2025-2026.xlsx
+++ b/Rekap Absen dan Nilai 2025-2026.xlsx
@@ -5,15 +5,15 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="KELAS 11" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="KELAS 10" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="XII IPS" sheetId="3" state="hidden" r:id="rId4"/>
+    <sheet name="KELAS 11" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="KELAS 10" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="XII IPS" sheetId="3" state="hidden" r:id="rId5"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId5"/>
+    <externalReference r:id="rId6"/>
   </externalReferences>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'KELAS 10'!$A$11:$L$129</definedName>
@@ -4329,16 +4329,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00%"/>
     <numFmt numFmtId="166" formatCode="m/d/yyyy\ h:mm"/>
-    <numFmt numFmtId="167" formatCode="General"/>
-    <numFmt numFmtId="168" formatCode="0"/>
-    <numFmt numFmtId="169" formatCode="0.00"/>
-    <numFmt numFmtId="170" formatCode="0."/>
-    <numFmt numFmtId="171" formatCode="0%"/>
-    <numFmt numFmtId="172" formatCode="_([$Rp-421]* #,##0_);_([$Rp-421]* \(#,##0\);_([$Rp-421]* \-_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="0"/>
+    <numFmt numFmtId="168" formatCode="0.00"/>
+    <numFmt numFmtId="169" formatCode="0."/>
+    <numFmt numFmtId="170" formatCode="0%"/>
+    <numFmt numFmtId="171" formatCode="_([$Rp-421]* #,##0_);_([$Rp-421]* \(#,##0\);_([$Rp-421]* \-_);_(@_)"/>
   </numFmts>
   <fonts count="52">
     <font>
@@ -4878,7 +4877,7 @@
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -5067,15 +5066,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5123,7 +5122,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5155,7 +5154,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5163,11 +5162,11 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5215,7 +5214,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5311,11 +5310,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5415,7 +5414,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5431,7 +5430,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5443,7 +5442,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5459,7 +5458,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5523,11 +5522,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="47" fillId="12" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="47" fillId="12" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="48" fillId="12" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="48" fillId="12" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5547,11 +5546,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="45" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="45" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -5623,7 +5622,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="47" fillId="12" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="47" fillId="12" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5635,7 +5634,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="45" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -5655,7 +5654,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="45" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -5663,11 +5662,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="45" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="45" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="45" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="45" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -5691,11 +5690,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="45" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="45" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -5743,7 +5742,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFFFFF"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5751,6 +5750,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5758,7 +5758,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF000000"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5766,6 +5766,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF00A933"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5773,6 +5774,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF81D41A"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5780,6 +5782,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFBF819E"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5787,6 +5790,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFDEE6EF"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5794,6 +5798,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFA6A6"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5801,6 +5806,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFD428"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5900,10 +5906,10 @@
       <xdr:rowOff>65160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>3240</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>402480</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>93960</xdr:rowOff>
+      <xdr:rowOff>94320</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -5913,9 +5919,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="1170000"/>
-          <a:ext cx="14657400" cy="28800"/>
+          <a:ext cx="5119560" cy="29160"/>
           <a:chOff x="35280" y="1170000"/>
-          <a:chExt cx="14657400" cy="28800"/>
+          <a:chExt cx="5119560" cy="29160"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -5925,8 +5931,8 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="39240" y="1188000"/>
-            <a:ext cx="14653800" cy="11160"/>
+            <a:off x="36720" y="1188000"/>
+            <a:ext cx="5118480" cy="11520"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -5947,7 +5953,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="1170000"/>
-            <a:ext cx="14653800" cy="11160"/>
+            <a:ext cx="5118480" cy="11520"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -5972,9 +5978,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>738360</xdr:colOff>
+      <xdr:colOff>738000</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>113400</xdr:rowOff>
+      <xdr:rowOff>113040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5989,11 +5995,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="57240"/>
-          <a:ext cx="1070280" cy="818280"/>
+          <a:ext cx="1069920" cy="817920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -6010,9 +6017,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>738360</xdr:colOff>
+      <xdr:colOff>738000</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>132480</xdr:rowOff>
+      <xdr:rowOff>132120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6027,11 +6034,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="8439120"/>
-          <a:ext cx="1070280" cy="818280"/>
+          <a:ext cx="1069920" cy="817920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -6048,9 +6056,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>738360</xdr:colOff>
+      <xdr:colOff>738000</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>132480</xdr:rowOff>
+      <xdr:rowOff>132120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6065,11 +6073,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="8439120"/>
-          <a:ext cx="1070280" cy="818280"/>
+          <a:ext cx="1069920" cy="817920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -6085,10 +6094,10 @@
       <xdr:rowOff>65160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>3240</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>402480</xdr:colOff>
       <xdr:row>55</xdr:row>
-      <xdr:rowOff>93960</xdr:rowOff>
+      <xdr:rowOff>94320</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6098,9 +6107,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="9771120"/>
-          <a:ext cx="14657400" cy="28800"/>
+          <a:ext cx="5119560" cy="29160"/>
           <a:chOff x="35280" y="9771120"/>
-          <a:chExt cx="14657400" cy="28800"/>
+          <a:chExt cx="5119560" cy="29160"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -6110,8 +6119,8 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="39240" y="9789120"/>
-            <a:ext cx="14653800" cy="11160"/>
+            <a:off x="36720" y="9789120"/>
+            <a:ext cx="5118480" cy="11520"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -6132,7 +6141,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="9771120"/>
-            <a:ext cx="14653800" cy="11160"/>
+            <a:ext cx="5118480" cy="11520"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -6157,9 +6166,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>738360</xdr:colOff>
+      <xdr:colOff>738000</xdr:colOff>
       <xdr:row>53</xdr:row>
-      <xdr:rowOff>126000</xdr:rowOff>
+      <xdr:rowOff>125640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6174,11 +6183,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="8667720"/>
-          <a:ext cx="1070280" cy="821520"/>
+          <a:ext cx="1069920" cy="821160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -6194,10 +6204,10 @@
       <xdr:rowOff>65160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>3240</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>402480</xdr:colOff>
       <xdr:row>114</xdr:row>
-      <xdr:rowOff>93960</xdr:rowOff>
+      <xdr:rowOff>94320</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6207,9 +6217,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="20096280"/>
-          <a:ext cx="14657400" cy="28800"/>
+          <a:ext cx="5119560" cy="29160"/>
           <a:chOff x="35280" y="20096280"/>
-          <a:chExt cx="14657400" cy="28800"/>
+          <a:chExt cx="5119560" cy="29160"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -6219,8 +6229,8 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="39240" y="20114280"/>
-            <a:ext cx="14653800" cy="11160"/>
+            <a:off x="36720" y="20114280"/>
+            <a:ext cx="5118480" cy="11520"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -6241,7 +6251,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="20096280"/>
-            <a:ext cx="14653800" cy="11160"/>
+            <a:ext cx="5118480" cy="11520"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -6266,9 +6276,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>741960</xdr:colOff>
+      <xdr:colOff>741600</xdr:colOff>
       <xdr:row>112</xdr:row>
-      <xdr:rowOff>107640</xdr:rowOff>
+      <xdr:rowOff>107280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6278,7 +6288,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4320" y="18977760"/>
-          <a:ext cx="1070280" cy="817920"/>
+          <a:ext cx="1069920" cy="817560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6309,15 +6319,19 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1800" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="1800" strike="noStrike" u="none">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
               <a:latin typeface="Times New Roman"/>
             </a:rPr>
             <a:t>Cxz </a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1800" spc="-1" strike="noStrike">
+          <a:endParaRPr b="0" lang="en-US" sz="1800" strike="noStrike" u="none">
+            <a:effectLst/>
+            <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
           </a:endParaRPr>
         </a:p>
@@ -6339,9 +6353,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>360</xdr:colOff>
+      <xdr:colOff>720</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>93960</xdr:rowOff>
+      <xdr:rowOff>94320</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6351,9 +6365,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="1112760"/>
-          <a:ext cx="2832120" cy="28800"/>
+          <a:ext cx="2832480" cy="29160"/>
           <a:chOff x="35280" y="1112760"/>
-          <a:chExt cx="2832120" cy="28800"/>
+          <a:chExt cx="2832480" cy="29160"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -6364,7 +6378,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="36360" y="1130760"/>
-            <a:ext cx="2831400" cy="11160"/>
+            <a:ext cx="2831760" cy="11520"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -6385,7 +6399,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="1112760"/>
-            <a:ext cx="2831400" cy="11160"/>
+            <a:ext cx="2831760" cy="11520"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -6410,9 +6424,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>751680</xdr:colOff>
+      <xdr:colOff>751320</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>24480</xdr:rowOff>
+      <xdr:rowOff>24120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6427,11 +6441,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="57240"/>
-          <a:ext cx="1069560" cy="824400"/>
+          <a:ext cx="1069200" cy="824040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -6448,9 +6463,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>360</xdr:colOff>
+      <xdr:colOff>720</xdr:colOff>
       <xdr:row>73</xdr:row>
-      <xdr:rowOff>93960</xdr:rowOff>
+      <xdr:rowOff>94320</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6460,9 +6475,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="12190320"/>
-          <a:ext cx="2832120" cy="28800"/>
+          <a:ext cx="2832480" cy="29160"/>
           <a:chOff x="35280" y="12190320"/>
-          <a:chExt cx="2832120" cy="28800"/>
+          <a:chExt cx="2832480" cy="29160"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -6473,7 +6488,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="36360" y="12208320"/>
-            <a:ext cx="2831400" cy="11160"/>
+            <a:ext cx="2831760" cy="11520"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -6494,7 +6509,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="12190320"/>
-            <a:ext cx="2831400" cy="11160"/>
+            <a:ext cx="2831760" cy="11520"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -6519,9 +6534,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>751680</xdr:colOff>
+      <xdr:colOff>751320</xdr:colOff>
       <xdr:row>72</xdr:row>
-      <xdr:rowOff>24480</xdr:rowOff>
+      <xdr:rowOff>24120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6536,11 +6551,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="11134800"/>
-          <a:ext cx="1069560" cy="824400"/>
+          <a:ext cx="1069200" cy="824040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -6557,9 +6573,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>360</xdr:colOff>
+      <xdr:colOff>720</xdr:colOff>
       <xdr:row>140</xdr:row>
-      <xdr:rowOff>93960</xdr:rowOff>
+      <xdr:rowOff>94320</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6569,9 +6585,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="23296680"/>
-          <a:ext cx="2832120" cy="28800"/>
+          <a:ext cx="2832480" cy="29160"/>
           <a:chOff x="35280" y="23296680"/>
-          <a:chExt cx="2832120" cy="28800"/>
+          <a:chExt cx="2832480" cy="29160"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -6582,7 +6598,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="36360" y="23314680"/>
-            <a:ext cx="2831400" cy="11160"/>
+            <a:ext cx="2831760" cy="11520"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -6603,7 +6619,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="23296680"/>
-            <a:ext cx="2831400" cy="11160"/>
+            <a:ext cx="2831760" cy="11520"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -6628,9 +6644,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>751680</xdr:colOff>
+      <xdr:colOff>751320</xdr:colOff>
       <xdr:row>139</xdr:row>
-      <xdr:rowOff>24480</xdr:rowOff>
+      <xdr:rowOff>24120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6645,11 +6661,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="22240800"/>
-          <a:ext cx="1069560" cy="824760"/>
+          <a:ext cx="1069200" cy="824400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -6671,9 +6688,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>46080</xdr:colOff>
+      <xdr:colOff>45720</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>150840</xdr:rowOff>
+      <xdr:rowOff>150480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6687,11 +6704,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="359640" y="238320"/>
-          <a:ext cx="795240" cy="922320"/>
+          <a:ext cx="794880" cy="921960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -6735,13 +6753,119 @@
 </externalLink>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AH1048576"/>
-  <sheetFormatPr defaultColWidth="11.515625" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.515625" defaultRowHeight="13.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.72"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="2" min="2" style="1" width="11.51"/>
@@ -6756,22 +6880,22 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="12" min="12" style="2" width="14.52"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="13" min="13" style="2" width="11.51"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="14" min="14" style="4" width="6.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="5" width="9.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="2" width="5.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="5.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="8.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="12.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="10.56"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="11.51"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="22" min="22" style="5" width="11.51"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="11.51"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="24" min="24" style="2" width="11.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="13.49"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="27" min="26" style="1" width="11.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="11.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="6" width="6.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="1" width="6.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="2" width="8.11"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="15" min="15" style="5" width="9.58"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="16" min="16" style="2" width="5.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="17" min="17" style="1" width="5.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="18" min="18" style="1" width="8.29"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="19" min="19" style="1" width="12.86"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="20" min="20" style="1" width="10.56"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="21" min="21" style="1" width="11.51"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="22" min="22" style="5" width="11.51"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="23" min="23" style="1" width="11.51"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="24" min="24" style="2" width="11.51"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="25" min="25" style="1" width="13.49"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="27" min="26" style="1" width="11.51"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="28" min="28" style="1" width="11.24"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="29" min="29" style="6" width="6.61"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="30" min="30" style="1" width="6.96"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="31" min="31" style="2" width="8.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="1" width="9.62"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="33" style="2" width="11.51"/>
   </cols>
@@ -18002,7 +18126,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AJ201"/>
-  <sheetFormatPr defaultColWidth="11.515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.515625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="77" width="4.52"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="2" min="2" style="77" width="11.51"/>
@@ -30490,7 +30614,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:XFD283"/>
-  <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="139" width="4.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="139" width="11.44"/>

--- a/Rekap Absen dan Nilai 2025-2026.xlsx
+++ b/Rekap Absen dan Nilai 2025-2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="KELAS 11" sheetId="1" state="visible" r:id="rId3"/>
@@ -5956,9 +5956,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>4320</xdr:colOff>
+      <xdr:colOff>4680</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>98640</xdr:rowOff>
+      <xdr:rowOff>99000</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -5968,9 +5968,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="1170000"/>
-          <a:ext cx="5634360" cy="33480"/>
+          <a:ext cx="5634720" cy="33840"/>
           <a:chOff x="35280" y="1170000"/>
-          <a:chExt cx="5634360" cy="33480"/>
+          <a:chExt cx="5634720" cy="33840"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -5981,7 +5981,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="36720" y="1188000"/>
-            <a:ext cx="5633280" cy="15840"/>
+            <a:ext cx="5633640" cy="16200"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -6002,7 +6002,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="1170000"/>
-            <a:ext cx="5632920" cy="15840"/>
+            <a:ext cx="5633280" cy="16200"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -6027,9 +6027,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>733680</xdr:colOff>
+      <xdr:colOff>733320</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>108720</xdr:rowOff>
+      <xdr:rowOff>108360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6044,7 +6044,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="57240"/>
-          <a:ext cx="1098720" cy="813600"/>
+          <a:ext cx="1098360" cy="813240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6066,9 +6066,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>733680</xdr:colOff>
+      <xdr:colOff>733320</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>127800</xdr:rowOff>
+      <xdr:rowOff>127440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6083,7 +6083,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="8439840"/>
-          <a:ext cx="1098720" cy="813600"/>
+          <a:ext cx="1098360" cy="813240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6105,9 +6105,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>733680</xdr:colOff>
+      <xdr:colOff>733320</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>127800</xdr:rowOff>
+      <xdr:rowOff>127440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6122,7 +6122,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="8439840"/>
-          <a:ext cx="1098720" cy="813600"/>
+          <a:ext cx="1098360" cy="813240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6144,9 +6144,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>4320</xdr:colOff>
+      <xdr:colOff>4680</xdr:colOff>
       <xdr:row>55</xdr:row>
-      <xdr:rowOff>98640</xdr:rowOff>
+      <xdr:rowOff>99000</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6156,9 +6156,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="9771840"/>
-          <a:ext cx="5634360" cy="33480"/>
+          <a:ext cx="5634720" cy="33840"/>
           <a:chOff x="35280" y="9771840"/>
-          <a:chExt cx="5634360" cy="33480"/>
+          <a:chExt cx="5634720" cy="33840"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -6169,7 +6169,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="36720" y="9789840"/>
-            <a:ext cx="5633280" cy="15840"/>
+            <a:ext cx="5633640" cy="16200"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -6190,7 +6190,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="9771840"/>
-            <a:ext cx="5632920" cy="15840"/>
+            <a:ext cx="5633280" cy="16200"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -6215,9 +6215,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>733680</xdr:colOff>
+      <xdr:colOff>733320</xdr:colOff>
       <xdr:row>53</xdr:row>
-      <xdr:rowOff>121680</xdr:rowOff>
+      <xdr:rowOff>121320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6232,7 +6232,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="8668440"/>
-          <a:ext cx="1098720" cy="816840"/>
+          <a:ext cx="1098360" cy="816480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6254,9 +6254,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>4320</xdr:colOff>
+      <xdr:colOff>4680</xdr:colOff>
       <xdr:row>114</xdr:row>
-      <xdr:rowOff>98640</xdr:rowOff>
+      <xdr:rowOff>99000</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6266,9 +6266,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="20097000"/>
-          <a:ext cx="5634360" cy="33480"/>
+          <a:ext cx="5634720" cy="33840"/>
           <a:chOff x="35280" y="20097000"/>
-          <a:chExt cx="5634360" cy="33480"/>
+          <a:chExt cx="5634720" cy="33840"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -6279,7 +6279,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="36720" y="20115000"/>
-            <a:ext cx="5633280" cy="15840"/>
+            <a:ext cx="5633640" cy="16200"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -6300,7 +6300,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="20097000"/>
-            <a:ext cx="5632920" cy="15840"/>
+            <a:ext cx="5633280" cy="16200"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -6325,9 +6325,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>737280</xdr:colOff>
+      <xdr:colOff>736920</xdr:colOff>
       <xdr:row>112</xdr:row>
-      <xdr:rowOff>102600</xdr:rowOff>
+      <xdr:rowOff>102240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6337,7 +6337,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4320" y="18978120"/>
-          <a:ext cx="1098720" cy="813240"/>
+          <a:ext cx="1098360" cy="812880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6403,9 +6403,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>5040</xdr:colOff>
+      <xdr:colOff>5400</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>98640</xdr:rowOff>
+      <xdr:rowOff>99000</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6415,9 +6415,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="1112760"/>
-          <a:ext cx="3120120" cy="33480"/>
+          <a:ext cx="3120480" cy="33840"/>
           <a:chOff x="35280" y="1112760"/>
-          <a:chExt cx="3120120" cy="33480"/>
+          <a:chExt cx="3120480" cy="33840"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -6428,7 +6428,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="36360" y="1130760"/>
-            <a:ext cx="3119400" cy="15840"/>
+            <a:ext cx="3119760" cy="16200"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -6449,7 +6449,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="1112760"/>
-            <a:ext cx="3119040" cy="15840"/>
+            <a:ext cx="3119400" cy="16200"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -6474,9 +6474,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>747000</xdr:colOff>
+      <xdr:colOff>746640</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>19800</xdr:rowOff>
+      <xdr:rowOff>19440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6491,7 +6491,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="57240"/>
-          <a:ext cx="1096200" cy="819720"/>
+          <a:ext cx="1095840" cy="819360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6513,9 +6513,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>5040</xdr:colOff>
+      <xdr:colOff>5400</xdr:colOff>
       <xdr:row>73</xdr:row>
-      <xdr:rowOff>98640</xdr:rowOff>
+      <xdr:rowOff>99000</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6525,9 +6525,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="12190320"/>
-          <a:ext cx="3120120" cy="33480"/>
+          <a:ext cx="3120480" cy="33840"/>
           <a:chOff x="35280" y="12190320"/>
-          <a:chExt cx="3120120" cy="33480"/>
+          <a:chExt cx="3120480" cy="33840"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -6538,7 +6538,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="36360" y="12208320"/>
-            <a:ext cx="3119400" cy="15840"/>
+            <a:ext cx="3119760" cy="16200"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -6559,7 +6559,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="12190320"/>
-            <a:ext cx="3119040" cy="15840"/>
+            <a:ext cx="3119400" cy="16200"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -6584,9 +6584,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>747000</xdr:colOff>
+      <xdr:colOff>746640</xdr:colOff>
       <xdr:row>72</xdr:row>
-      <xdr:rowOff>19800</xdr:rowOff>
+      <xdr:rowOff>19440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6601,7 +6601,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="11134800"/>
-          <a:ext cx="1096200" cy="819720"/>
+          <a:ext cx="1095840" cy="819360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6623,9 +6623,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>5040</xdr:colOff>
+      <xdr:colOff>5400</xdr:colOff>
       <xdr:row>140</xdr:row>
-      <xdr:rowOff>98640</xdr:rowOff>
+      <xdr:rowOff>99000</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6635,9 +6635,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="23296680"/>
-          <a:ext cx="3120120" cy="33480"/>
+          <a:ext cx="3120480" cy="33840"/>
           <a:chOff x="35280" y="23296680"/>
-          <a:chExt cx="3120120" cy="33480"/>
+          <a:chExt cx="3120480" cy="33840"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -6648,7 +6648,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="36360" y="23314680"/>
-            <a:ext cx="3119400" cy="15840"/>
+            <a:ext cx="3119760" cy="16200"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -6669,7 +6669,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="23296680"/>
-            <a:ext cx="3119040" cy="15840"/>
+            <a:ext cx="3119400" cy="16200"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -6694,9 +6694,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>747000</xdr:colOff>
+      <xdr:colOff>746640</xdr:colOff>
       <xdr:row>139</xdr:row>
-      <xdr:rowOff>19800</xdr:rowOff>
+      <xdr:rowOff>19440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6711,7 +6711,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="22240800"/>
-          <a:ext cx="1096200" cy="820080"/>
+          <a:ext cx="1095840" cy="819720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6738,9 +6738,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>41400</xdr:colOff>
+      <xdr:colOff>41040</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>146160</xdr:rowOff>
+      <xdr:rowOff>145800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6754,7 +6754,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="389520" y="238320"/>
-          <a:ext cx="870480" cy="917640"/>
+          <a:ext cx="870120" cy="917280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="AJ26" s="31"/>
       <c r="AK26" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="AJ38" s="31"/>
       <c r="AK38" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/Rekap Absen dan Nilai 2025-2026.xlsx
+++ b/Rekap Absen dan Nilai 2025-2026.xlsx
@@ -8670,19 +8670,19 @@
         <v>98</v>
       </c>
       <c r="AC13" s="78">
-        <f>SUM(AB13+X13+V13+T13+S13+R13+P13+O13)</f>
+        <f t="shared" ref="AC13:AC28" si="0">SUM(AB13+X13+V13+T13+S13+R13+P13+O13)</f>
         <v>798</v>
       </c>
       <c r="AD13" s="160">
-        <f>SUM(AA13+Z13+Y13+W13+U13+Q13)*100</f>
+        <f t="shared" ref="AD13:AD28" si="1">SUM(AA13+Z13+Y13+W13+U13+Q13)*100</f>
         <v>200</v>
       </c>
       <c r="AE13" s="196">
-        <f>(0.8*AC13)+(0.2*AD13)</f>
+        <f t="shared" ref="AE13:AE28" si="2">(0.8*AC13)+(0.2*AD13)</f>
         <v>678.4</v>
       </c>
       <c r="AF13" s="197">
-        <f>84+((AE13-$AE$48)/($AE$47-$AE$48)*(92-84))</f>
+        <f t="shared" ref="AF13:AF28" si="3">84+((AE13-$AE$48)/($AE$47-$AE$48)*(92-84))</f>
         <v>90.0056338028169</v>
       </c>
       <c r="AG13" s="160">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="AI13" s="160"/>
       <c r="AJ13" s="160">
-        <f>AQ13</f>
+        <f t="shared" ref="AJ13:AJ28" si="4">AQ13</f>
         <v>88</v>
       </c>
       <c r="AK13" s="160">
@@ -8707,11 +8707,11 @@
         <v>100</v>
       </c>
       <c r="AO13" s="161">
-        <f>AG13+AH13+AM13+AN13</f>
+        <f t="shared" ref="AO13:AO28" si="5">AG13+AH13+AM13+AN13</f>
         <v>400</v>
       </c>
       <c r="AP13" s="161">
-        <f>AI13+AK13+AL13</f>
+        <f t="shared" ref="AP13:AP28" si="6">AI13+AK13+AL13</f>
         <v>3</v>
       </c>
       <c r="AQ13" s="126">
@@ -8721,23 +8721,23 @@
         <v>64</v>
       </c>
       <c r="AT13" s="128">
-        <f>(90%*AO13)+(10%*AP13*100)</f>
+        <f t="shared" ref="AT13:AT28" si="7">(90%*AO13)+(10%*AP13*100)</f>
         <v>390</v>
       </c>
       <c r="AU13" s="204">
-        <f>(AT13/$AT$48)*100</f>
+        <f t="shared" ref="AU13:AU28" si="8">(AT13/$AT$48)*100</f>
         <v>82.9787234042553</v>
       </c>
       <c r="AV13" s="205">
-        <f>(50%*AU13)+(50%*AQ13)</f>
+        <f t="shared" ref="AV13:AV28" si="9">(50%*AU13)+(50%*AQ13)</f>
         <v>85.4893617021277</v>
       </c>
       <c r="AW13" s="206">
-        <f>(50%*AV13)+(50%*AF13)</f>
+        <f t="shared" ref="AW13:AW28" si="10">(50%*AV13)+(50%*AF13)</f>
         <v>87.7474977524723</v>
       </c>
       <c r="AX13" s="205">
-        <f>84+((AW13-$AW$49)/($AW$48-$AW$49)*(92-84))</f>
+        <f t="shared" ref="AX13:AX28" si="11">84+((AW13-$AW$49)/($AW$48-$AW$49)*(92-84))</f>
         <v>89.4992036186914</v>
       </c>
       <c r="AY13" s="207">
@@ -8826,19 +8826,19 @@
         <v>100</v>
       </c>
       <c r="AC14" s="78">
-        <f>SUM(AB14+X14+V14+T14+S14+R14+P14+O14)</f>
+        <f t="shared" si="0"/>
         <v>800</v>
       </c>
       <c r="AD14" s="160">
-        <f>SUM(AA14+Z14+Y14+W14+U14+Q14)*100</f>
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="AE14" s="196">
-        <f>(0.8*AC14)+(0.2*AD14)</f>
+        <f t="shared" si="2"/>
         <v>740</v>
       </c>
       <c r="AF14" s="197">
-        <f>84+((AE14-$AE$48)/($AE$47-$AE$48)*(92-84))</f>
+        <f t="shared" si="3"/>
         <v>90.8732394366197</v>
       </c>
       <c r="AG14" s="160">
@@ -8851,7 +8851,7 @@
         <v>3</v>
       </c>
       <c r="AJ14" s="160">
-        <f>AQ14</f>
+        <f t="shared" si="4"/>
         <v>94</v>
       </c>
       <c r="AK14" s="160">
@@ -8865,11 +8865,11 @@
         <v>100</v>
       </c>
       <c r="AO14" s="161">
-        <f>AG14+AH14+AM14+AN14</f>
+        <f t="shared" si="5"/>
         <v>400</v>
       </c>
       <c r="AP14" s="161">
-        <f>AI14+AK14+AL14</f>
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="AQ14" s="126">
@@ -8879,23 +8879,23 @@
         <v>70</v>
       </c>
       <c r="AT14" s="128">
-        <f>(90%*AO14)+(10%*AP14*100)</f>
+        <f t="shared" si="7"/>
         <v>440</v>
       </c>
       <c r="AU14" s="204">
-        <f>(AT14/$AT$48)*100</f>
+        <f t="shared" si="8"/>
         <v>93.6170212765958</v>
       </c>
       <c r="AV14" s="205">
-        <f>(50%*AU14)+(50%*AQ14)</f>
+        <f t="shared" si="9"/>
         <v>93.8085106382979</v>
       </c>
       <c r="AW14" s="206">
-        <f>(50%*AV14)+(50%*AF14)</f>
+        <f t="shared" si="10"/>
         <v>92.3408750374588</v>
       </c>
       <c r="AX14" s="205">
-        <f>84+((AW14-$AW$49)/($AW$48-$AW$49)*(92-84))</f>
+        <f t="shared" si="11"/>
         <v>92</v>
       </c>
       <c r="AY14" s="207">
@@ -8982,19 +8982,19 @@
         <v>100</v>
       </c>
       <c r="AC15" s="78">
-        <f>SUM(AB15+X15+V15+T15+S15+R15+P15+O15)</f>
+        <f t="shared" si="0"/>
         <v>800</v>
       </c>
       <c r="AD15" s="160">
-        <f>SUM(AA15+Z15+Y15+W15+U15+Q15)*100</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE15" s="196">
-        <f>(0.8*AC15)+(0.2*AD15)</f>
+        <f t="shared" si="2"/>
         <v>640</v>
       </c>
       <c r="AF15" s="197">
-        <f>84+((AE15-$AE$48)/($AE$47-$AE$48)*(92-84))</f>
+        <f t="shared" si="3"/>
         <v>89.4647887323944</v>
       </c>
       <c r="AG15" s="160">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="AI15" s="160"/>
       <c r="AJ15" s="160">
-        <f>AQ15</f>
+        <f t="shared" si="4"/>
         <v>85</v>
       </c>
       <c r="AK15" s="160">
@@ -9021,11 +9021,11 @@
         <v>100</v>
       </c>
       <c r="AO15" s="161">
-        <f>AG15+AH15+AM15+AN15</f>
+        <f t="shared" si="5"/>
         <v>400</v>
       </c>
       <c r="AP15" s="161">
-        <f>AI15+AK15+AL15</f>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="AQ15" s="126">
@@ -9035,23 +9035,23 @@
         <v>78</v>
       </c>
       <c r="AT15" s="128">
-        <f>(90%*AO15)+(10%*AP15*100)</f>
+        <f t="shared" si="7"/>
         <v>430</v>
       </c>
       <c r="AU15" s="204">
-        <f>(AT15/$AT$48)*100</f>
+        <f t="shared" si="8"/>
         <v>91.4893617021277</v>
       </c>
       <c r="AV15" s="205">
-        <f>(50%*AU15)+(50%*AQ15)</f>
+        <f t="shared" si="9"/>
         <v>88.2446808510638</v>
       </c>
       <c r="AW15" s="206">
-        <f>(50%*AV15)+(50%*AF15)</f>
+        <f t="shared" si="10"/>
         <v>88.8547347917291</v>
       </c>
       <c r="AX15" s="205">
-        <f>84+((AW15-$AW$49)/($AW$48-$AW$49)*(92-84))</f>
+        <f t="shared" si="11"/>
         <v>90.1020224618277</v>
       </c>
       <c r="AY15" s="207">
@@ -9142,19 +9142,19 @@
         <v>93</v>
       </c>
       <c r="AC16" s="78">
-        <f>SUM(AB16+X16+V16+T16+S16+R16+P16+O16)</f>
+        <f t="shared" si="0"/>
         <v>793</v>
       </c>
       <c r="AD16" s="160">
-        <f>SUM(AA16+Z16+Y16+W16+U16+Q16)*100</f>
+        <f t="shared" si="1"/>
         <v>400</v>
       </c>
       <c r="AE16" s="196">
-        <f>(0.8*AC16)+(0.2*AD16)</f>
+        <f t="shared" si="2"/>
         <v>714.4</v>
       </c>
       <c r="AF16" s="197">
-        <f>84+((AE16-$AE$48)/($AE$47-$AE$48)*(92-84))</f>
+        <f t="shared" si="3"/>
         <v>90.512676056338</v>
       </c>
       <c r="AG16" s="160">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="AI16" s="160"/>
       <c r="AJ16" s="160">
-        <f>AQ16</f>
+        <f t="shared" si="4"/>
         <v>80</v>
       </c>
       <c r="AK16" s="160"/>
@@ -9177,11 +9177,11 @@
         <v>100</v>
       </c>
       <c r="AO16" s="161">
-        <f>AG16+AH16+AM16+AN16</f>
+        <f t="shared" si="5"/>
         <v>400</v>
       </c>
       <c r="AP16" s="161">
-        <f>AI16+AK16+AL16</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AQ16" s="126">
@@ -9191,23 +9191,23 @@
         <v>84</v>
       </c>
       <c r="AT16" s="128">
-        <f>(90%*AO16)+(10%*AP16*100)</f>
+        <f t="shared" si="7"/>
         <v>360</v>
       </c>
       <c r="AU16" s="204">
-        <f>(AT16/$AT$48)*100</f>
+        <f t="shared" si="8"/>
         <v>76.5957446808511</v>
       </c>
       <c r="AV16" s="205">
-        <f>(50%*AU16)+(50%*AQ16)</f>
+        <f t="shared" si="9"/>
         <v>78.2978723404255</v>
       </c>
       <c r="AW16" s="206">
-        <f>(50%*AV16)+(50%*AF16)</f>
+        <f t="shared" si="10"/>
         <v>84.4052741983818</v>
       </c>
       <c r="AX16" s="205">
-        <f>84+((AW16-$AW$49)/($AW$48-$AW$49)*(92-84))</f>
+        <f t="shared" si="11"/>
         <v>87.6795793964633</v>
       </c>
       <c r="AY16" s="207">
@@ -9286,19 +9286,19 @@
         <v>90</v>
       </c>
       <c r="AC17" s="78">
-        <f>SUM(AB17+X17+V17+T17+S17+R17+P17+O17)</f>
+        <f t="shared" si="0"/>
         <v>290</v>
       </c>
       <c r="AD17" s="160">
-        <f>SUM(AA17+Z17+Y17+W17+U17+Q17)*100</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="AE17" s="196">
-        <f>(0.8*AC17)+(0.2*AD17)</f>
+        <f t="shared" si="2"/>
         <v>252</v>
       </c>
       <c r="AF17" s="197">
-        <f>84+((AE17-$AE$48)/($AE$47-$AE$48)*(92-84))</f>
+        <f t="shared" si="3"/>
         <v>84</v>
       </c>
       <c r="AG17" s="160">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="AI17" s="160"/>
       <c r="AJ17" s="160">
-        <f>AQ17</f>
+        <f t="shared" si="4"/>
         <v>94</v>
       </c>
       <c r="AK17" s="160"/>
@@ -9319,11 +9319,11 @@
         <v>100</v>
       </c>
       <c r="AO17" s="161">
-        <f>AG17+AH17+AM17+AN17</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="AP17" s="161">
-        <f>AI17+AK17+AL17</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AQ17" s="126">
@@ -9333,23 +9333,23 @@
         <v>91</v>
       </c>
       <c r="AT17" s="128">
-        <f>(90%*AO17)+(10%*AP17*100)</f>
+        <f t="shared" si="7"/>
         <v>270</v>
       </c>
       <c r="AU17" s="204">
-        <f>(AT17/$AT$48)*100</f>
+        <f t="shared" si="8"/>
         <v>57.4468085106383</v>
       </c>
       <c r="AV17" s="205">
-        <f>(50%*AU17)+(50%*AQ17)</f>
+        <f t="shared" si="9"/>
         <v>75.7234042553192</v>
       </c>
       <c r="AW17" s="206">
-        <f>(50%*AV17)+(50%*AF17)</f>
+        <f t="shared" si="10"/>
         <v>79.8617021276596</v>
       </c>
       <c r="AX17" s="205">
-        <f>84+((AW17-$AW$49)/($AW$48-$AW$49)*(92-84))</f>
+        <f t="shared" si="11"/>
         <v>85.2058987280332</v>
       </c>
       <c r="AY17" s="207">
@@ -9440,19 +9440,19 @@
         <v>90</v>
       </c>
       <c r="AC18" s="78">
-        <f>SUM(AB18+X18+V18+T18+S18+R18+P18+O18)</f>
+        <f t="shared" si="0"/>
         <v>790</v>
       </c>
       <c r="AD18" s="160">
-        <f>SUM(AA18+Z18+Y18+W18+U18+Q18)*100</f>
+        <f t="shared" si="1"/>
         <v>200</v>
       </c>
       <c r="AE18" s="196">
-        <f>(0.8*AC18)+(0.2*AD18)</f>
+        <f t="shared" si="2"/>
         <v>672</v>
       </c>
       <c r="AF18" s="197">
-        <f>84+((AE18-$AE$48)/($AE$47-$AE$48)*(92-84))</f>
+        <f t="shared" si="3"/>
         <v>89.9154929577465</v>
       </c>
       <c r="AG18" s="160">
@@ -9465,7 +9465,7 @@
         <v>1</v>
       </c>
       <c r="AJ18" s="160">
-        <f>AQ18</f>
+        <f t="shared" si="4"/>
         <v>88</v>
       </c>
       <c r="AK18" s="160">
@@ -9477,11 +9477,11 @@
       </c>
       <c r="AN18" s="161"/>
       <c r="AO18" s="161">
-        <f>AG18+AH18+AM18+AN18</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="AP18" s="161">
-        <f>AI18+AK18+AL18</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="AQ18" s="126">
@@ -9491,23 +9491,23 @@
         <v>97</v>
       </c>
       <c r="AT18" s="128">
-        <f>(90%*AO18)+(10%*AP18*100)</f>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="AU18" s="204">
-        <f>(AT18/$AT$48)*100</f>
+        <f t="shared" si="8"/>
         <v>63.8297872340426</v>
       </c>
       <c r="AV18" s="205">
-        <f>(50%*AU18)+(50%*AQ18)</f>
+        <f t="shared" si="9"/>
         <v>75.9148936170213</v>
       </c>
       <c r="AW18" s="206">
-        <f>(50%*AV18)+(50%*AF18)</f>
+        <f t="shared" si="10"/>
         <v>82.9151932873839</v>
       </c>
       <c r="AX18" s="205">
-        <f>84+((AW18-$AW$49)/($AW$48-$AW$49)*(92-84))</f>
+        <f t="shared" si="11"/>
         <v>86.868326865072</v>
       </c>
       <c r="AY18" s="207">
@@ -9596,19 +9596,19 @@
         <v>100</v>
       </c>
       <c r="AC19" s="78">
-        <f>SUM(AB19+X19+V19+T19+S19+R19+P19+O19)</f>
+        <f t="shared" si="0"/>
         <v>800</v>
       </c>
       <c r="AD19" s="160">
-        <f>SUM(AA19+Z19+Y19+W19+U19+Q19)*100</f>
+        <f t="shared" si="1"/>
         <v>200</v>
       </c>
       <c r="AE19" s="196">
-        <f>(0.8*AC19)+(0.2*AD19)</f>
+        <f t="shared" si="2"/>
         <v>680</v>
       </c>
       <c r="AF19" s="197">
-        <f>84+((AE19-$AE$48)/($AE$47-$AE$48)*(92-84))</f>
+        <f t="shared" si="3"/>
         <v>90.0281690140845</v>
       </c>
       <c r="AG19" s="160">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AI19" s="160"/>
       <c r="AJ19" s="160">
-        <f>AQ19</f>
+        <f t="shared" si="4"/>
         <v>91</v>
       </c>
       <c r="AK19" s="160">
@@ -9633,11 +9633,11 @@
         <v>100</v>
       </c>
       <c r="AO19" s="161">
-        <f>AG19+AH19+AM19+AN19</f>
+        <f t="shared" si="5"/>
         <v>400</v>
       </c>
       <c r="AP19" s="161">
-        <f>AI19+AK19+AL19</f>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="AQ19" s="126">
@@ -9647,23 +9647,23 @@
         <v>103</v>
       </c>
       <c r="AT19" s="128">
-        <f>(90%*AO19)+(10%*AP19*100)</f>
+        <f t="shared" si="7"/>
         <v>400</v>
       </c>
       <c r="AU19" s="204">
-        <f>(AT19/$AT$48)*100</f>
+        <f t="shared" si="8"/>
         <v>85.1063829787234</v>
       </c>
       <c r="AV19" s="205">
-        <f>(50%*AU19)+(50%*AQ19)</f>
+        <f t="shared" si="9"/>
         <v>88.0531914893617</v>
       </c>
       <c r="AW19" s="206">
-        <f>(50%*AV19)+(50%*AF19)</f>
+        <f t="shared" si="10"/>
         <v>89.0406802517231</v>
       </c>
       <c r="AX19" s="205">
-        <f>84+((AW19-$AW$49)/($AW$48-$AW$49)*(92-84))</f>
+        <f t="shared" si="11"/>
         <v>90.2032577195963</v>
       </c>
       <c r="AY19" s="207">
@@ -9752,19 +9752,19 @@
         <v>85</v>
       </c>
       <c r="AC20" s="78">
-        <f>SUM(AB20+X20+V20+T20+S20+R20+P20+O20)</f>
+        <f t="shared" si="0"/>
         <v>785</v>
       </c>
       <c r="AD20" s="160">
-        <f>SUM(AA20+Z20+Y20+W20+U20+Q20)*100</f>
+        <f t="shared" si="1"/>
         <v>200</v>
       </c>
       <c r="AE20" s="196">
-        <f>(0.8*AC20)+(0.2*AD20)</f>
+        <f t="shared" si="2"/>
         <v>668</v>
       </c>
       <c r="AF20" s="197">
-        <f>84+((AE20-$AE$48)/($AE$47-$AE$48)*(92-84))</f>
+        <f t="shared" si="3"/>
         <v>89.8591549295775</v>
       </c>
       <c r="AG20" s="160">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="AI20" s="160"/>
       <c r="AJ20" s="160">
-        <f>AQ20</f>
+        <f t="shared" si="4"/>
         <v>82</v>
       </c>
       <c r="AK20" s="160">
@@ -9789,11 +9789,11 @@
         <v>100</v>
       </c>
       <c r="AO20" s="161">
-        <f>AG20+AH20+AM20+AN20</f>
+        <f t="shared" si="5"/>
         <v>400</v>
       </c>
       <c r="AP20" s="161">
-        <f>AI20+AK20+AL20</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="AQ20" s="126">
@@ -9803,23 +9803,23 @@
         <v>109</v>
       </c>
       <c r="AT20" s="128">
-        <f>(90%*AO20)+(10%*AP20*100)</f>
+        <f t="shared" si="7"/>
         <v>390</v>
       </c>
       <c r="AU20" s="204">
-        <f>(AT20/$AT$48)*100</f>
+        <f t="shared" si="8"/>
         <v>82.9787234042553</v>
       </c>
       <c r="AV20" s="205">
-        <f>(50%*AU20)+(50%*AQ20)</f>
+        <f t="shared" si="9"/>
         <v>82.4893617021277</v>
       </c>
       <c r="AW20" s="206">
-        <f>(50%*AV20)+(50%*AF20)</f>
+        <f t="shared" si="10"/>
         <v>86.1742583158526</v>
       </c>
       <c r="AX20" s="205">
-        <f>84+((AW20-$AW$49)/($AW$48-$AW$49)*(92-84))</f>
+        <f t="shared" si="11"/>
         <v>88.6426766569524</v>
       </c>
       <c r="AY20" s="207">
@@ -9908,19 +9908,19 @@
         <v>100</v>
       </c>
       <c r="AC21" s="78">
-        <f>SUM(AB21+X21+V21+T21+S21+R21+P21+O21)</f>
+        <f t="shared" si="0"/>
         <v>800</v>
       </c>
       <c r="AD21" s="160">
-        <f>SUM(AA21+Z21+Y21+W21+U21+Q21)*100</f>
+        <f t="shared" si="1"/>
         <v>400</v>
       </c>
       <c r="AE21" s="196">
-        <f>(0.8*AC21)+(0.2*AD21)</f>
+        <f t="shared" si="2"/>
         <v>720</v>
       </c>
       <c r="AF21" s="197">
-        <f>84+((AE21-$AE$48)/($AE$47-$AE$48)*(92-84))</f>
+        <f t="shared" si="3"/>
         <v>90.5915492957747</v>
       </c>
       <c r="AG21" s="160">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="AI21" s="160"/>
       <c r="AJ21" s="160">
-        <f>AQ21</f>
+        <f t="shared" si="4"/>
         <v>91</v>
       </c>
       <c r="AK21" s="160"/>
@@ -9945,11 +9945,11 @@
         <v>100</v>
       </c>
       <c r="AO21" s="161">
-        <f>AG21+AH21+AM21+AN21</f>
+        <f t="shared" si="5"/>
         <v>400</v>
       </c>
       <c r="AP21" s="161">
-        <f>AI21+AK21+AL21</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AQ21" s="126">
@@ -9959,23 +9959,23 @@
         <v>116</v>
       </c>
       <c r="AT21" s="128">
-        <f>(90%*AO21)+(10%*AP21*100)</f>
+        <f t="shared" si="7"/>
         <v>370</v>
       </c>
       <c r="AU21" s="204">
-        <f>(AT21/$AT$48)*100</f>
+        <f t="shared" si="8"/>
         <v>78.7234042553192</v>
       </c>
       <c r="AV21" s="205">
-        <f>(50%*AU21)+(50%*AQ21)</f>
+        <f t="shared" si="9"/>
         <v>84.8617021276596</v>
       </c>
       <c r="AW21" s="206">
-        <f>(50%*AV21)+(50%*AF21)</f>
+        <f t="shared" si="10"/>
         <v>87.7266257117171</v>
       </c>
       <c r="AX21" s="205">
-        <f>84+((AW21-$AW$49)/($AW$48-$AW$49)*(92-84))</f>
+        <f t="shared" si="11"/>
         <v>89.4878401445519</v>
       </c>
       <c r="AY21" s="207">
@@ -10066,19 +10066,19 @@
         <v>100</v>
       </c>
       <c r="AC22" s="78">
-        <f>SUM(AB22+X22+V22+T22+S22+R22+P22+O22)</f>
+        <f t="shared" si="0"/>
         <v>800</v>
       </c>
       <c r="AD22" s="160">
-        <f>SUM(AA22+Z22+Y22+W22+U22+Q22)*100</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="AE22" s="196">
-        <f>(0.8*AC22)+(0.2*AD22)</f>
+        <f t="shared" si="2"/>
         <v>700</v>
       </c>
       <c r="AF22" s="197">
-        <f>84+((AE22-$AE$48)/($AE$47-$AE$48)*(92-84))</f>
+        <f t="shared" si="3"/>
         <v>90.3098591549296</v>
       </c>
       <c r="AG22" s="160">
@@ -10091,7 +10091,7 @@
         <v>1</v>
       </c>
       <c r="AJ22" s="160">
-        <f>AQ22</f>
+        <f t="shared" si="4"/>
         <v>82</v>
       </c>
       <c r="AK22" s="160"/>
@@ -10103,11 +10103,11 @@
         <v>100</v>
       </c>
       <c r="AO22" s="161">
-        <f>AG22+AH22+AM22+AN22</f>
+        <f t="shared" si="5"/>
         <v>400</v>
       </c>
       <c r="AP22" s="161">
-        <f>AI22+AK22+AL22</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AQ22" s="126">
@@ -10117,23 +10117,23 @@
         <v>123</v>
       </c>
       <c r="AT22" s="128">
-        <f>(90%*AO22)+(10%*AP22*100)</f>
+        <f t="shared" si="7"/>
         <v>370</v>
       </c>
       <c r="AU22" s="204">
-        <f>(AT22/$AT$48)*100</f>
+        <f t="shared" si="8"/>
         <v>78.7234042553192</v>
       </c>
       <c r="AV22" s="205">
-        <f>(50%*AU22)+(50%*AQ22)</f>
+        <f t="shared" si="9"/>
         <v>80.3617021276596</v>
       </c>
       <c r="AW22" s="206">
-        <f>(50%*AV22)+(50%*AF22)</f>
+        <f t="shared" si="10"/>
         <v>85.3357806412946</v>
       </c>
       <c r="AX22" s="205">
-        <f>84+((AW22-$AW$49)/($AW$48-$AW$49)*(92-84))</f>
+        <f t="shared" si="11"/>
         <v>88.1861798781669</v>
       </c>
       <c r="AY22" s="207">
@@ -10222,19 +10222,19 @@
         <v>99</v>
       </c>
       <c r="AC23" s="78">
-        <f>SUM(AB23+X23+V23+T23+S23+R23+P23+O23)</f>
+        <f t="shared" si="0"/>
         <v>799</v>
       </c>
       <c r="AD23" s="160">
-        <f>SUM(AA23+Z23+Y23+W23+U23+Q23)*100</f>
+        <f t="shared" si="1"/>
         <v>200</v>
       </c>
       <c r="AE23" s="196">
-        <f>(0.8*AC23)+(0.2*AD23)</f>
+        <f t="shared" si="2"/>
         <v>679.2</v>
       </c>
       <c r="AF23" s="197">
-        <f>84+((AE23-$AE$48)/($AE$47-$AE$48)*(92-84))</f>
+        <f t="shared" si="3"/>
         <v>90.0169014084507</v>
       </c>
       <c r="AG23" s="160">
@@ -10247,7 +10247,7 @@
         <v>1</v>
       </c>
       <c r="AJ23" s="160">
-        <f>AQ23</f>
+        <f t="shared" si="4"/>
         <v>88</v>
       </c>
       <c r="AK23" s="160">
@@ -10261,11 +10261,11 @@
         <v>100</v>
       </c>
       <c r="AO23" s="161">
-        <f>AG23+AH23+AM23+AN23</f>
+        <f t="shared" si="5"/>
         <v>400</v>
       </c>
       <c r="AP23" s="161">
-        <f>AI23+AK23+AL23</f>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="AQ23" s="126">
@@ -10275,23 +10275,23 @@
         <v>131</v>
       </c>
       <c r="AT23" s="128">
-        <f>(90%*AO23)+(10%*AP23*100)</f>
+        <f t="shared" si="7"/>
         <v>420</v>
       </c>
       <c r="AU23" s="204">
-        <f>(AT23/$AT$48)*100</f>
+        <f t="shared" si="8"/>
         <v>89.3617021276596</v>
       </c>
       <c r="AV23" s="205">
-        <f>(50%*AU23)+(50%*AQ23)</f>
+        <f t="shared" si="9"/>
         <v>88.6808510638298</v>
       </c>
       <c r="AW23" s="206">
-        <f>(50%*AV23)+(50%*AF23)</f>
+        <f t="shared" si="10"/>
         <v>89.3488762361402</v>
       </c>
       <c r="AX23" s="205">
-        <f>84+((AW23-$AW$49)/($AW$48-$AW$49)*(92-84))</f>
+        <f t="shared" si="11"/>
         <v>90.3710504687535</v>
       </c>
       <c r="AY23" s="207">
@@ -10378,19 +10378,19 @@
         <v>85</v>
       </c>
       <c r="AC24" s="78">
-        <f>SUM(AB24+X24+V24+T24+S24+R24+P24+O24)</f>
+        <f t="shared" si="0"/>
         <v>785</v>
       </c>
       <c r="AD24" s="160">
-        <f>SUM(AA24+Z24+Y24+W24+U24+Q24)*100</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE24" s="196">
-        <f>(0.8*AC24)+(0.2*AD24)</f>
+        <f t="shared" si="2"/>
         <v>628</v>
       </c>
       <c r="AF24" s="197">
-        <f>84+((AE24-$AE$48)/($AE$47-$AE$48)*(92-84))</f>
+        <f t="shared" si="3"/>
         <v>89.2957746478873</v>
       </c>
       <c r="AG24" s="160">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="AI24" s="160"/>
       <c r="AJ24" s="160">
-        <f>AQ24</f>
+        <f t="shared" si="4"/>
         <v>82</v>
       </c>
       <c r="AK24" s="160"/>
@@ -10411,11 +10411,11 @@
         <v>100</v>
       </c>
       <c r="AO24" s="161">
-        <f>AG24+AH24+AM24+AN24</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="AP24" s="161">
-        <f>AI24+AK24+AL24</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AQ24" s="126">
@@ -10425,23 +10425,23 @@
         <v>137</v>
       </c>
       <c r="AT24" s="128">
-        <f>(90%*AO24)+(10%*AP24*100)</f>
+        <f t="shared" si="7"/>
         <v>270</v>
       </c>
       <c r="AU24" s="204">
-        <f>(AT24/$AT$48)*100</f>
+        <f t="shared" si="8"/>
         <v>57.4468085106383</v>
       </c>
       <c r="AV24" s="205">
-        <f>(50%*AU24)+(50%*AQ24)</f>
+        <f t="shared" si="9"/>
         <v>69.7234042553192</v>
       </c>
       <c r="AW24" s="206">
-        <f>(50%*AV24)+(50%*AF24)</f>
+        <f t="shared" si="10"/>
         <v>79.5095894516032</v>
       </c>
       <c r="AX24" s="205">
-        <f>84+((AW24-$AW$49)/($AW$48-$AW$49)*(92-84))</f>
+        <f t="shared" si="11"/>
         <v>85.0141961851194</v>
       </c>
       <c r="AY24" s="207">
@@ -10528,19 +10528,19 @@
         <v>100</v>
       </c>
       <c r="AC25" s="78">
-        <f>SUM(AB25+X25+V25+T25+S25+R25+P25+O25)</f>
+        <f t="shared" si="0"/>
         <v>800</v>
       </c>
       <c r="AD25" s="160">
-        <f>SUM(AA25+Z25+Y25+W25+U25+Q25)*100</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE25" s="196">
-        <f>(0.8*AC25)+(0.2*AD25)</f>
+        <f t="shared" si="2"/>
         <v>640</v>
       </c>
       <c r="AF25" s="197">
-        <f>84+((AE25-$AE$48)/($AE$47-$AE$48)*(92-84))</f>
+        <f t="shared" si="3"/>
         <v>89.4647887323944</v>
       </c>
       <c r="AG25" s="160">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="AI25" s="160"/>
       <c r="AJ25" s="160">
-        <f>AQ25</f>
+        <f t="shared" si="4"/>
         <v>91</v>
       </c>
       <c r="AK25" s="160"/>
@@ -10563,11 +10563,11 @@
         <v>100</v>
       </c>
       <c r="AO25" s="161">
-        <f>AG25+AH25+AM25+AN25</f>
+        <f t="shared" si="5"/>
         <v>400</v>
       </c>
       <c r="AP25" s="161">
-        <f>AI25+AK25+AL25</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AQ25" s="126">
@@ -10577,23 +10577,23 @@
         <v>145</v>
       </c>
       <c r="AT25" s="128">
-        <f>(90%*AO25)+(10%*AP25*100)</f>
+        <f t="shared" si="7"/>
         <v>360</v>
       </c>
       <c r="AU25" s="204">
-        <f>(AT25/$AT$48)*100</f>
+        <f t="shared" si="8"/>
         <v>76.5957446808511</v>
       </c>
       <c r="AV25" s="205">
-        <f>(50%*AU25)+(50%*AQ25)</f>
+        <f t="shared" si="9"/>
         <v>83.7978723404255</v>
       </c>
       <c r="AW25" s="206">
-        <f>(50%*AV25)+(50%*AF25)</f>
+        <f t="shared" si="10"/>
         <v>86.6313305364099</v>
       </c>
       <c r="AX25" s="205">
-        <f>84+((AW25-$AW$49)/($AW$48-$AW$49)*(92-84))</f>
+        <f t="shared" si="11"/>
         <v>88.8915228727646</v>
       </c>
       <c r="AY25" s="207">
@@ -10688,19 +10688,19 @@
         <v>100</v>
       </c>
       <c r="AC26" s="78">
-        <f>SUM(AB26+X26+V26+T26+S26+R26+P26+O26)</f>
+        <f t="shared" si="0"/>
         <v>800</v>
       </c>
       <c r="AD26" s="160">
-        <f>SUM(AA26+Z26+Y26+W26+U26+Q26)*100</f>
+        <f t="shared" si="1"/>
         <v>700</v>
       </c>
       <c r="AE26" s="196">
-        <f>(0.8*AC26)+(0.2*AD26)</f>
+        <f t="shared" si="2"/>
         <v>780</v>
       </c>
       <c r="AF26" s="197">
-        <f>84+((AE26-$AE$48)/($AE$47-$AE$48)*(92-84))</f>
+        <f t="shared" si="3"/>
         <v>91.4366197183099</v>
       </c>
       <c r="AG26" s="160">
@@ -10713,7 +10713,7 @@
         <v>2</v>
       </c>
       <c r="AJ26" s="160">
-        <f>AQ26</f>
+        <f t="shared" si="4"/>
         <v>85</v>
       </c>
       <c r="AK26" s="160">
@@ -10727,11 +10727,11 @@
         <v>100</v>
       </c>
       <c r="AO26" s="161">
-        <f>AG26+AH26+AM26+AN26</f>
+        <f t="shared" si="5"/>
         <v>400</v>
       </c>
       <c r="AP26" s="161">
-        <f>AI26+AK26+AL26</f>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="AQ26" s="126">
@@ -10741,23 +10741,23 @@
         <v>152</v>
       </c>
       <c r="AT26" s="128">
-        <f>(90%*AO26)+(10%*AP26*100)</f>
+        <f t="shared" si="7"/>
         <v>430</v>
       </c>
       <c r="AU26" s="204">
-        <f>(AT26/$AT$48)*100</f>
+        <f t="shared" si="8"/>
         <v>91.4893617021277</v>
       </c>
       <c r="AV26" s="205">
-        <f>(50%*AU26)+(50%*AQ26)</f>
+        <f t="shared" si="9"/>
         <v>88.2446808510638</v>
       </c>
       <c r="AW26" s="206">
-        <f>(50%*AV26)+(50%*AF26)</f>
+        <f t="shared" si="10"/>
         <v>89.8406502846868</v>
       </c>
       <c r="AX26" s="205">
-        <f>84+((AW26-$AW$49)/($AW$48-$AW$49)*(92-84))</f>
+        <f t="shared" si="11"/>
         <v>90.6387895819865</v>
       </c>
       <c r="AY26" s="207">
@@ -10846,19 +10846,19 @@
         <v>99</v>
       </c>
       <c r="AC27" s="78">
-        <f>SUM(AB27+X27+V27+T27+S27+R27+P27+O27)</f>
+        <f t="shared" si="0"/>
         <v>799</v>
       </c>
       <c r="AD27" s="160">
-        <f>SUM(AA27+Z27+Y27+W27+U27+Q27)*100</f>
+        <f t="shared" si="1"/>
         <v>400</v>
       </c>
       <c r="AE27" s="196">
-        <f>(0.8*AC27)+(0.2*AD27)</f>
+        <f t="shared" si="2"/>
         <v>719.2</v>
       </c>
       <c r="AF27" s="197">
-        <f>84+((AE27-$AE$48)/($AE$47-$AE$48)*(92-84))</f>
+        <f t="shared" si="3"/>
         <v>90.5802816901409</v>
       </c>
       <c r="AG27" s="160">
@@ -10869,7 +10869,7 @@
       </c>
       <c r="AI27" s="160"/>
       <c r="AJ27" s="160">
-        <f>AQ27</f>
+        <f t="shared" si="4"/>
         <v>94</v>
       </c>
       <c r="AK27" s="160">
@@ -10885,11 +10885,11 @@
         <v>100</v>
       </c>
       <c r="AO27" s="161">
-        <f>AG27+AH27+AM27+AN27</f>
+        <f t="shared" si="5"/>
         <v>400</v>
       </c>
       <c r="AP27" s="161">
-        <f>AI27+AK27+AL27</f>
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="AQ27" s="126">
@@ -10899,23 +10899,23 @@
         <v>159</v>
       </c>
       <c r="AT27" s="128">
-        <f>(90%*AO27)+(10%*AP27*100)</f>
+        <f t="shared" si="7"/>
         <v>440</v>
       </c>
       <c r="AU27" s="204">
-        <f>(AT27/$AT$48)*100</f>
+        <f t="shared" si="8"/>
         <v>93.6170212765958</v>
       </c>
       <c r="AV27" s="205">
-        <f>(50%*AU27)+(50%*AQ27)</f>
+        <f t="shared" si="9"/>
         <v>93.8085106382979</v>
       </c>
       <c r="AW27" s="206">
-        <f>(50%*AV27)+(50%*AF27)</f>
+        <f t="shared" si="10"/>
         <v>92.1943961642194</v>
       </c>
       <c r="AX27" s="205">
-        <f>84+((AW27-$AW$49)/($AW$48-$AW$49)*(92-84))</f>
+        <f t="shared" si="11"/>
         <v>91.9202517421478</v>
       </c>
       <c r="AY27" s="207">
@@ -10992,19 +10992,19 @@
         <v>90</v>
       </c>
       <c r="AC28" s="78">
-        <f>SUM(AB28+X28+V28+T28+S28+R28+P28+O28)</f>
+        <f t="shared" si="0"/>
         <v>790</v>
       </c>
       <c r="AD28" s="160">
-        <f>SUM(AA28+Z28+Y28+W28+U28+Q28)*100</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE28" s="196">
-        <f>(0.8*AC28)+(0.2*AD28)</f>
+        <f t="shared" si="2"/>
         <v>632</v>
       </c>
       <c r="AF28" s="197">
-        <f>84+((AE28-$AE$48)/($AE$47-$AE$48)*(92-84))</f>
+        <f t="shared" si="3"/>
         <v>89.3521126760563</v>
       </c>
       <c r="AG28" s="160">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="AI28" s="160"/>
       <c r="AJ28" s="160">
-        <f>AQ28</f>
+        <f t="shared" si="4"/>
         <v>76</v>
       </c>
       <c r="AK28" s="160">
@@ -11029,11 +11029,11 @@
         <v>100</v>
       </c>
       <c r="AO28" s="161">
-        <f>AG28+AH28+AM28+AN28</f>
+        <f t="shared" si="5"/>
         <v>400</v>
       </c>
       <c r="AP28" s="161">
-        <f>AI28+AK28+AL28</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="AQ28" s="126">
@@ -11043,23 +11043,23 @@
         <v>164</v>
       </c>
       <c r="AT28" s="128">
-        <f>(90%*AO28)+(10%*AP28*100)</f>
+        <f t="shared" si="7"/>
         <v>380</v>
       </c>
       <c r="AU28" s="204">
-        <f>(AT28/$AT$48)*100</f>
+        <f t="shared" si="8"/>
         <v>80.8510638297872</v>
       </c>
       <c r="AV28" s="205">
-        <f>(50%*AU28)+(50%*AQ28)</f>
+        <f t="shared" si="9"/>
         <v>78.4255319148936</v>
       </c>
       <c r="AW28" s="206">
-        <f>(50%*AV28)+(50%*AF28)</f>
+        <f t="shared" si="10"/>
         <v>83.888822295475</v>
       </c>
       <c r="AX28" s="205">
-        <f>84+((AW28-$AW$49)/($AW$48-$AW$49)*(92-84))</f>
+        <f t="shared" si="11"/>
         <v>87.3984047901163</v>
       </c>
       <c r="AY28" s="207">
@@ -11152,19 +11152,19 @@
         <v>100</v>
       </c>
       <c r="AC29" s="78">
-        <f t="shared" ref="AC29:AC46" si="0">SUM(AB29+X29+V29+T29+S29+R29+P29+O29)</f>
+        <f t="shared" ref="AC29:AC46" si="12">SUM(AB29+X29+V29+T29+S29+R29+P29+O29)</f>
         <v>800</v>
       </c>
       <c r="AD29" s="160">
-        <f t="shared" ref="AD29:AD46" si="1">SUM(AA29+Z29+Y29+W29+U29+Q29)*100</f>
+        <f t="shared" ref="AD29:AD46" si="13">SUM(AA29+Z29+Y29+W29+U29+Q29)*100</f>
         <v>400</v>
       </c>
       <c r="AE29" s="196">
-        <f t="shared" ref="AE29:AE46" si="2">(0.8*AC29)+(0.2*AD29)</f>
+        <f t="shared" ref="AE29:AE46" si="14">(0.8*AC29)+(0.2*AD29)</f>
         <v>720</v>
       </c>
       <c r="AF29" s="197">
-        <f t="shared" ref="AF29:AF46" si="3">84+((AE29-$AE$48)/($AE$47-$AE$48)*(92-84))</f>
+        <f t="shared" ref="AF29:AF46" si="15">84+((AE29-$AE$48)/($AE$47-$AE$48)*(92-84))</f>
         <v>90.5915492957747</v>
       </c>
       <c r="AG29" s="160">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="AI29" s="160"/>
       <c r="AJ29" s="160">
-        <f t="shared" ref="AJ29:AJ46" si="4">AQ29</f>
+        <f t="shared" ref="AJ29:AJ46" si="16">AQ29</f>
         <v>94</v>
       </c>
       <c r="AK29" s="160">
@@ -11189,11 +11189,11 @@
         <v>100</v>
       </c>
       <c r="AO29" s="161">
-        <f t="shared" ref="AO29:AO46" si="5">AG29+AH29+AM29+AN29</f>
+        <f t="shared" ref="AO29:AO46" si="17">AG29+AH29+AM29+AN29</f>
         <v>400</v>
       </c>
       <c r="AP29" s="161">
-        <f t="shared" ref="AP29:AP46" si="6">AI29+AK29+AL29</f>
+        <f t="shared" ref="AP29:AP46" si="18">AI29+AK29+AL29</f>
         <v>5</v>
       </c>
       <c r="AQ29" s="126">
@@ -11203,23 +11203,23 @@
         <v>172</v>
       </c>
       <c r="AT29" s="128">
-        <f t="shared" ref="AT29:AT46" si="7">(90%*AO29)+(10%*AP29*100)</f>
+        <f t="shared" ref="AT29:AT46" si="19">(90%*AO29)+(10%*AP29*100)</f>
         <v>410</v>
       </c>
       <c r="AU29" s="204">
-        <f t="shared" ref="AU29:AU46" si="8">(AT29/$AT$48)*100</f>
+        <f t="shared" ref="AU29:AU46" si="20">(AT29/$AT$48)*100</f>
         <v>87.2340425531915</v>
       </c>
       <c r="AV29" s="205">
-        <f t="shared" ref="AV29:AV46" si="9">(50%*AU29)+(50%*AQ29)</f>
+        <f t="shared" ref="AV29:AV46" si="21">(50%*AU29)+(50%*AQ29)</f>
         <v>90.6170212765958</v>
       </c>
       <c r="AW29" s="206">
-        <f t="shared" ref="AW29:AW46" si="10">(50%*AV29)+(50%*AF29)</f>
+        <f t="shared" ref="AW29:AW46" si="22">(50%*AV29)+(50%*AF29)</f>
         <v>90.6042852861852</v>
       </c>
       <c r="AX29" s="205">
-        <f t="shared" ref="AX29:AX46" si="11">84+((AW29-$AW$49)/($AW$48-$AW$49)*(92-84))</f>
+        <f t="shared" ref="AX29:AX46" si="23">84+((AW29-$AW$49)/($AW$48-$AW$49)*(92-84))</f>
         <v>91.054539373459</v>
       </c>
       <c r="AY29" s="207">
@@ -11308,19 +11308,19 @@
         <v>95</v>
       </c>
       <c r="AC30" s="78">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>795</v>
       </c>
       <c r="AD30" s="160">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>200</v>
       </c>
       <c r="AE30" s="196">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>676</v>
       </c>
       <c r="AF30" s="197">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>89.9718309859155</v>
       </c>
       <c r="AG30" s="160">
@@ -11331,7 +11331,7 @@
       </c>
       <c r="AI30" s="160"/>
       <c r="AJ30" s="160">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>72</v>
       </c>
       <c r="AK30" s="160">
@@ -11345,11 +11345,11 @@
         <v>100</v>
       </c>
       <c r="AO30" s="161">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>400</v>
       </c>
       <c r="AP30" s="161">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>3</v>
       </c>
       <c r="AQ30" s="126">
@@ -11359,23 +11359,23 @@
         <v>179</v>
       </c>
       <c r="AT30" s="128">
-        <f t="shared" si="7"/>
+        <f t="shared" si="19"/>
         <v>390</v>
       </c>
       <c r="AU30" s="204">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>82.9787234042553</v>
       </c>
       <c r="AV30" s="205">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>77.4893617021277</v>
       </c>
       <c r="AW30" s="206">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>83.7305963440216</v>
       </c>
       <c r="AX30" s="205">
-        <f t="shared" si="11"/>
+        <f t="shared" si="23"/>
         <v>87.3122610091303</v>
       </c>
       <c r="AY30" s="207">
@@ -11472,19 +11472,19 @@
         <v>100</v>
       </c>
       <c r="AC31" s="78">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>800</v>
       </c>
       <c r="AD31" s="160">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>900</v>
       </c>
       <c r="AE31" s="196">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>820</v>
       </c>
       <c r="AF31" s="197">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>92</v>
       </c>
       <c r="AG31" s="160">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="AI31" s="160"/>
       <c r="AJ31" s="160">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>91</v>
       </c>
       <c r="AK31" s="160">
@@ -11509,11 +11509,11 @@
         <v>100</v>
       </c>
       <c r="AO31" s="161">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>400</v>
       </c>
       <c r="AP31" s="161">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>4</v>
       </c>
       <c r="AQ31" s="126">
@@ -11523,23 +11523,23 @@
         <v>185</v>
       </c>
       <c r="AT31" s="128">
-        <f t="shared" si="7"/>
+        <f t="shared" si="19"/>
         <v>400</v>
       </c>
       <c r="AU31" s="204">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>85.1063829787234</v>
       </c>
       <c r="AV31" s="205">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>88.0531914893617</v>
       </c>
       <c r="AW31" s="206">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>90.0265957446808</v>
       </c>
       <c r="AX31" s="205">
-        <f t="shared" si="11"/>
+        <f t="shared" si="23"/>
         <v>90.740024839755</v>
       </c>
       <c r="AY31" s="207">
@@ -11630,19 +11630,19 @@
         <v>98</v>
       </c>
       <c r="AC32" s="78">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>798</v>
       </c>
       <c r="AD32" s="160">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>300</v>
       </c>
       <c r="AE32" s="196">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>698.4</v>
       </c>
       <c r="AF32" s="197">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>90.287323943662</v>
       </c>
       <c r="AG32" s="160">
@@ -11653,7 +11653,7 @@
       </c>
       <c r="AI32" s="160"/>
       <c r="AJ32" s="160">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>88</v>
       </c>
       <c r="AK32" s="160"/>
@@ -11665,11 +11665,11 @@
         <v>100</v>
       </c>
       <c r="AO32" s="161">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>400</v>
       </c>
       <c r="AP32" s="161">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AQ32" s="126">
@@ -11679,23 +11679,23 @@
         <v>191</v>
       </c>
       <c r="AT32" s="128">
-        <f t="shared" si="7"/>
+        <f t="shared" si="19"/>
         <v>360</v>
       </c>
       <c r="AU32" s="204">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>76.5957446808511</v>
       </c>
       <c r="AV32" s="205">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>82.2978723404255</v>
       </c>
       <c r="AW32" s="206">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>86.2925981420437</v>
       </c>
       <c r="AX32" s="205">
-        <f t="shared" si="11"/>
+        <f t="shared" si="23"/>
         <v>88.7071050264815</v>
       </c>
       <c r="AY32" s="207">
@@ -11788,19 +11788,19 @@
         <v>93</v>
       </c>
       <c r="AC33" s="78">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>793</v>
       </c>
       <c r="AD33" s="160">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>500</v>
       </c>
       <c r="AE33" s="196">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>734.4</v>
       </c>
       <c r="AF33" s="197">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>90.7943661971831</v>
       </c>
       <c r="AG33" s="160">
@@ -11813,7 +11813,7 @@
         <v>1</v>
       </c>
       <c r="AJ33" s="160">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>88</v>
       </c>
       <c r="AK33" s="160"/>
@@ -11825,11 +11825,11 @@
         <v>100</v>
       </c>
       <c r="AO33" s="161">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>400</v>
       </c>
       <c r="AP33" s="161">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="AQ33" s="126">
@@ -11839,23 +11839,23 @@
         <v>198</v>
       </c>
       <c r="AT33" s="128">
-        <f t="shared" si="7"/>
+        <f t="shared" si="19"/>
         <v>370</v>
       </c>
       <c r="AU33" s="204">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>78.7234042553192</v>
       </c>
       <c r="AV33" s="205">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>83.3617021276596</v>
       </c>
       <c r="AW33" s="206">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>87.0780341624213</v>
       </c>
       <c r="AX33" s="205">
-        <f t="shared" si="11"/>
+        <f t="shared" si="23"/>
         <v>89.1347240605046</v>
       </c>
       <c r="AY33" s="207">
@@ -11944,19 +11944,19 @@
         <v>99</v>
       </c>
       <c r="AC34" s="78">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>799</v>
       </c>
       <c r="AD34" s="160">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>200</v>
       </c>
       <c r="AE34" s="196">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>679.2</v>
       </c>
       <c r="AF34" s="197">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>90.0169014084507</v>
       </c>
       <c r="AG34" s="160">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="AI34" s="160"/>
       <c r="AJ34" s="160">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>88</v>
       </c>
       <c r="AK34" s="160">
@@ -11977,11 +11977,11 @@
       <c r="AM34" s="161"/>
       <c r="AN34" s="161"/>
       <c r="AO34" s="161">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>200</v>
       </c>
       <c r="AP34" s="161">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="AQ34" s="126">
@@ -11991,23 +11991,23 @@
         <v>205</v>
       </c>
       <c r="AT34" s="128">
-        <f t="shared" si="7"/>
+        <f t="shared" si="19"/>
         <v>200</v>
       </c>
       <c r="AU34" s="204">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>42.5531914893617</v>
       </c>
       <c r="AV34" s="205">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>65.2765957446808</v>
       </c>
       <c r="AW34" s="206">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>77.6467485765658</v>
       </c>
       <c r="AX34" s="205">
-        <f t="shared" si="11"/>
+        <f t="shared" si="23"/>
         <v>84</v>
       </c>
       <c r="AY34" s="207">
@@ -12102,19 +12102,19 @@
         <v>100</v>
       </c>
       <c r="AC35" s="78">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>800</v>
       </c>
       <c r="AD35" s="160">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>600</v>
       </c>
       <c r="AE35" s="196">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>760</v>
       </c>
       <c r="AF35" s="197">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>91.1549295774648</v>
       </c>
       <c r="AG35" s="160">
@@ -12125,7 +12125,7 @@
       </c>
       <c r="AI35" s="160"/>
       <c r="AJ35" s="160">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>91</v>
       </c>
       <c r="AK35" s="160">
@@ -12139,11 +12139,11 @@
         <v>100</v>
       </c>
       <c r="AO35" s="161">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>400</v>
       </c>
       <c r="AP35" s="161">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>5</v>
       </c>
       <c r="AQ35" s="126">
@@ -12153,23 +12153,23 @@
         <v>212</v>
       </c>
       <c r="AT35" s="128">
-        <f t="shared" si="7"/>
+        <f t="shared" si="19"/>
         <v>410</v>
       </c>
       <c r="AU35" s="204">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>87.2340425531915</v>
       </c>
       <c r="AV35" s="205">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>89.1170212765958</v>
       </c>
       <c r="AW35" s="206">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>90.1359754270303</v>
       </c>
       <c r="AX35" s="205">
-        <f t="shared" si="11"/>
+        <f t="shared" si="23"/>
         <v>90.7995749913836</v>
       </c>
       <c r="AY35" s="207">
@@ -12258,19 +12258,19 @@
         <v>100</v>
       </c>
       <c r="AC36" s="78">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>800</v>
       </c>
       <c r="AD36" s="160">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="AE36" s="196">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>660</v>
       </c>
       <c r="AF36" s="197">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>89.7464788732394</v>
       </c>
       <c r="AG36" s="160">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="AI36" s="160"/>
       <c r="AJ36" s="160">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>91</v>
       </c>
       <c r="AK36" s="160">
@@ -12295,11 +12295,11 @@
         <v>100</v>
       </c>
       <c r="AO36" s="161">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>400</v>
       </c>
       <c r="AP36" s="161">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>5</v>
       </c>
       <c r="AQ36" s="126">
@@ -12309,23 +12309,23 @@
         <v>219</v>
       </c>
       <c r="AT36" s="128">
-        <f t="shared" si="7"/>
+        <f t="shared" si="19"/>
         <v>410</v>
       </c>
       <c r="AU36" s="204">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>87.2340425531915</v>
       </c>
       <c r="AV36" s="205">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>89.1170212765958</v>
       </c>
       <c r="AW36" s="206">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>89.4317500749176</v>
       </c>
       <c r="AX36" s="205">
-        <f t="shared" si="11"/>
+        <f t="shared" si="23"/>
         <v>90.4161699055559</v>
       </c>
       <c r="AY36" s="207">
@@ -12416,19 +12416,19 @@
         <v>100</v>
       </c>
       <c r="AC37" s="78">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>800</v>
       </c>
       <c r="AD37" s="160">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>200</v>
       </c>
       <c r="AE37" s="196">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>680</v>
       </c>
       <c r="AF37" s="197">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>90.0281690140845</v>
       </c>
       <c r="AG37" s="160">
@@ -12441,7 +12441,7 @@
         <v>4</v>
       </c>
       <c r="AJ37" s="160">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>94</v>
       </c>
       <c r="AK37" s="160">
@@ -12451,11 +12451,11 @@
       <c r="AM37" s="161"/>
       <c r="AN37" s="161"/>
       <c r="AO37" s="161">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>200</v>
       </c>
       <c r="AP37" s="161">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>7</v>
       </c>
       <c r="AQ37" s="126">
@@ -12465,23 +12465,23 @@
         <v>226</v>
       </c>
       <c r="AT37" s="128">
-        <f t="shared" si="7"/>
+        <f t="shared" si="19"/>
         <v>250</v>
       </c>
       <c r="AU37" s="204">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>53.1914893617021</v>
       </c>
       <c r="AV37" s="205">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>73.5957446808511</v>
       </c>
       <c r="AW37" s="206">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>81.8119568474678</v>
       </c>
       <c r="AX37" s="205">
-        <f t="shared" si="11"/>
+        <f t="shared" si="23"/>
         <v>86.2676860891254</v>
       </c>
       <c r="AY37" s="207">
@@ -12574,19 +12574,19 @@
         <v>100</v>
       </c>
       <c r="AC38" s="78">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>800</v>
       </c>
       <c r="AD38" s="160">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>700</v>
       </c>
       <c r="AE38" s="196">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>780</v>
       </c>
       <c r="AF38" s="197">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>91.4366197183099</v>
       </c>
       <c r="AG38" s="160">
@@ -12599,7 +12599,7 @@
         <v>2</v>
       </c>
       <c r="AJ38" s="160">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>94</v>
       </c>
       <c r="AK38" s="160">
@@ -12613,11 +12613,11 @@
         <v>100</v>
       </c>
       <c r="AO38" s="161">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>400</v>
       </c>
       <c r="AP38" s="161">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>7</v>
       </c>
       <c r="AQ38" s="126">
@@ -12627,23 +12627,23 @@
         <v>233</v>
       </c>
       <c r="AT38" s="128">
-        <f t="shared" si="7"/>
+        <f t="shared" si="19"/>
         <v>430</v>
       </c>
       <c r="AU38" s="204">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>91.4893617021277</v>
       </c>
       <c r="AV38" s="205">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>92.7446808510638</v>
       </c>
       <c r="AW38" s="206">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>92.0906502846868</v>
       </c>
       <c r="AX38" s="205">
-        <f t="shared" si="11"/>
+        <f t="shared" si="23"/>
         <v>91.8637688312059</v>
       </c>
       <c r="AY38" s="207">
@@ -12730,19 +12730,19 @@
         <v>90</v>
       </c>
       <c r="AC39" s="78">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>690</v>
       </c>
       <c r="AD39" s="160">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="AE39" s="196">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>572</v>
       </c>
       <c r="AF39" s="197">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>88.5070422535211</v>
       </c>
       <c r="AG39" s="160">
@@ -12755,7 +12755,7 @@
         <v>1</v>
       </c>
       <c r="AJ39" s="160">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>91</v>
       </c>
       <c r="AK39" s="160">
@@ -12769,11 +12769,11 @@
         <v>100</v>
       </c>
       <c r="AO39" s="161">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>400</v>
       </c>
       <c r="AP39" s="161">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>4</v>
       </c>
       <c r="AQ39" s="126">
@@ -12783,23 +12783,23 @@
         <v>239</v>
       </c>
       <c r="AT39" s="128">
-        <f t="shared" si="7"/>
+        <f t="shared" si="19"/>
         <v>400</v>
       </c>
       <c r="AU39" s="204">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>85.1063829787234</v>
       </c>
       <c r="AV39" s="205">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>88.0531914893617</v>
       </c>
       <c r="AW39" s="206">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>88.2801168714414</v>
       </c>
       <c r="AX39" s="205">
-        <f t="shared" si="11"/>
+        <f t="shared" si="23"/>
         <v>89.7891802269024</v>
       </c>
       <c r="AY39" s="207">
@@ -12888,19 +12888,19 @@
         <v>90</v>
       </c>
       <c r="AC40" s="78">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>790</v>
       </c>
       <c r="AD40" s="160">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>200</v>
       </c>
       <c r="AE40" s="196">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>672</v>
       </c>
       <c r="AF40" s="197">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>89.9154929577465</v>
       </c>
       <c r="AG40" s="160">
@@ -12911,7 +12911,7 @@
       </c>
       <c r="AI40" s="160"/>
       <c r="AJ40" s="160">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>79</v>
       </c>
       <c r="AK40" s="160">
@@ -12925,11 +12925,11 @@
         <v>100</v>
       </c>
       <c r="AO40" s="161">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>400</v>
       </c>
       <c r="AP40" s="161">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="AQ40" s="126">
@@ -12939,23 +12939,23 @@
         <v>246</v>
       </c>
       <c r="AT40" s="128">
-        <f t="shared" si="7"/>
+        <f t="shared" si="19"/>
         <v>380</v>
       </c>
       <c r="AU40" s="204">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>80.8510638297872</v>
       </c>
       <c r="AV40" s="205">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>79.9255319148936</v>
       </c>
       <c r="AW40" s="206">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>84.9205124363201</v>
       </c>
       <c r="AX40" s="205">
-        <f t="shared" si="11"/>
+        <f t="shared" si="23"/>
         <v>87.9600932408539</v>
       </c>
       <c r="AY40" s="207">
@@ -13042,19 +13042,19 @@
         <v>100</v>
       </c>
       <c r="AC41" s="78">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>800</v>
       </c>
       <c r="AD41" s="160">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AE41" s="196">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>640</v>
       </c>
       <c r="AF41" s="197">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>89.4647887323944</v>
       </c>
       <c r="AG41" s="160">
@@ -13065,7 +13065,7 @@
       </c>
       <c r="AI41" s="160"/>
       <c r="AJ41" s="160">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>79</v>
       </c>
       <c r="AK41" s="160">
@@ -13079,11 +13079,11 @@
         <v>100</v>
       </c>
       <c r="AO41" s="161">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>400</v>
       </c>
       <c r="AP41" s="161">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="AQ41" s="126">
@@ -13093,23 +13093,23 @@
         <v>252</v>
       </c>
       <c r="AT41" s="128">
-        <f t="shared" si="7"/>
+        <f t="shared" si="19"/>
         <v>380</v>
       </c>
       <c r="AU41" s="204">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>80.8510638297872</v>
       </c>
       <c r="AV41" s="205">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>79.9255319148936</v>
       </c>
       <c r="AW41" s="206">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>84.695160323644</v>
       </c>
       <c r="AX41" s="205">
-        <f t="shared" si="11"/>
+        <f t="shared" si="23"/>
         <v>87.837403613389</v>
       </c>
       <c r="AY41" s="207">
@@ -13190,19 +13190,19 @@
         <v>95</v>
       </c>
       <c r="AC42" s="78">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>795</v>
       </c>
       <c r="AD42" s="160">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AE42" s="196">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>636</v>
       </c>
       <c r="AF42" s="197">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>89.4084507042253</v>
       </c>
       <c r="AG42" s="160">
@@ -13215,7 +13215,7 @@
         <v>2</v>
       </c>
       <c r="AJ42" s="160">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>82</v>
       </c>
       <c r="AK42" s="160">
@@ -13231,11 +13231,11 @@
         <v>100</v>
       </c>
       <c r="AO42" s="161">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>400</v>
       </c>
       <c r="AP42" s="161">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>11</v>
       </c>
       <c r="AQ42" s="126">
@@ -13245,23 +13245,23 @@
         <v>256</v>
       </c>
       <c r="AT42" s="128">
-        <f t="shared" si="7"/>
+        <f t="shared" si="19"/>
         <v>470</v>
       </c>
       <c r="AU42" s="204">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>100</v>
       </c>
       <c r="AV42" s="205">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>91</v>
       </c>
       <c r="AW42" s="206">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>90.2042253521127</v>
       </c>
       <c r="AX42" s="205">
-        <f t="shared" si="11"/>
+        <f t="shared" si="23"/>
         <v>90.8367326544888</v>
       </c>
       <c r="AY42" s="207">
@@ -13350,19 +13350,19 @@
         <v>95</v>
       </c>
       <c r="AC43" s="78">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>795</v>
       </c>
       <c r="AD43" s="160">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>200</v>
       </c>
       <c r="AE43" s="196">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>676</v>
       </c>
       <c r="AF43" s="197">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>89.9718309859155</v>
       </c>
       <c r="AG43" s="160">
@@ -13373,7 +13373,7 @@
       </c>
       <c r="AI43" s="160"/>
       <c r="AJ43" s="160">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>94</v>
       </c>
       <c r="AK43" s="160">
@@ -13383,11 +13383,11 @@
       <c r="AM43" s="161"/>
       <c r="AN43" s="161"/>
       <c r="AO43" s="161">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>200</v>
       </c>
       <c r="AP43" s="161">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="AQ43" s="126">
@@ -13397,23 +13397,23 @@
         <v>262</v>
       </c>
       <c r="AT43" s="128">
-        <f t="shared" si="7"/>
+        <f t="shared" si="19"/>
         <v>200</v>
       </c>
       <c r="AU43" s="204">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>42.5531914893617</v>
       </c>
       <c r="AV43" s="205">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>68.2765957446808</v>
       </c>
       <c r="AW43" s="206">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>79.1242133652982</v>
       </c>
       <c r="AX43" s="205">
-        <f t="shared" si="11"/>
+        <f t="shared" si="23"/>
         <v>84.8043838700665</v>
       </c>
       <c r="AY43" s="207">
@@ -13504,19 +13504,19 @@
         <v>80</v>
       </c>
       <c r="AC44" s="78">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>780</v>
       </c>
       <c r="AD44" s="160">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>300</v>
       </c>
       <c r="AE44" s="196">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>684</v>
       </c>
       <c r="AF44" s="197">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>90.0845070422535</v>
       </c>
       <c r="AG44" s="160">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="AI44" s="160"/>
       <c r="AJ44" s="160">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>88</v>
       </c>
       <c r="AK44" s="160">
@@ -13541,11 +13541,11 @@
         <v>100</v>
       </c>
       <c r="AO44" s="161">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>400</v>
       </c>
       <c r="AP44" s="161">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>3</v>
       </c>
       <c r="AQ44" s="126">
@@ -13555,23 +13555,23 @@
         <v>269</v>
       </c>
       <c r="AT44" s="128">
-        <f t="shared" si="7"/>
+        <f t="shared" si="19"/>
         <v>390</v>
       </c>
       <c r="AU44" s="204">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>82.9787234042553</v>
       </c>
       <c r="AV44" s="205">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>85.4893617021277</v>
       </c>
       <c r="AW44" s="206">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>87.7869343721906</v>
       </c>
       <c r="AX44" s="205">
-        <f t="shared" si="11"/>
+        <f t="shared" si="23"/>
         <v>89.5206743034978</v>
       </c>
       <c r="AY44" s="207">
@@ -13666,19 +13666,19 @@
         <v>100</v>
       </c>
       <c r="AC45" s="78">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>800</v>
       </c>
       <c r="AD45" s="160">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>600</v>
       </c>
       <c r="AE45" s="196">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>760</v>
       </c>
       <c r="AF45" s="197">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>91.1549295774648</v>
       </c>
       <c r="AG45" s="160">
@@ -13689,7 +13689,7 @@
       </c>
       <c r="AI45" s="160"/>
       <c r="AJ45" s="160">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>85</v>
       </c>
       <c r="AK45" s="160">
@@ -13703,11 +13703,11 @@
         <v>100</v>
       </c>
       <c r="AO45" s="161">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>400</v>
       </c>
       <c r="AP45" s="161">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>4</v>
       </c>
       <c r="AQ45" s="126">
@@ -13717,23 +13717,23 @@
         <v>275</v>
       </c>
       <c r="AT45" s="128">
-        <f t="shared" si="7"/>
+        <f t="shared" si="19"/>
         <v>400</v>
       </c>
       <c r="AU45" s="204">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>85.1063829787234</v>
       </c>
       <c r="AV45" s="205">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>85.0531914893617</v>
       </c>
       <c r="AW45" s="206">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>88.1040605334132</v>
       </c>
       <c r="AX45" s="205">
-        <f t="shared" si="11"/>
+        <f t="shared" si="23"/>
         <v>89.6933289554455</v>
       </c>
       <c r="AY45" s="207">
@@ -13822,19 +13822,19 @@
         <v>95</v>
       </c>
       <c r="AC46" s="78">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>795</v>
       </c>
       <c r="AD46" s="160">
-        <f t="shared" si="1"/>
+        <f t="shared" si="13"/>
         <v>300</v>
       </c>
       <c r="AE46" s="196">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>696</v>
       </c>
       <c r="AF46" s="197">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>90.2535211267606</v>
       </c>
       <c r="AG46" s="160">
@@ -13845,7 +13845,7 @@
       </c>
       <c r="AI46" s="160"/>
       <c r="AJ46" s="160">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>91</v>
       </c>
       <c r="AK46" s="160">
@@ -13859,11 +13859,11 @@
         <v>100</v>
       </c>
       <c r="AO46" s="161">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>400</v>
       </c>
       <c r="AP46" s="161">
-        <f t="shared" si="6"/>
+        <f t="shared" si="18"/>
         <v>5</v>
       </c>
       <c r="AQ46" s="126">
@@ -13873,23 +13873,23 @@
         <v>282</v>
       </c>
       <c r="AT46" s="128">
-        <f t="shared" si="7"/>
+        <f t="shared" si="19"/>
         <v>410</v>
       </c>
       <c r="AU46" s="204">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>87.2340425531915</v>
       </c>
       <c r="AV46" s="205">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v>89.1170212765958</v>
       </c>
       <c r="AW46" s="206">
-        <f t="shared" si="10"/>
+        <f t="shared" si="22"/>
         <v>89.6852712016781</v>
       </c>
       <c r="AX46" s="205">
-        <f t="shared" si="11"/>
+        <f t="shared" si="23"/>
         <v>90.5541957364539</v>
       </c>
       <c r="AY46" s="207">
@@ -14442,19 +14442,19 @@
       </c>
       <c r="AB62" s="194"/>
       <c r="AC62" s="200">
-        <f t="shared" ref="AC62:AC97" si="12">O62+P62+R62+S62+T62+AA62</f>
+        <f t="shared" ref="AC62:AC97" si="24">O62+P62+R62+S62+T62+AA62</f>
         <v>600</v>
       </c>
       <c r="AD62" s="180">
-        <f t="shared" ref="AD62:AD97" si="13">(Q62+U62+W62+Y62)*100</f>
+        <f t="shared" ref="AD62:AD97" si="25">(Q62+U62+W62+Y62)*100</f>
         <v>100</v>
       </c>
       <c r="AE62" s="196">
-        <f t="shared" ref="AE62:AE97" si="14">(0.8*AC62)+(0.2*AD62)</f>
+        <f t="shared" ref="AE62:AE97" si="26">(0.8*AC62)+(0.2*AD62)</f>
         <v>500</v>
       </c>
       <c r="AF62" s="201">
-        <f t="shared" ref="AF62:AF97" si="15">84+((AE62-$AE$99)/($AE$98-$AE$99)*(92-84))</f>
+        <f t="shared" ref="AF62:AF97" si="27">84+((AE62-$AE$99)/($AE$98-$AE$99)*(92-84))</f>
         <v>89.5238095238095</v>
       </c>
       <c r="AG62" s="160"/>
@@ -14465,7 +14465,7 @@
         <v>2</v>
       </c>
       <c r="AJ62" s="160">
-        <f t="shared" ref="AJ62:AJ97" si="16">AQ62</f>
+        <f t="shared" ref="AJ62:AJ97" si="28">AQ62</f>
         <v>94</v>
       </c>
       <c r="AK62" s="160"/>
@@ -14477,11 +14477,11 @@
         <v>100</v>
       </c>
       <c r="AO62" s="161">
-        <f t="shared" ref="AO62:AO97" si="17">AG62+AH62+AM62+AN62</f>
+        <f t="shared" ref="AO62:AO97" si="29">AG62+AH62+AM62+AN62</f>
         <v>300</v>
       </c>
       <c r="AP62" s="161">
-        <f t="shared" ref="AP62:AP97" si="18">AI62+AK62+AL62</f>
+        <f t="shared" ref="AP62:AP97" si="30">AI62+AK62+AL62</f>
         <v>2</v>
       </c>
       <c r="AQ62" s="126">
@@ -14491,23 +14491,23 @@
         <v>304</v>
       </c>
       <c r="AT62" s="128">
-        <f t="shared" ref="AT62:AT97" si="19">(90%*AO62)+(10%*AP62*100)</f>
+        <f t="shared" ref="AT62:AT97" si="31">(90%*AO62)+(10%*AP62*100)</f>
         <v>290</v>
       </c>
       <c r="AU62" s="204">
-        <f t="shared" ref="AU62:AU97" si="20">(AT62/$AT$99)*100</f>
+        <f t="shared" ref="AU62:AU97" si="32">(AT62/$AT$99)*100</f>
         <v>90.625</v>
       </c>
       <c r="AV62" s="205">
-        <f t="shared" ref="AV62:AV97" si="21">(50%*AU62)+(50%*AQ62)</f>
+        <f t="shared" ref="AV62:AV97" si="33">(50%*AU62)+(50%*AQ62)</f>
         <v>92.3125</v>
       </c>
       <c r="AW62" s="206">
-        <f t="shared" ref="AW62:AW97" si="22">(50%*AV62)+(50%*AF62)</f>
+        <f t="shared" ref="AW62:AW97" si="34">(50%*AV62)+(50%*AF62)</f>
         <v>90.9181547619048</v>
       </c>
       <c r="AX62" s="206">
-        <f t="shared" ref="AX62:AX97" si="23">84+((AW62-$AW$100)/($AW$99-$AW$100)*(92-84))</f>
+        <f t="shared" ref="AX62:AX97" si="35">84+((AW62-$AW$100)/($AW$99-$AW$100)*(92-84))</f>
         <v>89.1719782640623</v>
       </c>
       <c r="AY62" s="207">
@@ -14594,19 +14594,19 @@
       </c>
       <c r="AB63" s="194"/>
       <c r="AC63" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>600</v>
       </c>
       <c r="AD63" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="AE63" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>500</v>
       </c>
       <c r="AF63" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>89.5238095238095</v>
       </c>
       <c r="AG63" s="160"/>
@@ -14617,7 +14617,7 @@
         <v>1</v>
       </c>
       <c r="AJ63" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>79</v>
       </c>
       <c r="AK63" s="160">
@@ -14631,11 +14631,11 @@
         <v>100</v>
       </c>
       <c r="AO63" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP63" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>3</v>
       </c>
       <c r="AQ63" s="126">
@@ -14645,23 +14645,23 @@
         <v>310</v>
       </c>
       <c r="AT63" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>300</v>
       </c>
       <c r="AU63" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>93.75</v>
       </c>
       <c r="AV63" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>86.375</v>
       </c>
       <c r="AW63" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>87.9494047619048</v>
       </c>
       <c r="AX63" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>86.8280217359377</v>
       </c>
       <c r="AY63" s="207">
@@ -14746,19 +14746,19 @@
       </c>
       <c r="AB64" s="195"/>
       <c r="AC64" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>575</v>
       </c>
       <c r="AD64" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE64" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>460</v>
       </c>
       <c r="AF64" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>87.6190476190476</v>
       </c>
       <c r="AG64" s="160"/>
@@ -14767,7 +14767,7 @@
       </c>
       <c r="AI64" s="160"/>
       <c r="AJ64" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>91</v>
       </c>
       <c r="AK64" s="160">
@@ -14781,11 +14781,11 @@
         <v>100</v>
       </c>
       <c r="AO64" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP64" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>3</v>
       </c>
       <c r="AQ64" s="126">
@@ -14795,23 +14795,23 @@
         <v>316</v>
       </c>
       <c r="AT64" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>300</v>
       </c>
       <c r="AU64" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>93.75</v>
       </c>
       <c r="AV64" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>92.375</v>
       </c>
       <c r="AW64" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>89.9970238095238</v>
       </c>
       <c r="AX64" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>88.4447055367895</v>
       </c>
       <c r="AY64" s="207">
@@ -14898,19 +14898,19 @@
       </c>
       <c r="AB65" s="194"/>
       <c r="AC65" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>600</v>
       </c>
       <c r="AD65" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="AE65" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>500</v>
       </c>
       <c r="AF65" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>89.5238095238095</v>
       </c>
       <c r="AG65" s="160"/>
@@ -14921,7 +14921,7 @@
         <v>2</v>
       </c>
       <c r="AJ65" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>94</v>
       </c>
       <c r="AK65" s="160">
@@ -14935,11 +14935,11 @@
         <v>100</v>
       </c>
       <c r="AO65" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP65" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>5</v>
       </c>
       <c r="AQ65" s="126">
@@ -14949,23 +14949,23 @@
         <v>322</v>
       </c>
       <c r="AT65" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>320</v>
       </c>
       <c r="AU65" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>100</v>
       </c>
       <c r="AV65" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>97</v>
       </c>
       <c r="AW65" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>93.2619047619048</v>
       </c>
       <c r="AX65" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>91.0224702599501</v>
       </c>
       <c r="AY65" s="207">
@@ -15050,19 +15050,19 @@
       </c>
       <c r="AB66" s="194"/>
       <c r="AC66" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>580</v>
       </c>
       <c r="AD66" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE66" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>464</v>
       </c>
       <c r="AF66" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>87.8095238095238</v>
       </c>
       <c r="AG66" s="160"/>
@@ -15071,7 +15071,7 @@
       </c>
       <c r="AI66" s="160"/>
       <c r="AJ66" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>76</v>
       </c>
       <c r="AK66" s="160">
@@ -15085,11 +15085,11 @@
         <v>100</v>
       </c>
       <c r="AO66" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP66" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AQ66" s="126">
@@ -15099,23 +15099,23 @@
         <v>328</v>
       </c>
       <c r="AT66" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>280</v>
       </c>
       <c r="AU66" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>87.5</v>
       </c>
       <c r="AV66" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>81.75</v>
       </c>
       <c r="AW66" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>84.7797619047619</v>
       </c>
       <c r="AX66" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>84.3254516081657</v>
       </c>
       <c r="AY66" s="207">
@@ -15200,19 +15200,19 @@
       </c>
       <c r="AB67" s="194"/>
       <c r="AC67" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>595</v>
       </c>
       <c r="AD67" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE67" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>476</v>
       </c>
       <c r="AF67" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>88.3809523809524</v>
       </c>
       <c r="AG67" s="160"/>
@@ -15221,7 +15221,7 @@
       </c>
       <c r="AI67" s="160"/>
       <c r="AJ67" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>88</v>
       </c>
       <c r="AK67" s="160"/>
@@ -15233,11 +15233,11 @@
         <v>100</v>
       </c>
       <c r="AO67" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP67" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AQ67" s="126">
@@ -15247,23 +15247,23 @@
         <v>335</v>
       </c>
       <c r="AT67" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>270</v>
       </c>
       <c r="AU67" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>84.375</v>
       </c>
       <c r="AV67" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>86.1875</v>
       </c>
       <c r="AW67" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>87.2842261904762</v>
       </c>
       <c r="AX67" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>86.3028344837715</v>
       </c>
       <c r="AY67" s="207">
@@ -15348,19 +15348,19 @@
       </c>
       <c r="AB68" s="194"/>
       <c r="AC68" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>575</v>
       </c>
       <c r="AD68" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE68" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>460</v>
       </c>
       <c r="AF68" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>87.6190476190476</v>
       </c>
       <c r="AG68" s="160"/>
@@ -15369,7 +15369,7 @@
       </c>
       <c r="AI68" s="160"/>
       <c r="AJ68" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>82</v>
       </c>
       <c r="AK68" s="160"/>
@@ -15381,11 +15381,11 @@
         <v>100</v>
       </c>
       <c r="AO68" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP68" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AQ68" s="126">
@@ -15395,23 +15395,23 @@
         <v>341</v>
       </c>
       <c r="AT68" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>270</v>
       </c>
       <c r="AU68" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>84.375</v>
       </c>
       <c r="AV68" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>83.1875</v>
       </c>
       <c r="AW68" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>85.4032738095238</v>
       </c>
       <c r="AX68" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>84.8177412248495</v>
       </c>
       <c r="AY68" s="207">
@@ -15498,19 +15498,19 @@
       </c>
       <c r="AB69" s="194"/>
       <c r="AC69" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>575</v>
       </c>
       <c r="AD69" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="AE69" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>480</v>
       </c>
       <c r="AF69" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>88.5714285714286</v>
       </c>
       <c r="AG69" s="160"/>
@@ -15519,7 +15519,7 @@
       </c>
       <c r="AI69" s="160"/>
       <c r="AJ69" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>88</v>
       </c>
       <c r="AK69" s="160">
@@ -15533,11 +15533,11 @@
         <v>100</v>
       </c>
       <c r="AO69" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP69" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>3</v>
       </c>
       <c r="AQ69" s="126">
@@ -15547,23 +15547,23 @@
         <v>347</v>
       </c>
       <c r="AT69" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>300</v>
       </c>
       <c r="AU69" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>93.75</v>
       </c>
       <c r="AV69" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>90.875</v>
       </c>
       <c r="AW69" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>89.7232142857143</v>
       </c>
       <c r="AX69" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>88.2285210750477</v>
       </c>
       <c r="AY69" s="207">
@@ -15652,19 +15652,19 @@
       </c>
       <c r="AB70" s="194"/>
       <c r="AC70" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>500</v>
       </c>
       <c r="AD70" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>300</v>
       </c>
       <c r="AE70" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>460</v>
       </c>
       <c r="AF70" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>87.6190476190476</v>
       </c>
       <c r="AG70" s="160"/>
@@ -15675,7 +15675,7 @@
         <v>2</v>
       </c>
       <c r="AJ70" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>91</v>
       </c>
       <c r="AK70" s="160">
@@ -15689,11 +15689,11 @@
         <v>100</v>
       </c>
       <c r="AO70" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP70" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>3</v>
       </c>
       <c r="AQ70" s="126">
@@ -15703,23 +15703,23 @@
         <v>354</v>
       </c>
       <c r="AT70" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>300</v>
       </c>
       <c r="AU70" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>93.75</v>
       </c>
       <c r="AV70" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>92.375</v>
       </c>
       <c r="AW70" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>89.9970238095238</v>
       </c>
       <c r="AX70" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>88.4447055367895</v>
       </c>
       <c r="AY70" s="207">
@@ -15804,19 +15804,19 @@
       </c>
       <c r="AB71" s="194"/>
       <c r="AC71" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>560</v>
       </c>
       <c r="AD71" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE71" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>448</v>
       </c>
       <c r="AF71" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>87.0476190476191</v>
       </c>
       <c r="AG71" s="160"/>
@@ -15825,7 +15825,7 @@
       </c>
       <c r="AI71" s="160"/>
       <c r="AJ71" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>79</v>
       </c>
       <c r="AK71" s="160"/>
@@ -15837,11 +15837,11 @@
         <v>100</v>
       </c>
       <c r="AO71" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP71" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AQ71" s="126">
@@ -15851,23 +15851,23 @@
         <v>360</v>
       </c>
       <c r="AT71" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>270</v>
       </c>
       <c r="AU71" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>84.375</v>
       </c>
       <c r="AV71" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>81.6875</v>
       </c>
       <c r="AW71" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>84.3675595238095</v>
       </c>
       <c r="AX71" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>84</v>
       </c>
       <c r="AY71" s="207">
@@ -15952,19 +15952,19 @@
       </c>
       <c r="AB72" s="194"/>
       <c r="AC72" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>595</v>
       </c>
       <c r="AD72" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE72" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>476</v>
       </c>
       <c r="AF72" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>88.3809523809524</v>
       </c>
       <c r="AG72" s="160"/>
@@ -15973,7 +15973,7 @@
       </c>
       <c r="AI72" s="160"/>
       <c r="AJ72" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>91</v>
       </c>
       <c r="AK72" s="160"/>
@@ -15985,11 +15985,11 @@
         <v>100</v>
       </c>
       <c r="AO72" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP72" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AQ72" s="126">
@@ -15999,23 +15999,23 @@
         <v>366</v>
       </c>
       <c r="AT72" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>270</v>
       </c>
       <c r="AU72" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>84.375</v>
       </c>
       <c r="AV72" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>87.6875</v>
       </c>
       <c r="AW72" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>88.0342261904762</v>
       </c>
       <c r="AX72" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>86.8949919224556</v>
       </c>
       <c r="AY72" s="207">
@@ -16100,19 +16100,19 @@
       </c>
       <c r="AB73" s="194"/>
       <c r="AC73" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>600</v>
       </c>
       <c r="AD73" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE73" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>480</v>
       </c>
       <c r="AF73" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>88.5714285714286</v>
       </c>
       <c r="AG73" s="160"/>
@@ -16123,7 +16123,7 @@
         <v>2</v>
       </c>
       <c r="AJ73" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>91</v>
       </c>
       <c r="AK73" s="160"/>
@@ -16135,11 +16135,11 @@
         <v>100</v>
       </c>
       <c r="AO73" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP73" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>2</v>
       </c>
       <c r="AQ73" s="126">
@@ -16149,23 +16149,23 @@
         <v>373</v>
       </c>
       <c r="AT73" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>290</v>
       </c>
       <c r="AU73" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>90.625</v>
       </c>
       <c r="AV73" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>90.8125</v>
       </c>
       <c r="AW73" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>89.6919642857143</v>
       </c>
       <c r="AX73" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>88.2038478484359</v>
       </c>
       <c r="AY73" s="207">
@@ -16248,19 +16248,19 @@
       </c>
       <c r="AB74" s="194"/>
       <c r="AC74" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>490</v>
       </c>
       <c r="AD74" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE74" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>392</v>
       </c>
       <c r="AF74" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>84.3809523809524</v>
       </c>
       <c r="AG74" s="160"/>
@@ -16269,7 +16269,7 @@
       </c>
       <c r="AI74" s="160"/>
       <c r="AJ74" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>94</v>
       </c>
       <c r="AK74" s="160"/>
@@ -16281,11 +16281,11 @@
         <v>100</v>
       </c>
       <c r="AO74" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP74" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AQ74" s="126">
@@ -16295,23 +16295,23 @@
         <v>379</v>
       </c>
       <c r="AT74" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>270</v>
       </c>
       <c r="AU74" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>84.375</v>
       </c>
       <c r="AV74" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>89.1875</v>
       </c>
       <c r="AW74" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>86.7842261904762</v>
       </c>
       <c r="AX74" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>85.9080628579821</v>
       </c>
       <c r="AY74" s="207">
@@ -16402,19 +16402,19 @@
       </c>
       <c r="AB75" s="194"/>
       <c r="AC75" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>590</v>
       </c>
       <c r="AD75" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>400</v>
       </c>
       <c r="AE75" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>552</v>
       </c>
       <c r="AF75" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>92</v>
       </c>
       <c r="AG75" s="160"/>
@@ -16425,7 +16425,7 @@
         <v>2</v>
       </c>
       <c r="AJ75" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>94</v>
       </c>
       <c r="AK75" s="160">
@@ -16439,11 +16439,11 @@
         <v>100</v>
       </c>
       <c r="AO75" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP75" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>5</v>
       </c>
       <c r="AQ75" s="126">
@@ -16453,23 +16453,23 @@
         <v>385</v>
       </c>
       <c r="AT75" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>320</v>
       </c>
       <c r="AU75" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>100</v>
       </c>
       <c r="AV75" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>97</v>
       </c>
       <c r="AW75" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>94.5</v>
       </c>
       <c r="AX75" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>92</v>
       </c>
       <c r="AY75" s="207">
@@ -16554,19 +16554,19 @@
       </c>
       <c r="AB76" s="194"/>
       <c r="AC76" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>585</v>
       </c>
       <c r="AD76" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE76" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>468</v>
       </c>
       <c r="AF76" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>88</v>
       </c>
       <c r="AG76" s="160"/>
@@ -16575,7 +16575,7 @@
       </c>
       <c r="AI76" s="160"/>
       <c r="AJ76" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>91</v>
       </c>
       <c r="AK76" s="160">
@@ -16589,11 +16589,11 @@
         <v>100</v>
       </c>
       <c r="AO76" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP76" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>2</v>
       </c>
       <c r="AQ76" s="126">
@@ -16603,23 +16603,23 @@
         <v>391</v>
       </c>
       <c r="AT76" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>290</v>
       </c>
       <c r="AU76" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>90.625</v>
       </c>
       <c r="AV76" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>90.8125</v>
       </c>
       <c r="AW76" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>89.40625</v>
       </c>
       <c r="AX76" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>87.9782640622705</v>
       </c>
       <c r="AY76" s="207">
@@ -16704,19 +16704,19 @@
       </c>
       <c r="AB77" s="194"/>
       <c r="AC77" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>595</v>
       </c>
       <c r="AD77" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE77" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>476</v>
       </c>
       <c r="AF77" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>88.3809523809524</v>
       </c>
       <c r="AG77" s="160"/>
@@ -16727,7 +16727,7 @@
         <v>3</v>
       </c>
       <c r="AJ77" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>94</v>
       </c>
       <c r="AK77" s="160">
@@ -16741,11 +16741,11 @@
         <v>100</v>
       </c>
       <c r="AO77" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP77" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>5</v>
       </c>
       <c r="AQ77" s="126">
@@ -16755,23 +16755,23 @@
         <v>398</v>
       </c>
       <c r="AT77" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>320</v>
       </c>
       <c r="AU77" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>100</v>
       </c>
       <c r="AV77" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>97</v>
       </c>
       <c r="AW77" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>92.6904761904762</v>
       </c>
       <c r="AX77" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>90.5713026876193</v>
       </c>
       <c r="AY77" s="207">
@@ -16858,19 +16858,19 @@
       </c>
       <c r="AB78" s="195"/>
       <c r="AC78" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>595</v>
       </c>
       <c r="AD78" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>200</v>
       </c>
       <c r="AE78" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>516</v>
       </c>
       <c r="AF78" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>90.2857142857143</v>
       </c>
       <c r="AG78" s="160"/>
@@ -16879,7 +16879,7 @@
       </c>
       <c r="AI78" s="160"/>
       <c r="AJ78" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>88</v>
       </c>
       <c r="AK78" s="160">
@@ -16893,11 +16893,11 @@
         <v>100</v>
       </c>
       <c r="AO78" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP78" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AQ78" s="126">
@@ -16907,23 +16907,23 @@
         <v>404</v>
       </c>
       <c r="AT78" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>280</v>
       </c>
       <c r="AU78" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>87.5</v>
       </c>
       <c r="AV78" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>87.75</v>
       </c>
       <c r="AW78" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>89.0178571428571</v>
       </c>
       <c r="AX78" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>87.671611102952</v>
       </c>
       <c r="AY78" s="207">
@@ -17008,19 +17008,19 @@
       </c>
       <c r="AB79" s="194"/>
       <c r="AC79" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>580</v>
       </c>
       <c r="AD79" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE79" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>464</v>
       </c>
       <c r="AF79" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>87.8095238095238</v>
       </c>
       <c r="AG79" s="160"/>
@@ -17029,7 +17029,7 @@
       </c>
       <c r="AI79" s="160"/>
       <c r="AJ79" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>82</v>
       </c>
       <c r="AK79" s="160"/>
@@ -17041,11 +17041,11 @@
         <v>100</v>
       </c>
       <c r="AO79" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP79" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AQ79" s="126">
@@ -17055,23 +17055,23 @@
         <v>411</v>
       </c>
       <c r="AT79" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>270</v>
       </c>
       <c r="AU79" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>84.375</v>
       </c>
       <c r="AV79" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>83.1875</v>
       </c>
       <c r="AW79" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>85.4985119047619</v>
       </c>
       <c r="AX79" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>84.8929358202379</v>
       </c>
       <c r="AY79" s="207">
@@ -17156,19 +17156,19 @@
       </c>
       <c r="AB80" s="194"/>
       <c r="AC80" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>575</v>
       </c>
       <c r="AD80" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE80" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>460</v>
       </c>
       <c r="AF80" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>87.6190476190476</v>
       </c>
       <c r="AG80" s="160"/>
@@ -17177,7 +17177,7 @@
       </c>
       <c r="AI80" s="160"/>
       <c r="AJ80" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>91</v>
       </c>
       <c r="AK80" s="160">
@@ -17191,11 +17191,11 @@
         <v>100</v>
       </c>
       <c r="AO80" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP80" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AQ80" s="126">
@@ -17205,23 +17205,23 @@
         <v>417</v>
       </c>
       <c r="AT80" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>280</v>
       </c>
       <c r="AU80" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>87.5</v>
       </c>
       <c r="AV80" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>89.25</v>
       </c>
       <c r="AW80" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>88.4345238095238</v>
       </c>
       <c r="AX80" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>87.2110442061977</v>
       </c>
       <c r="AY80" s="207">
@@ -17306,19 +17306,19 @@
       </c>
       <c r="AB81" s="194"/>
       <c r="AC81" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>575</v>
       </c>
       <c r="AD81" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE81" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>460</v>
       </c>
       <c r="AF81" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>87.6190476190476</v>
       </c>
       <c r="AG81" s="160"/>
@@ -17329,7 +17329,7 @@
         <v>1</v>
       </c>
       <c r="AJ81" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>94</v>
       </c>
       <c r="AK81" s="160">
@@ -17343,11 +17343,11 @@
         <v>100</v>
       </c>
       <c r="AO81" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP81" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>2</v>
       </c>
       <c r="AQ81" s="126">
@@ -17357,23 +17357,23 @@
         <v>423</v>
       </c>
       <c r="AT81" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>290</v>
       </c>
       <c r="AU81" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>90.625</v>
       </c>
       <c r="AV81" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>92.3125</v>
       </c>
       <c r="AW81" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>89.9657738095238</v>
       </c>
       <c r="AX81" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>88.4200323101777</v>
       </c>
       <c r="AY81" s="207">
@@ -17458,19 +17458,19 @@
       </c>
       <c r="AB82" s="194"/>
       <c r="AC82" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>600</v>
       </c>
       <c r="AD82" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE82" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>480</v>
       </c>
       <c r="AF82" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>88.5714285714286</v>
       </c>
       <c r="AG82" s="160"/>
@@ -17481,7 +17481,7 @@
         <v>1</v>
       </c>
       <c r="AJ82" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>88</v>
       </c>
       <c r="AK82" s="160"/>
@@ -17493,11 +17493,11 @@
         <v>100</v>
       </c>
       <c r="AO82" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP82" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AQ82" s="126">
@@ -17507,23 +17507,23 @@
         <v>430</v>
       </c>
       <c r="AT82" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>280</v>
       </c>
       <c r="AU82" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>87.5</v>
       </c>
       <c r="AV82" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>87.75</v>
       </c>
       <c r="AW82" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>88.1607142857143</v>
       </c>
       <c r="AX82" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>86.9948597444559</v>
       </c>
       <c r="AY82" s="207">
@@ -17608,19 +17608,19 @@
       </c>
       <c r="AB83" s="194"/>
       <c r="AC83" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>560</v>
       </c>
       <c r="AD83" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE83" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>448</v>
       </c>
       <c r="AF83" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>87.0476190476191</v>
       </c>
       <c r="AG83" s="160"/>
@@ -17629,7 +17629,7 @@
       </c>
       <c r="AI83" s="160"/>
       <c r="AJ83" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>94</v>
       </c>
       <c r="AK83" s="160"/>
@@ -17641,11 +17641,11 @@
         <v>100</v>
       </c>
       <c r="AO83" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP83" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AQ83" s="126">
@@ -17655,23 +17655,23 @@
         <v>437</v>
       </c>
       <c r="AT83" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>270</v>
       </c>
       <c r="AU83" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>84.375</v>
       </c>
       <c r="AV83" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>89.1875</v>
       </c>
       <c r="AW83" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>88.1175595238095</v>
       </c>
       <c r="AX83" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>86.9607871934205</v>
       </c>
       <c r="AY83" s="207">
@@ -17756,19 +17756,19 @@
       </c>
       <c r="AB84" s="194"/>
       <c r="AC84" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>560</v>
       </c>
       <c r="AD84" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE84" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>448</v>
       </c>
       <c r="AF84" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>87.0476190476191</v>
       </c>
       <c r="AG84" s="160"/>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="AI84" s="160"/>
       <c r="AJ84" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>91</v>
       </c>
       <c r="AK84" s="160"/>
@@ -17789,11 +17789,11 @@
         <v>100</v>
       </c>
       <c r="AO84" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP84" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AQ84" s="126">
@@ -17803,23 +17803,23 @@
         <v>444</v>
       </c>
       <c r="AT84" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>270</v>
       </c>
       <c r="AU84" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>84.375</v>
       </c>
       <c r="AV84" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>87.6875</v>
       </c>
       <c r="AW84" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>87.3675595238095</v>
       </c>
       <c r="AX84" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>86.3686297547364</v>
       </c>
       <c r="AY84" s="207">
@@ -17904,19 +17904,19 @@
       </c>
       <c r="AB85" s="194"/>
       <c r="AC85" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>580</v>
       </c>
       <c r="AD85" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE85" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>464</v>
       </c>
       <c r="AF85" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>87.8095238095238</v>
       </c>
       <c r="AG85" s="160"/>
@@ -17925,7 +17925,7 @@
       </c>
       <c r="AI85" s="160"/>
       <c r="AJ85" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>94</v>
       </c>
       <c r="AK85" s="160"/>
@@ -17937,11 +17937,11 @@
         <v>100</v>
       </c>
       <c r="AO85" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP85" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AQ85" s="126">
@@ -17951,23 +17951,23 @@
         <v>450</v>
       </c>
       <c r="AT85" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>270</v>
       </c>
       <c r="AU85" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>84.375</v>
       </c>
       <c r="AV85" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>89.1875</v>
       </c>
       <c r="AW85" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>88.4985119047619</v>
       </c>
       <c r="AX85" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>87.2615655749743</v>
       </c>
       <c r="AY85" s="207">
@@ -18052,19 +18052,19 @@
       </c>
       <c r="AB86" s="194"/>
       <c r="AC86" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>575</v>
       </c>
       <c r="AD86" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE86" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>460</v>
       </c>
       <c r="AF86" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>87.6190476190476</v>
       </c>
       <c r="AG86" s="160"/>
@@ -18075,7 +18075,7 @@
         <v>1</v>
       </c>
       <c r="AJ86" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>94</v>
       </c>
       <c r="AK86" s="160"/>
@@ -18087,11 +18087,11 @@
         <v>100</v>
       </c>
       <c r="AO86" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP86" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AQ86" s="126">
@@ -18101,23 +18101,23 @@
         <v>456</v>
       </c>
       <c r="AT86" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>280</v>
       </c>
       <c r="AU86" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>87.5</v>
       </c>
       <c r="AV86" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>90.75</v>
       </c>
       <c r="AW86" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>89.1845238095238</v>
       </c>
       <c r="AX86" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>87.8032016448818</v>
       </c>
       <c r="AY86" s="207">
@@ -18204,19 +18204,19 @@
       </c>
       <c r="AB87" s="194"/>
       <c r="AC87" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>600</v>
       </c>
       <c r="AD87" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="AE87" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>500</v>
       </c>
       <c r="AF87" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>89.5238095238095</v>
       </c>
       <c r="AG87" s="160"/>
@@ -18227,7 +18227,7 @@
         <v>1</v>
       </c>
       <c r="AJ87" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>88</v>
       </c>
       <c r="AK87" s="160">
@@ -18241,11 +18241,11 @@
         <v>100</v>
       </c>
       <c r="AO87" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP87" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>3</v>
       </c>
       <c r="AQ87" s="126">
@@ -18255,23 +18255,23 @@
         <v>462</v>
       </c>
       <c r="AT87" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>300</v>
       </c>
       <c r="AU87" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>93.75</v>
       </c>
       <c r="AV87" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>90.875</v>
       </c>
       <c r="AW87" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>90.1994047619048</v>
       </c>
       <c r="AX87" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>88.60449405199</v>
       </c>
       <c r="AY87" s="207">
@@ -18356,19 +18356,19 @@
       </c>
       <c r="AB88" s="194"/>
       <c r="AC88" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>590</v>
       </c>
       <c r="AD88" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE88" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>472</v>
       </c>
       <c r="AF88" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>88.1904761904762</v>
       </c>
       <c r="AG88" s="160"/>
@@ -18377,7 +18377,7 @@
       </c>
       <c r="AI88" s="160"/>
       <c r="AJ88" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>88</v>
       </c>
       <c r="AK88" s="160"/>
@@ -18389,11 +18389,11 @@
         <v>100</v>
       </c>
       <c r="AO88" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP88" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AQ88" s="126">
@@ -18403,23 +18403,23 @@
         <v>467</v>
       </c>
       <c r="AT88" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>270</v>
       </c>
       <c r="AU88" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>84.375</v>
       </c>
       <c r="AV88" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>86.1875</v>
       </c>
       <c r="AW88" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>87.1889880952381</v>
       </c>
       <c r="AX88" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>86.227639888383</v>
       </c>
       <c r="AY88" s="207">
@@ -18504,19 +18504,19 @@
       </c>
       <c r="AB89" s="194"/>
       <c r="AC89" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>600</v>
       </c>
       <c r="AD89" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE89" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>480</v>
       </c>
       <c r="AF89" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>88.5714285714286</v>
       </c>
       <c r="AG89" s="160"/>
@@ -18525,7 +18525,7 @@
       </c>
       <c r="AI89" s="160"/>
       <c r="AJ89" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>88</v>
       </c>
       <c r="AK89" s="160">
@@ -18539,11 +18539,11 @@
         <v>100</v>
       </c>
       <c r="AO89" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP89" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>2</v>
       </c>
       <c r="AQ89" s="126">
@@ -18553,23 +18553,23 @@
         <v>473</v>
       </c>
       <c r="AT89" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>290</v>
       </c>
       <c r="AU89" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>90.625</v>
       </c>
       <c r="AV89" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>89.3125</v>
       </c>
       <c r="AW89" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>88.9419642857143</v>
       </c>
       <c r="AX89" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>87.6116904097518</v>
       </c>
       <c r="AY89" s="207">
@@ -18654,19 +18654,19 @@
       </c>
       <c r="AB90" s="194"/>
       <c r="AC90" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>600</v>
       </c>
       <c r="AD90" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE90" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>480</v>
       </c>
       <c r="AF90" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>88.5714285714286</v>
       </c>
       <c r="AG90" s="160"/>
@@ -18675,7 +18675,7 @@
       </c>
       <c r="AI90" s="160"/>
       <c r="AJ90" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>94</v>
       </c>
       <c r="AK90" s="160"/>
@@ -18687,11 +18687,11 @@
         <v>100</v>
       </c>
       <c r="AO90" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP90" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AQ90" s="126">
@@ -18701,23 +18701,23 @@
         <v>479</v>
       </c>
       <c r="AT90" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>270</v>
       </c>
       <c r="AU90" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>84.375</v>
       </c>
       <c r="AV90" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>89.1875</v>
       </c>
       <c r="AW90" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>88.8794642857143</v>
       </c>
       <c r="AX90" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>87.5623439565281</v>
       </c>
       <c r="AY90" s="207">
@@ -18792,19 +18792,19 @@
       </c>
       <c r="AB91" s="194"/>
       <c r="AC91" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>595</v>
       </c>
       <c r="AD91" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE91" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>476</v>
       </c>
       <c r="AF91" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>88.3809523809524</v>
       </c>
       <c r="AG91" s="160"/>
@@ -18813,7 +18813,7 @@
       </c>
       <c r="AI91" s="160"/>
       <c r="AJ91" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>94</v>
       </c>
       <c r="AK91" s="160"/>
@@ -18825,11 +18825,11 @@
         <v>100</v>
       </c>
       <c r="AO91" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP91" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AQ91" s="126">
@@ -18839,23 +18839,23 @@
         <v>485</v>
       </c>
       <c r="AT91" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>270</v>
       </c>
       <c r="AU91" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>84.375</v>
       </c>
       <c r="AV91" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>89.1875</v>
       </c>
       <c r="AW91" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>88.7842261904762</v>
       </c>
       <c r="AX91" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>87.4871493611397</v>
       </c>
       <c r="AY91" s="207">
@@ -18944,19 +18944,19 @@
       </c>
       <c r="AB92" s="194"/>
       <c r="AC92" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>580</v>
       </c>
       <c r="AD92" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>200</v>
       </c>
       <c r="AE92" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>504</v>
       </c>
       <c r="AF92" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>89.7142857142857</v>
       </c>
       <c r="AG92" s="160"/>
@@ -18967,7 +18967,7 @@
         <v>1</v>
       </c>
       <c r="AJ92" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>88</v>
       </c>
       <c r="AK92" s="160">
@@ -18981,11 +18981,11 @@
         <v>100</v>
       </c>
       <c r="AO92" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP92" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>2</v>
       </c>
       <c r="AQ92" s="126">
@@ -18995,23 +18995,23 @@
         <v>491</v>
       </c>
       <c r="AT92" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>290</v>
       </c>
       <c r="AU92" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>90.625</v>
       </c>
       <c r="AV92" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>89.3125</v>
       </c>
       <c r="AW92" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>89.5133928571429</v>
       </c>
       <c r="AX92" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>88.0628579820825</v>
       </c>
       <c r="AY92" s="207">
@@ -19096,19 +19096,19 @@
       </c>
       <c r="AB93" s="194"/>
       <c r="AC93" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>585</v>
       </c>
       <c r="AD93" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE93" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>468</v>
       </c>
       <c r="AF93" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>88</v>
       </c>
       <c r="AG93" s="160"/>
@@ -19117,7 +19117,7 @@
       </c>
       <c r="AI93" s="160"/>
       <c r="AJ93" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>91</v>
       </c>
       <c r="AK93" s="160">
@@ -19131,11 +19131,11 @@
         <v>100</v>
       </c>
       <c r="AO93" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP93" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>2</v>
       </c>
       <c r="AQ93" s="126">
@@ -19145,23 +19145,23 @@
         <v>497</v>
       </c>
       <c r="AT93" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>290</v>
       </c>
       <c r="AU93" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>90.625</v>
       </c>
       <c r="AV93" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>90.8125</v>
       </c>
       <c r="AW93" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>89.40625</v>
       </c>
       <c r="AX93" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>87.9782640622705</v>
       </c>
       <c r="AY93" s="207">
@@ -19244,19 +19244,19 @@
       </c>
       <c r="AB94" s="194"/>
       <c r="AC94" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>480</v>
       </c>
       <c r="AD94" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE94" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>384</v>
       </c>
       <c r="AF94" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>84</v>
       </c>
       <c r="AG94" s="160"/>
@@ -19265,7 +19265,7 @@
       </c>
       <c r="AI94" s="160"/>
       <c r="AJ94" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>83</v>
       </c>
       <c r="AK94" s="160">
@@ -19279,11 +19279,11 @@
         <v>100</v>
       </c>
       <c r="AO94" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP94" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AQ94" s="126">
@@ -19293,23 +19293,23 @@
         <v>503</v>
       </c>
       <c r="AT94" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>280</v>
       </c>
       <c r="AU94" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>87.5</v>
       </c>
       <c r="AV94" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>85.25</v>
       </c>
       <c r="AW94" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>84.625</v>
       </c>
       <c r="AX94" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>84.2032603906594</v>
       </c>
       <c r="AY94" s="207">
@@ -19394,19 +19394,19 @@
       </c>
       <c r="AB95" s="194"/>
       <c r="AC95" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>600</v>
       </c>
       <c r="AD95" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE95" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>480</v>
       </c>
       <c r="AF95" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>88.5714285714286</v>
       </c>
       <c r="AG95" s="160"/>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="AI95" s="160"/>
       <c r="AJ95" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>82</v>
       </c>
       <c r="AK95" s="160">
@@ -19429,11 +19429,11 @@
         <v>100</v>
       </c>
       <c r="AO95" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP95" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AQ95" s="126">
@@ -19443,23 +19443,23 @@
         <v>508</v>
       </c>
       <c r="AT95" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>280</v>
       </c>
       <c r="AU95" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>87.5</v>
       </c>
       <c r="AV95" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>84.75</v>
       </c>
       <c r="AW95" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>86.6607142857143</v>
       </c>
       <c r="AX95" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>85.8105448670877</v>
       </c>
       <c r="AY95" s="207">
@@ -19544,19 +19544,19 @@
       </c>
       <c r="AB96" s="194"/>
       <c r="AC96" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>575</v>
       </c>
       <c r="AD96" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE96" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>460</v>
       </c>
       <c r="AF96" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>87.6190476190476</v>
       </c>
       <c r="AG96" s="160"/>
@@ -19565,7 +19565,7 @@
       </c>
       <c r="AI96" s="160"/>
       <c r="AJ96" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>94</v>
       </c>
       <c r="AK96" s="160">
@@ -19579,11 +19579,11 @@
         <v>100</v>
       </c>
       <c r="AO96" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP96" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AQ96" s="126">
@@ -19593,23 +19593,23 @@
         <v>517</v>
       </c>
       <c r="AT96" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>280</v>
       </c>
       <c r="AU96" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>87.5</v>
       </c>
       <c r="AV96" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>90.75</v>
       </c>
       <c r="AW96" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>89.1845238095238</v>
       </c>
       <c r="AX96" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>87.8032016448818</v>
       </c>
       <c r="AY96" s="207">
@@ -19696,19 +19696,19 @@
       </c>
       <c r="AB97" s="194"/>
       <c r="AC97" s="200">
-        <f t="shared" si="12"/>
+        <f t="shared" si="24"/>
         <v>600</v>
       </c>
       <c r="AD97" s="180">
-        <f t="shared" si="13"/>
+        <f t="shared" si="25"/>
         <v>100</v>
       </c>
       <c r="AE97" s="196">
-        <f t="shared" si="14"/>
+        <f t="shared" si="26"/>
         <v>500</v>
       </c>
       <c r="AF97" s="201">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>89.5238095238095</v>
       </c>
       <c r="AG97" s="160"/>
@@ -19719,7 +19719,7 @@
         <v>2</v>
       </c>
       <c r="AJ97" s="160">
-        <f t="shared" si="16"/>
+        <f t="shared" si="28"/>
         <v>94</v>
       </c>
       <c r="AK97" s="160"/>
@@ -19731,11 +19731,11 @@
         <v>100</v>
       </c>
       <c r="AO97" s="161">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>300</v>
       </c>
       <c r="AP97" s="161">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>2</v>
       </c>
       <c r="AQ97" s="126">
@@ -19745,23 +19745,23 @@
         <v>524</v>
       </c>
       <c r="AT97" s="128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="31"/>
         <v>290</v>
       </c>
       <c r="AU97" s="204">
-        <f t="shared" si="20"/>
+        <f t="shared" si="32"/>
         <v>90.625</v>
       </c>
       <c r="AV97" s="205">
-        <f t="shared" si="21"/>
+        <f t="shared" si="33"/>
         <v>92.3125</v>
       </c>
       <c r="AW97" s="206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="34"/>
         <v>90.9181547619048</v>
       </c>
       <c r="AX97" s="206">
-        <f t="shared" si="23"/>
+        <f t="shared" si="35"/>
         <v>89.1719782640623</v>
       </c>
       <c r="AY97" s="207">
@@ -20443,19 +20443,19 @@
         <v>90</v>
       </c>
       <c r="AC121" s="78">
-        <f t="shared" ref="AC121:AC159" si="24">O121+P121+R121+S121+AB121</f>
+        <f t="shared" ref="AC121:AC159" si="36">O121+P121+R121+S121+AB121</f>
         <v>490</v>
       </c>
       <c r="AD121" s="160">
-        <f t="shared" ref="AD121:AD159" si="25">(Q121+T121+Y121+AA121)*100</f>
+        <f t="shared" ref="AD121:AD159" si="37">(Q121+T121+Y121+AA121)*100</f>
         <v>0</v>
       </c>
       <c r="AE121" s="196">
-        <f t="shared" ref="AE121:AE159" si="26">(0.8*AC121)+(0.2*AD121)</f>
+        <f t="shared" ref="AE121:AE159" si="38">(0.8*AC121)+(0.2*AD121)</f>
         <v>392</v>
       </c>
       <c r="AF121" s="201">
-        <f t="shared" ref="AF121:AF161" si="27">84+((AE121-$AE$161)/($AE$160-$AE$161)*(92-84))</f>
+        <f t="shared" ref="AF121:AF161" si="39">84+((AE121-$AE$161)/($AE$160-$AE$161)*(92-84))</f>
         <v>86.88</v>
       </c>
       <c r="AG121" s="160"/>
@@ -20464,7 +20464,7 @@
       </c>
       <c r="AI121" s="160"/>
       <c r="AJ121" s="160">
-        <f t="shared" ref="AJ121:AJ159" si="28">AQ121</f>
+        <f t="shared" ref="AJ121:AJ159" si="40">AQ121</f>
         <v>94</v>
       </c>
       <c r="AK121" s="160"/>
@@ -20472,11 +20472,11 @@
       <c r="AM121" s="161"/>
       <c r="AN121" s="161"/>
       <c r="AO121" s="161">
-        <f t="shared" ref="AO121:AO159" si="29">AG121+AH121+AM121+AN121</f>
+        <f t="shared" ref="AO121:AO159" si="41">AG121+AH121+AM121+AN121</f>
         <v>100</v>
       </c>
       <c r="AP121" s="160">
-        <f t="shared" ref="AP121:AP159" si="30">AI121+AK121+AL121</f>
+        <f t="shared" ref="AP121:AP159" si="42">AI121+AK121+AL121</f>
         <v>0</v>
       </c>
       <c r="AQ121" s="126">
@@ -20486,23 +20486,23 @@
         <v>551</v>
       </c>
       <c r="AT121" s="128">
-        <f t="shared" ref="AT121:AT159" si="31">(90%*AO121)+(10%*AP121*100)</f>
+        <f t="shared" ref="AT121:AT159" si="43">(90%*AO121)+(10%*AP121*100)</f>
         <v>90</v>
       </c>
       <c r="AU121" s="204">
-        <f t="shared" ref="AU121:AU159" si="32">(AT121/$AT$161)*100</f>
+        <f t="shared" ref="AU121:AU159" si="44">(AT121/$AT$161)*100</f>
         <v>56.25</v>
       </c>
       <c r="AV121" s="205">
-        <f t="shared" ref="AV121:AV159" si="33">(50%*AU121)+(50%*AQ121)</f>
+        <f t="shared" ref="AV121:AV159" si="45">(50%*AU121)+(50%*AQ121)</f>
         <v>75.125</v>
       </c>
       <c r="AW121" s="206">
-        <f t="shared" ref="AW121:AW159" si="34">(50%*AV121)+(50%*AF121)</f>
+        <f t="shared" ref="AW121:AW159" si="46">(50%*AV121)+(50%*AF121)</f>
         <v>81.0025</v>
       </c>
       <c r="AX121" s="206">
-        <f t="shared" ref="AX121:AX159" si="35">84+((AW121-$AW$162)/($AW$161-$AW$162)*(92-84))</f>
+        <f t="shared" ref="AX121:AX159" si="47">84+((AW121-$AW$162)/($AW$161-$AW$162)*(92-84))</f>
         <v>88.5884133755332</v>
       </c>
       <c r="AY121" s="207">
@@ -20587,19 +20587,19 @@
         <v>100</v>
       </c>
       <c r="AC122" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>500</v>
       </c>
       <c r="AD122" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>100</v>
       </c>
       <c r="AE122" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>420</v>
       </c>
       <c r="AF122" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>88</v>
       </c>
       <c r="AG122" s="160"/>
@@ -20608,7 +20608,7 @@
       </c>
       <c r="AI122" s="160"/>
       <c r="AJ122" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>91</v>
       </c>
       <c r="AK122" s="160"/>
@@ -20616,11 +20616,11 @@
       <c r="AM122" s="161"/>
       <c r="AN122" s="161"/>
       <c r="AO122" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP122" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ122" s="126">
@@ -20630,23 +20630,23 @@
         <v>558</v>
       </c>
       <c r="AT122" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU122" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV122" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>73.625</v>
       </c>
       <c r="AW122" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>80.8125</v>
       </c>
       <c r="AX122" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>88.5047474886473</v>
       </c>
       <c r="AY122" s="207">
@@ -20729,19 +20729,19 @@
         <v>90</v>
       </c>
       <c r="AC123" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>490</v>
       </c>
       <c r="AD123" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AE123" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>392</v>
       </c>
       <c r="AF123" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>86.88</v>
       </c>
       <c r="AG123" s="160"/>
@@ -20750,7 +20750,7 @@
       </c>
       <c r="AI123" s="160"/>
       <c r="AJ123" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>94</v>
       </c>
       <c r="AK123" s="160"/>
@@ -20758,11 +20758,11 @@
       <c r="AM123" s="161"/>
       <c r="AN123" s="161"/>
       <c r="AO123" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP123" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ123" s="126">
@@ -20772,23 +20772,23 @@
         <v>563</v>
       </c>
       <c r="AT123" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU123" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV123" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>75.125</v>
       </c>
       <c r="AW123" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>81.0025</v>
       </c>
       <c r="AX123" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>88.5884133755332</v>
       </c>
       <c r="AY123" s="207">
@@ -20871,19 +20871,19 @@
         <v>100</v>
       </c>
       <c r="AC124" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>500</v>
       </c>
       <c r="AD124" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AE124" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>400</v>
       </c>
       <c r="AF124" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>87.2</v>
       </c>
       <c r="AG124" s="160"/>
@@ -20894,7 +20894,7 @@
         <v>1</v>
       </c>
       <c r="AJ124" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>94</v>
       </c>
       <c r="AK124" s="160"/>
@@ -20902,11 +20902,11 @@
       <c r="AM124" s="161"/>
       <c r="AN124" s="161"/>
       <c r="AO124" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP124" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>1</v>
       </c>
       <c r="AQ124" s="126">
@@ -20916,23 +20916,23 @@
         <v>570</v>
       </c>
       <c r="AT124" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>100</v>
       </c>
       <c r="AU124" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>62.5</v>
       </c>
       <c r="AV124" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>78.25</v>
       </c>
       <c r="AW124" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>82.725</v>
       </c>
       <c r="AX124" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>89.3469106921701</v>
       </c>
       <c r="AY124" s="207">
@@ -21005,19 +21005,19 @@
         <v>90</v>
       </c>
       <c r="AC125" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>490</v>
       </c>
       <c r="AD125" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AE125" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>392</v>
       </c>
       <c r="AF125" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>86.88</v>
       </c>
       <c r="AG125" s="160"/>
@@ -21026,7 +21026,7 @@
       </c>
       <c r="AI125" s="160"/>
       <c r="AJ125" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>94</v>
       </c>
       <c r="AK125" s="160"/>
@@ -21034,11 +21034,11 @@
       <c r="AM125" s="161"/>
       <c r="AN125" s="161"/>
       <c r="AO125" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP125" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ125" s="126">
@@ -21048,23 +21048,23 @@
         <v>575</v>
       </c>
       <c r="AT125" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU125" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV125" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>75.125</v>
       </c>
       <c r="AW125" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>81.0025</v>
       </c>
       <c r="AX125" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>88.5884133755332</v>
       </c>
       <c r="AY125" s="207">
@@ -21147,19 +21147,19 @@
         <v>90</v>
       </c>
       <c r="AC126" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>490</v>
       </c>
       <c r="AD126" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>100</v>
       </c>
       <c r="AE126" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>412</v>
       </c>
       <c r="AF126" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>87.68</v>
       </c>
       <c r="AG126" s="160"/>
@@ -21168,7 +21168,7 @@
       </c>
       <c r="AI126" s="160"/>
       <c r="AJ126" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>88</v>
       </c>
       <c r="AK126" s="160"/>
@@ -21176,11 +21176,11 @@
       <c r="AM126" s="161"/>
       <c r="AN126" s="161"/>
       <c r="AO126" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP126" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ126" s="126">
@@ -21190,23 +21190,23 @@
         <v>580</v>
       </c>
       <c r="AT126" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU126" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV126" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>72.125</v>
       </c>
       <c r="AW126" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>79.9025</v>
       </c>
       <c r="AX126" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>88.104031925141</v>
       </c>
       <c r="AY126" s="207">
@@ -21289,19 +21289,19 @@
         <v>100</v>
       </c>
       <c r="AC127" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>500</v>
       </c>
       <c r="AD127" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AE127" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>400</v>
       </c>
       <c r="AF127" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>87.2</v>
       </c>
       <c r="AG127" s="160"/>
@@ -21310,7 +21310,7 @@
       </c>
       <c r="AI127" s="160"/>
       <c r="AJ127" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>79</v>
       </c>
       <c r="AK127" s="160"/>
@@ -21318,11 +21318,11 @@
       <c r="AM127" s="161"/>
       <c r="AN127" s="161"/>
       <c r="AO127" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP127" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ127" s="126">
@@ -21332,23 +21332,23 @@
         <v>586</v>
       </c>
       <c r="AT127" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU127" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV127" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>67.625</v>
       </c>
       <c r="AW127" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>77.4125</v>
       </c>
       <c r="AX127" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>87.0075684601624</v>
       </c>
       <c r="AY127" s="207">
@@ -21433,19 +21433,19 @@
         <v>90</v>
       </c>
       <c r="AC128" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>490</v>
       </c>
       <c r="AD128" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>100</v>
       </c>
       <c r="AE128" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>412</v>
       </c>
       <c r="AF128" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>87.68</v>
       </c>
       <c r="AG128" s="160">
@@ -21456,7 +21456,7 @@
       </c>
       <c r="AI128" s="160"/>
       <c r="AJ128" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>91</v>
       </c>
       <c r="AK128" s="160"/>
@@ -21464,11 +21464,11 @@
       <c r="AM128" s="161"/>
       <c r="AN128" s="161"/>
       <c r="AO128" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>102</v>
       </c>
       <c r="AP128" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ128" s="126">
@@ -21478,23 +21478,23 @@
         <v>593</v>
       </c>
       <c r="AT128" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>91.8</v>
       </c>
       <c r="AU128" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>57.375</v>
       </c>
       <c r="AV128" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>74.1875</v>
       </c>
       <c r="AW128" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>80.93375</v>
       </c>
       <c r="AX128" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>88.5581395348837</v>
       </c>
       <c r="AY128" s="207">
@@ -21577,19 +21577,19 @@
         <v>100</v>
       </c>
       <c r="AC129" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>500</v>
       </c>
       <c r="AD129" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AE129" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>400</v>
       </c>
       <c r="AF129" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>87.2</v>
       </c>
       <c r="AG129" s="160"/>
@@ -21598,7 +21598,7 @@
       </c>
       <c r="AI129" s="160"/>
       <c r="AJ129" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>79</v>
       </c>
       <c r="AK129" s="160"/>
@@ -21606,11 +21606,11 @@
       <c r="AM129" s="161"/>
       <c r="AN129" s="161"/>
       <c r="AO129" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP129" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ129" s="126">
@@ -21620,23 +21620,23 @@
         <v>598</v>
       </c>
       <c r="AT129" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU129" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV129" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>67.625</v>
       </c>
       <c r="AW129" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>77.4125</v>
       </c>
       <c r="AX129" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>87.0075684601624</v>
       </c>
       <c r="AY129" s="207">
@@ -21723,19 +21723,19 @@
         <v>100</v>
       </c>
       <c r="AC130" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>500</v>
       </c>
       <c r="AD130" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>600</v>
       </c>
       <c r="AE130" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>520</v>
       </c>
       <c r="AF130" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>92</v>
       </c>
       <c r="AG130" s="160"/>
@@ -21744,7 +21744,7 @@
       </c>
       <c r="AI130" s="160"/>
       <c r="AJ130" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>94</v>
       </c>
       <c r="AK130" s="160"/>
@@ -21752,11 +21752,11 @@
       <c r="AM130" s="161"/>
       <c r="AN130" s="161"/>
       <c r="AO130" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP130" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ130" s="126">
@@ -21766,23 +21766,23 @@
         <v>603</v>
       </c>
       <c r="AT130" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU130" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV130" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>75.125</v>
       </c>
       <c r="AW130" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>83.5625</v>
       </c>
       <c r="AX130" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>89.7157011146278</v>
       </c>
       <c r="AY130" s="207">
@@ -21869,19 +21869,19 @@
         <v>100</v>
       </c>
       <c r="AC131" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>500</v>
       </c>
       <c r="AD131" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>300</v>
       </c>
       <c r="AE131" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>460</v>
       </c>
       <c r="AF131" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>89.6</v>
       </c>
       <c r="AG131" s="160"/>
@@ -21892,7 +21892,7 @@
         <v>2</v>
       </c>
       <c r="AJ131" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>94</v>
       </c>
       <c r="AK131" s="160">
@@ -21902,11 +21902,11 @@
       <c r="AM131" s="161"/>
       <c r="AN131" s="161"/>
       <c r="AO131" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP131" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>3</v>
       </c>
       <c r="AQ131" s="126">
@@ -21916,23 +21916,23 @@
         <v>609</v>
       </c>
       <c r="AT131" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>120</v>
       </c>
       <c r="AU131" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>75</v>
       </c>
       <c r="AV131" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>84.5</v>
       </c>
       <c r="AW131" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>87.05</v>
       </c>
       <c r="AX131" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>91.2514104857575</v>
       </c>
       <c r="AY131" s="207">
@@ -22015,19 +22015,19 @@
         <v>100</v>
       </c>
       <c r="AC132" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>500</v>
       </c>
       <c r="AD132" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AE132" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>400</v>
       </c>
       <c r="AF132" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>87.2</v>
       </c>
       <c r="AG132" s="160"/>
@@ -22036,7 +22036,7 @@
       </c>
       <c r="AI132" s="160"/>
       <c r="AJ132" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>88</v>
       </c>
       <c r="AK132" s="160"/>
@@ -22044,11 +22044,11 @@
       <c r="AM132" s="161"/>
       <c r="AN132" s="161"/>
       <c r="AO132" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP132" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ132" s="126">
@@ -22058,23 +22058,23 @@
         <v>616</v>
       </c>
       <c r="AT132" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU132" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV132" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>72.125</v>
       </c>
       <c r="AW132" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>79.6625</v>
       </c>
       <c r="AX132" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>87.9983486996009</v>
       </c>
       <c r="AY132" s="207">
@@ -22159,19 +22159,19 @@
         <v>100</v>
       </c>
       <c r="AC133" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>500</v>
       </c>
       <c r="AD133" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>100</v>
       </c>
       <c r="AE133" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>420</v>
       </c>
       <c r="AF133" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>88</v>
       </c>
       <c r="AG133" s="160"/>
@@ -22180,7 +22180,7 @@
       </c>
       <c r="AI133" s="160"/>
       <c r="AJ133" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>88</v>
       </c>
       <c r="AK133" s="160"/>
@@ -22188,11 +22188,11 @@
       <c r="AM133" s="161"/>
       <c r="AN133" s="161"/>
       <c r="AO133" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP133" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ133" s="126">
@@ -22202,23 +22202,23 @@
         <v>620</v>
       </c>
       <c r="AT133" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU133" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV133" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>72.125</v>
       </c>
       <c r="AW133" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>80.0625</v>
       </c>
       <c r="AX133" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>88.1744874088345</v>
       </c>
       <c r="AY133" s="207">
@@ -22301,19 +22301,19 @@
         <v>95</v>
       </c>
       <c r="AC134" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>495</v>
       </c>
       <c r="AD134" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AE134" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>396</v>
       </c>
       <c r="AF134" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>87.04</v>
       </c>
       <c r="AG134" s="160"/>
@@ -22322,7 +22322,7 @@
       </c>
       <c r="AI134" s="160"/>
       <c r="AJ134" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>91</v>
       </c>
       <c r="AK134" s="160"/>
@@ -22330,11 +22330,11 @@
       <c r="AM134" s="161"/>
       <c r="AN134" s="161"/>
       <c r="AO134" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP134" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ134" s="126">
@@ -22344,23 +22344,23 @@
         <v>626</v>
       </c>
       <c r="AT134" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU134" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV134" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>73.625</v>
       </c>
       <c r="AW134" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>80.3325</v>
       </c>
       <c r="AX134" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>88.2933810375671</v>
       </c>
       <c r="AY134" s="207">
@@ -22451,19 +22451,19 @@
         <v>100</v>
       </c>
       <c r="AC135" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>500</v>
       </c>
       <c r="AD135" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>500</v>
       </c>
       <c r="AE135" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>500</v>
       </c>
       <c r="AF135" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>91.2</v>
       </c>
       <c r="AG135" s="160"/>
@@ -22474,7 +22474,7 @@
         <v>2</v>
       </c>
       <c r="AJ135" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>91</v>
       </c>
       <c r="AK135" s="160"/>
@@ -22482,11 +22482,11 @@
       <c r="AM135" s="161"/>
       <c r="AN135" s="161"/>
       <c r="AO135" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP135" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>2</v>
       </c>
       <c r="AQ135" s="126">
@@ -22496,23 +22496,23 @@
         <v>633</v>
       </c>
       <c r="AT135" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>110</v>
       </c>
       <c r="AU135" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>68.75</v>
       </c>
       <c r="AV135" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>79.875</v>
       </c>
       <c r="AW135" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>85.5375</v>
       </c>
       <c r="AX135" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>90.5853859914683</v>
       </c>
       <c r="AY135" s="207">
@@ -22597,19 +22597,19 @@
         <v>92</v>
       </c>
       <c r="AC136" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>492</v>
       </c>
       <c r="AD136" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>100</v>
       </c>
       <c r="AE136" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>413.6</v>
       </c>
       <c r="AF136" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>87.744</v>
       </c>
       <c r="AG136" s="160"/>
@@ -22618,7 +22618,7 @@
       </c>
       <c r="AI136" s="160"/>
       <c r="AJ136" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>91</v>
       </c>
       <c r="AK136" s="160"/>
@@ -22626,11 +22626,11 @@
       <c r="AM136" s="161"/>
       <c r="AN136" s="161"/>
       <c r="AO136" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP136" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ136" s="126">
@@ -22640,23 +22640,23 @@
         <v>637</v>
       </c>
       <c r="AT136" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU136" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV136" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>73.625</v>
       </c>
       <c r="AW136" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>80.6845</v>
       </c>
       <c r="AX136" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>88.4483831016926</v>
       </c>
       <c r="AY136" s="207">
@@ -22741,19 +22741,19 @@
         <v>90</v>
       </c>
       <c r="AC137" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>490</v>
       </c>
       <c r="AD137" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>600</v>
       </c>
       <c r="AE137" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>512</v>
       </c>
       <c r="AF137" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>91.68</v>
       </c>
       <c r="AG137" s="160"/>
@@ -22762,7 +22762,7 @@
       </c>
       <c r="AI137" s="160"/>
       <c r="AJ137" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>85</v>
       </c>
       <c r="AK137" s="160"/>
@@ -22770,11 +22770,11 @@
       <c r="AM137" s="161"/>
       <c r="AN137" s="161"/>
       <c r="AO137" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP137" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ137" s="126">
@@ -22784,23 +22784,23 @@
         <v>643</v>
       </c>
       <c r="AT137" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU137" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV137" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>70.625</v>
       </c>
       <c r="AW137" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>81.1525</v>
       </c>
       <c r="AX137" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>88.6544653914958</v>
       </c>
       <c r="AY137" s="207">
@@ -22889,19 +22889,19 @@
         <v>100</v>
       </c>
       <c r="AC138" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>500</v>
       </c>
       <c r="AD138" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>300</v>
       </c>
       <c r="AE138" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>460</v>
       </c>
       <c r="AF138" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>89.6</v>
       </c>
       <c r="AG138" s="160"/>
@@ -22910,7 +22910,7 @@
       </c>
       <c r="AI138" s="160"/>
       <c r="AJ138" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>94</v>
       </c>
       <c r="AK138" s="160"/>
@@ -22918,11 +22918,11 @@
       <c r="AM138" s="161"/>
       <c r="AN138" s="161"/>
       <c r="AO138" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP138" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ138" s="126">
@@ -22932,23 +22932,23 @@
         <v>649</v>
       </c>
       <c r="AT138" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU138" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV138" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>75.125</v>
       </c>
       <c r="AW138" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>82.3625</v>
       </c>
       <c r="AX138" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>89.1872849869272</v>
       </c>
       <c r="AY138" s="207">
@@ -23031,19 +23031,19 @@
         <v>94</v>
       </c>
       <c r="AC139" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>494</v>
       </c>
       <c r="AD139" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AE139" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>395.2</v>
       </c>
       <c r="AF139" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>87.008</v>
       </c>
       <c r="AG139" s="160"/>
@@ -23052,7 +23052,7 @@
       </c>
       <c r="AI139" s="160"/>
       <c r="AJ139" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>91</v>
       </c>
       <c r="AK139" s="160"/>
@@ -23060,11 +23060,11 @@
       <c r="AM139" s="161"/>
       <c r="AN139" s="161"/>
       <c r="AO139" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP139" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ139" s="126">
@@ -23074,23 +23074,23 @@
         <v>655</v>
       </c>
       <c r="AT139" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU139" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV139" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>73.625</v>
       </c>
       <c r="AW139" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>80.3165</v>
       </c>
       <c r="AX139" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>88.2863354891977</v>
       </c>
       <c r="AY139" s="207">
@@ -23173,19 +23173,19 @@
         <v>95</v>
       </c>
       <c r="AC140" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>495</v>
       </c>
       <c r="AD140" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AE140" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>396</v>
       </c>
       <c r="AF140" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>87.04</v>
       </c>
       <c r="AG140" s="160"/>
@@ -23194,7 +23194,7 @@
       </c>
       <c r="AI140" s="160"/>
       <c r="AJ140" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>94</v>
       </c>
       <c r="AK140" s="160"/>
@@ -23202,11 +23202,11 @@
       <c r="AM140" s="161"/>
       <c r="AN140" s="161"/>
       <c r="AO140" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP140" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ140" s="126">
@@ -23216,23 +23216,23 @@
         <v>662</v>
       </c>
       <c r="AT140" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU140" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV140" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>75.125</v>
       </c>
       <c r="AW140" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>81.0825</v>
       </c>
       <c r="AX140" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>88.6236411173799</v>
       </c>
       <c r="AY140" s="207">
@@ -23315,19 +23315,19 @@
         <v>100</v>
       </c>
       <c r="AC141" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>500</v>
       </c>
       <c r="AD141" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AE141" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>400</v>
       </c>
       <c r="AF141" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>87.2</v>
       </c>
       <c r="AG141" s="160"/>
@@ -23336,7 +23336,7 @@
       </c>
       <c r="AI141" s="160"/>
       <c r="AJ141" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>94</v>
       </c>
       <c r="AK141" s="160"/>
@@ -23344,11 +23344,11 @@
       <c r="AM141" s="161"/>
       <c r="AN141" s="161"/>
       <c r="AO141" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP141" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ141" s="126">
@@ -23358,23 +23358,23 @@
         <v>669</v>
       </c>
       <c r="AT141" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU141" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV141" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>75.125</v>
       </c>
       <c r="AW141" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>81.1625</v>
       </c>
       <c r="AX141" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>88.6588688592266</v>
       </c>
       <c r="AY141" s="207">
@@ -23457,19 +23457,19 @@
         <v>98</v>
       </c>
       <c r="AC142" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>498</v>
       </c>
       <c r="AD142" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AE142" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>398.4</v>
       </c>
       <c r="AF142" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>87.136</v>
       </c>
       <c r="AG142" s="160"/>
@@ -23478,7 +23478,7 @@
       </c>
       <c r="AI142" s="160"/>
       <c r="AJ142" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>82</v>
       </c>
       <c r="AK142" s="160"/>
@@ -23486,11 +23486,11 @@
       <c r="AM142" s="161"/>
       <c r="AN142" s="161"/>
       <c r="AO142" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP142" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ142" s="126">
@@ -23500,23 +23500,23 @@
         <v>675</v>
       </c>
       <c r="AT142" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU142" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV142" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>69.125</v>
       </c>
       <c r="AW142" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>78.1305</v>
       </c>
       <c r="AX142" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>87.3237374432365</v>
       </c>
       <c r="AY142" s="207">
@@ -23603,19 +23603,19 @@
         <v>100</v>
       </c>
       <c r="AC143" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>500</v>
       </c>
       <c r="AD143" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>600</v>
       </c>
       <c r="AE143" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>520</v>
       </c>
       <c r="AF143" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>92</v>
       </c>
       <c r="AG143" s="160"/>
@@ -23624,7 +23624,7 @@
       </c>
       <c r="AI143" s="160"/>
       <c r="AJ143" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>94</v>
       </c>
       <c r="AK143" s="160"/>
@@ -23632,11 +23632,11 @@
       <c r="AM143" s="161"/>
       <c r="AN143" s="161"/>
       <c r="AO143" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP143" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ143" s="126">
@@ -23646,23 +23646,23 @@
         <v>681</v>
       </c>
       <c r="AT143" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU143" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV143" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>75.125</v>
       </c>
       <c r="AW143" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>83.5625</v>
       </c>
       <c r="AX143" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>89.7157011146278</v>
       </c>
       <c r="AY143" s="207">
@@ -23745,19 +23745,19 @@
         <v>90</v>
       </c>
       <c r="AC144" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>490</v>
       </c>
       <c r="AD144" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AE144" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>392</v>
       </c>
       <c r="AF144" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>86.88</v>
       </c>
       <c r="AG144" s="160"/>
@@ -23766,7 +23766,7 @@
       </c>
       <c r="AI144" s="160"/>
       <c r="AJ144" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>94</v>
       </c>
       <c r="AK144" s="160"/>
@@ -23774,11 +23774,11 @@
       <c r="AM144" s="161"/>
       <c r="AN144" s="161"/>
       <c r="AO144" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP144" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ144" s="126">
@@ -23788,23 +23788,23 @@
         <v>687</v>
       </c>
       <c r="AT144" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU144" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV144" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>75.125</v>
       </c>
       <c r="AW144" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>81.0025</v>
       </c>
       <c r="AX144" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>88.5884133755332</v>
       </c>
       <c r="AY144" s="207">
@@ -23889,19 +23889,19 @@
         <v>95</v>
       </c>
       <c r="AC145" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>495</v>
       </c>
       <c r="AD145" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>100</v>
       </c>
       <c r="AE145" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>416</v>
       </c>
       <c r="AF145" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>87.84</v>
       </c>
       <c r="AG145" s="160"/>
@@ -23910,7 +23910,7 @@
       </c>
       <c r="AI145" s="160"/>
       <c r="AJ145" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>94</v>
       </c>
       <c r="AK145" s="160"/>
@@ -23918,11 +23918,11 @@
       <c r="AM145" s="161"/>
       <c r="AN145" s="161"/>
       <c r="AO145" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP145" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ145" s="126">
@@ -23932,23 +23932,23 @@
         <v>693</v>
       </c>
       <c r="AT145" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU145" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV145" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>75.125</v>
       </c>
       <c r="AW145" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>81.4825</v>
       </c>
       <c r="AX145" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>88.7997798266135</v>
       </c>
       <c r="AY145" s="207">
@@ -24029,19 +24029,19 @@
         <v>100</v>
       </c>
       <c r="AC146" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>500</v>
       </c>
       <c r="AD146" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AE146" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>400</v>
       </c>
       <c r="AF146" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>87.2</v>
       </c>
       <c r="AG146" s="160"/>
@@ -24050,7 +24050,7 @@
       </c>
       <c r="AI146" s="160"/>
       <c r="AJ146" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>76</v>
       </c>
       <c r="AK146" s="160"/>
@@ -24058,11 +24058,11 @@
       <c r="AM146" s="161"/>
       <c r="AN146" s="161"/>
       <c r="AO146" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP146" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ146" s="126">
@@ -24072,23 +24072,23 @@
         <v>700</v>
       </c>
       <c r="AT146" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU146" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV146" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>66.125</v>
       </c>
       <c r="AW146" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>76.6625</v>
       </c>
       <c r="AX146" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>86.6773083803495</v>
       </c>
       <c r="AY146" s="207">
@@ -24177,19 +24177,19 @@
         <v>100</v>
       </c>
       <c r="AC147" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>500</v>
       </c>
       <c r="AD147" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>200</v>
       </c>
       <c r="AE147" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>440</v>
       </c>
       <c r="AF147" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>88.8</v>
       </c>
       <c r="AG147" s="160"/>
@@ -24200,7 +24200,7 @@
         <v>1</v>
       </c>
       <c r="AJ147" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>94</v>
       </c>
       <c r="AK147" s="160"/>
@@ -24208,11 +24208,11 @@
       <c r="AM147" s="161"/>
       <c r="AN147" s="161"/>
       <c r="AO147" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP147" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>1</v>
       </c>
       <c r="AQ147" s="126">
@@ -24222,23 +24222,23 @@
         <v>706</v>
       </c>
       <c r="AT147" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>100</v>
       </c>
       <c r="AU147" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>62.5</v>
       </c>
       <c r="AV147" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>78.25</v>
       </c>
       <c r="AW147" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>83.525</v>
       </c>
       <c r="AX147" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>89.6991881106371</v>
       </c>
       <c r="AY147" s="207">
@@ -24325,19 +24325,19 @@
         <v>95</v>
       </c>
       <c r="AC148" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>495</v>
       </c>
       <c r="AD148" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>200</v>
       </c>
       <c r="AE148" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>436</v>
       </c>
       <c r="AF148" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>88.64</v>
       </c>
       <c r="AG148" s="160"/>
@@ -24346,7 +24346,7 @@
       </c>
       <c r="AI148" s="160"/>
       <c r="AJ148" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>94</v>
       </c>
       <c r="AK148" s="160"/>
@@ -24354,11 +24354,11 @@
       <c r="AM148" s="161"/>
       <c r="AN148" s="161"/>
       <c r="AO148" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP148" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ148" s="126">
@@ -24368,23 +24368,23 @@
         <v>712</v>
       </c>
       <c r="AT148" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU148" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV148" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>75.125</v>
       </c>
       <c r="AW148" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>81.8825</v>
       </c>
       <c r="AX148" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>88.975918535847</v>
       </c>
       <c r="AY148" s="207">
@@ -24469,19 +24469,19 @@
         <v>100</v>
       </c>
       <c r="AC149" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>500</v>
       </c>
       <c r="AD149" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>100</v>
       </c>
       <c r="AE149" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>420</v>
       </c>
       <c r="AF149" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>88</v>
       </c>
       <c r="AG149" s="160"/>
@@ -24492,7 +24492,7 @@
         <v>7</v>
       </c>
       <c r="AJ149" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>79</v>
       </c>
       <c r="AK149" s="160"/>
@@ -24500,11 +24500,11 @@
       <c r="AM149" s="161"/>
       <c r="AN149" s="161"/>
       <c r="AO149" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP149" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>7</v>
       </c>
       <c r="AQ149" s="126">
@@ -24514,23 +24514,23 @@
         <v>716</v>
       </c>
       <c r="AT149" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>160</v>
       </c>
       <c r="AU149" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>100</v>
       </c>
       <c r="AV149" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>89.5</v>
       </c>
       <c r="AW149" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>88.75</v>
       </c>
       <c r="AX149" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>92</v>
       </c>
       <c r="AY149" s="207">
@@ -24613,19 +24613,19 @@
         <v>100</v>
       </c>
       <c r="AC150" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>500</v>
       </c>
       <c r="AD150" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AE150" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>400</v>
       </c>
       <c r="AF150" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>87.2</v>
       </c>
       <c r="AG150" s="160"/>
@@ -24634,7 +24634,7 @@
       </c>
       <c r="AI150" s="160"/>
       <c r="AJ150" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>94</v>
       </c>
       <c r="AK150" s="160"/>
@@ -24642,11 +24642,11 @@
       <c r="AM150" s="161"/>
       <c r="AN150" s="161"/>
       <c r="AO150" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP150" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ150" s="126">
@@ -24656,23 +24656,23 @@
         <v>722</v>
       </c>
       <c r="AT150" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU150" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV150" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>75.125</v>
       </c>
       <c r="AW150" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>81.1625</v>
       </c>
       <c r="AX150" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>88.6588688592266</v>
       </c>
       <c r="AY150" s="207">
@@ -24755,19 +24755,19 @@
         <v>100</v>
       </c>
       <c r="AC151" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>500</v>
       </c>
       <c r="AD151" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AE151" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>400</v>
       </c>
       <c r="AF151" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>87.2</v>
       </c>
       <c r="AG151" s="160"/>
@@ -24776,7 +24776,7 @@
       </c>
       <c r="AI151" s="160"/>
       <c r="AJ151" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>94</v>
       </c>
       <c r="AK151" s="160"/>
@@ -24784,11 +24784,11 @@
       <c r="AM151" s="161"/>
       <c r="AN151" s="161"/>
       <c r="AO151" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP151" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ151" s="126">
@@ -24798,23 +24798,23 @@
         <v>728</v>
       </c>
       <c r="AT151" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU151" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV151" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>75.125</v>
       </c>
       <c r="AW151" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>81.1625</v>
       </c>
       <c r="AX151" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>88.6588688592266</v>
       </c>
       <c r="AY151" s="207">
@@ -24899,19 +24899,19 @@
         <v>100</v>
       </c>
       <c r="AC152" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>500</v>
       </c>
       <c r="AD152" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>100</v>
       </c>
       <c r="AE152" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>420</v>
       </c>
       <c r="AF152" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>88</v>
       </c>
       <c r="AG152" s="160"/>
@@ -24920,7 +24920,7 @@
       </c>
       <c r="AI152" s="160"/>
       <c r="AJ152" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>88</v>
       </c>
       <c r="AK152" s="160"/>
@@ -24928,11 +24928,11 @@
       <c r="AM152" s="161"/>
       <c r="AN152" s="161"/>
       <c r="AO152" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP152" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ152" s="126">
@@ -24942,23 +24942,23 @@
         <v>734</v>
       </c>
       <c r="AT152" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU152" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV152" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>72.125</v>
       </c>
       <c r="AW152" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>80.0625</v>
       </c>
       <c r="AX152" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>88.1744874088345</v>
       </c>
       <c r="AY152" s="207">
@@ -25041,19 +25041,19 @@
         <v>98</v>
       </c>
       <c r="AC153" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>498</v>
       </c>
       <c r="AD153" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>100</v>
       </c>
       <c r="AE153" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>418.4</v>
       </c>
       <c r="AF153" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>87.936</v>
       </c>
       <c r="AG153" s="160"/>
@@ -25062,7 +25062,7 @@
       </c>
       <c r="AI153" s="160"/>
       <c r="AJ153" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>88</v>
       </c>
       <c r="AK153" s="160"/>
@@ -25070,11 +25070,11 @@
       <c r="AM153" s="161"/>
       <c r="AN153" s="161"/>
       <c r="AO153" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP153" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ153" s="126">
@@ -25084,23 +25084,23 @@
         <v>741</v>
       </c>
       <c r="AT153" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU153" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV153" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>72.125</v>
       </c>
       <c r="AW153" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>80.0305</v>
       </c>
       <c r="AX153" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>88.1603963120958</v>
       </c>
       <c r="AY153" s="207">
@@ -25181,19 +25181,19 @@
       <c r="AA154" s="160"/>
       <c r="AB154" s="160"/>
       <c r="AC154" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>400</v>
       </c>
       <c r="AD154" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AE154" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>320</v>
       </c>
       <c r="AF154" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>84</v>
       </c>
       <c r="AG154" s="160"/>
@@ -25202,7 +25202,7 @@
       </c>
       <c r="AI154" s="160"/>
       <c r="AJ154" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>94</v>
       </c>
       <c r="AK154" s="160"/>
@@ -25210,11 +25210,11 @@
       <c r="AM154" s="161"/>
       <c r="AN154" s="161"/>
       <c r="AO154" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP154" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ154" s="126">
@@ -25224,23 +25224,23 @@
         <v>747</v>
       </c>
       <c r="AT154" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU154" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV154" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>75.125</v>
       </c>
       <c r="AW154" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>79.5625</v>
       </c>
       <c r="AX154" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>87.9543140222926</v>
       </c>
       <c r="AY154" s="207">
@@ -25325,19 +25325,19 @@
         <v>100</v>
       </c>
       <c r="AC155" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>500</v>
       </c>
       <c r="AD155" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>200</v>
       </c>
       <c r="AE155" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>440</v>
       </c>
       <c r="AF155" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>88.8</v>
       </c>
       <c r="AG155" s="160"/>
@@ -25346,7 +25346,7 @@
       </c>
       <c r="AI155" s="160"/>
       <c r="AJ155" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>94</v>
       </c>
       <c r="AK155" s="160">
@@ -25356,11 +25356,11 @@
       <c r="AM155" s="161"/>
       <c r="AN155" s="161"/>
       <c r="AO155" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP155" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>1</v>
       </c>
       <c r="AQ155" s="126">
@@ -25370,23 +25370,23 @@
         <v>753</v>
       </c>
       <c r="AT155" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>100</v>
       </c>
       <c r="AU155" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>62.5</v>
       </c>
       <c r="AV155" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>78.25</v>
       </c>
       <c r="AW155" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>83.525</v>
       </c>
       <c r="AX155" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>89.6991881106371</v>
       </c>
       <c r="AY155" s="207">
@@ -25469,19 +25469,19 @@
         <v>95</v>
       </c>
       <c r="AC156" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>495</v>
       </c>
       <c r="AD156" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AE156" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>396</v>
       </c>
       <c r="AF156" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>87.04</v>
       </c>
       <c r="AG156" s="160"/>
@@ -25490,7 +25490,7 @@
       </c>
       <c r="AI156" s="160"/>
       <c r="AJ156" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>52</v>
       </c>
       <c r="AK156" s="160"/>
@@ -25498,11 +25498,11 @@
       <c r="AM156" s="161"/>
       <c r="AN156" s="161"/>
       <c r="AO156" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP156" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ156" s="126">
@@ -25512,23 +25512,23 @@
         <v>760</v>
       </c>
       <c r="AT156" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU156" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV156" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>54.125</v>
       </c>
       <c r="AW156" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>70.5825</v>
       </c>
       <c r="AX156" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>84</v>
       </c>
       <c r="AY156" s="207">
@@ -25617,19 +25617,19 @@
         <v>100</v>
       </c>
       <c r="AC157" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>500</v>
       </c>
       <c r="AD157" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>200</v>
       </c>
       <c r="AE157" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>440</v>
       </c>
       <c r="AF157" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>88.8</v>
       </c>
       <c r="AG157" s="160"/>
@@ -25638,7 +25638,7 @@
       </c>
       <c r="AI157" s="160"/>
       <c r="AJ157" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>85</v>
       </c>
       <c r="AK157" s="160"/>
@@ -25646,11 +25646,11 @@
       <c r="AM157" s="161"/>
       <c r="AN157" s="161"/>
       <c r="AO157" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP157" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ157" s="126">
@@ -25660,23 +25660,23 @@
         <v>766</v>
       </c>
       <c r="AT157" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU157" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV157" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>70.625</v>
       </c>
       <c r="AW157" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>79.7125</v>
       </c>
       <c r="AX157" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>88.0203660382551</v>
       </c>
       <c r="AY157" s="207">
@@ -25761,19 +25761,19 @@
         <v>100</v>
       </c>
       <c r="AC158" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>500</v>
       </c>
       <c r="AD158" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>100</v>
       </c>
       <c r="AE158" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>420</v>
       </c>
       <c r="AF158" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>88</v>
       </c>
       <c r="AG158" s="160"/>
@@ -25782,7 +25782,7 @@
       </c>
       <c r="AI158" s="160"/>
       <c r="AJ158" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>94</v>
       </c>
       <c r="AK158" s="160"/>
@@ -25790,11 +25790,11 @@
       <c r="AM158" s="161"/>
       <c r="AN158" s="161"/>
       <c r="AO158" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP158" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ158" s="126">
@@ -25804,23 +25804,23 @@
         <v>773</v>
       </c>
       <c r="AT158" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU158" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV158" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>75.125</v>
       </c>
       <c r="AW158" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>81.5625</v>
       </c>
       <c r="AX158" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>88.8350075684602</v>
       </c>
       <c r="AY158" s="207">
@@ -25903,19 +25903,19 @@
         <v>95</v>
       </c>
       <c r="AC159" s="78">
-        <f t="shared" si="24"/>
+        <f t="shared" si="36"/>
         <v>495</v>
       </c>
       <c r="AD159" s="160">
-        <f t="shared" si="25"/>
+        <f t="shared" si="37"/>
         <v>100</v>
       </c>
       <c r="AE159" s="196">
-        <f t="shared" si="26"/>
+        <f t="shared" si="38"/>
         <v>416</v>
       </c>
       <c r="AF159" s="201">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>87.84</v>
       </c>
       <c r="AG159" s="160"/>
@@ -25924,7 +25924,7 @@
       </c>
       <c r="AI159" s="160"/>
       <c r="AJ159" s="160">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>94</v>
       </c>
       <c r="AK159" s="160"/>
@@ -25932,11 +25932,11 @@
       <c r="AM159" s="161"/>
       <c r="AN159" s="161"/>
       <c r="AO159" s="161">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>100</v>
       </c>
       <c r="AP159" s="160">
-        <f t="shared" si="30"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AQ159" s="126">
@@ -25946,23 +25946,23 @@
         <v>779</v>
       </c>
       <c r="AT159" s="128">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>90</v>
       </c>
       <c r="AU159" s="204">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>56.25</v>
       </c>
       <c r="AV159" s="205">
-        <f t="shared" si="33"/>
+        <f t="shared" si="45"/>
         <v>75.125</v>
       </c>
       <c r="AW159" s="206">
-        <f t="shared" si="34"/>
+        <f t="shared" si="46"/>
         <v>81.4825</v>
       </c>
       <c r="AX159" s="206">
-        <f t="shared" si="35"/>
+        <f t="shared" si="47"/>
         <v>88.7997798266135</v>
       </c>
       <c r="AY159" s="207">
@@ -25994,7 +25994,7 @@
         <v>520</v>
       </c>
       <c r="AF160" s="216">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>92</v>
       </c>
     </row>
@@ -26021,7 +26021,7 @@
         <v>320</v>
       </c>
       <c r="AF161" s="216">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>84</v>
       </c>
       <c r="AT161" s="128">
@@ -31854,13 +31854,17 @@
       <c r="AF59" s="112">
         <v>40</v>
       </c>
-      <c r="AG59" s="96"/>
-      <c r="AH59" s="96"/>
+      <c r="AG59" s="96">
+        <v>100</v>
+      </c>
+      <c r="AH59" s="96">
+        <v>100</v>
+      </c>
       <c r="AI59" s="96"/>
       <c r="AJ59" s="96"/>
       <c r="AK59" s="67">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AL59" s="66">
         <v>96</v>
@@ -31870,18 +31874,18 @@
       </c>
       <c r="AN59" s="67">
         <f t="shared" si="4"/>
-        <v>28.8</v>
+        <v>63.8</v>
       </c>
       <c r="AO59" s="114">
         <f t="shared" si="5"/>
-        <v>34.4</v>
+        <v>51.9</v>
       </c>
       <c r="AP59" s="115">
         <f t="shared" si="6"/>
-        <v>77.4875</v>
+        <v>81.0421875</v>
       </c>
       <c r="AQ59" s="117">
-        <v>77.4875</v>
+        <v>81.04</v>
       </c>
       <c r="AR59" s="92" t="s">
         <v>950</v>
@@ -33707,7 +33711,7 @@
       </c>
       <c r="AO86" s="114">
         <f t="shared" si="14"/>
-        <v>48.6101804123711</v>
+        <v>48.6101804123712</v>
       </c>
       <c r="AP86" s="115">
         <f t="shared" si="15"/>
@@ -33832,7 +33836,7 @@
       </c>
       <c r="AO87" s="114">
         <f t="shared" si="14"/>
-        <v>83.4684278350515</v>
+        <v>83.4684278350516</v>
       </c>
       <c r="AP87" s="115">
         <f t="shared" si="15"/>
@@ -34086,7 +34090,7 @@
       </c>
       <c r="AP89" s="115">
         <f t="shared" si="15"/>
-        <v>89.6612016611057</v>
+        <v>89.6612016611056</v>
       </c>
       <c r="AQ89" s="117">
         <v>89.6612016611057</v>
@@ -34342,7 +34346,7 @@
       </c>
       <c r="AO91" s="114">
         <f t="shared" si="14"/>
-        <v>73.5288659793814</v>
+        <v>73.5288659793815</v>
       </c>
       <c r="AP91" s="115">
         <f t="shared" si="15"/>
@@ -34469,7 +34473,7 @@
       </c>
       <c r="AO92" s="114">
         <f t="shared" si="14"/>
-        <v>82.1710051546392</v>
+        <v>82.1710051546391</v>
       </c>
       <c r="AP92" s="115">
         <f t="shared" si="15"/>
@@ -34567,16 +34571,18 @@
         <v>85.5154639175258</v>
       </c>
       <c r="AG93" s="96">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH93" s="96">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AI93" s="96"/>
-      <c r="AJ93" s="77"/>
+      <c r="AJ93" s="77">
+        <v>85</v>
+      </c>
       <c r="AK93" s="67">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="AL93" s="67">
         <v>92</v>
@@ -34586,18 +34592,18 @@
       </c>
       <c r="AN93" s="67">
         <f t="shared" si="13"/>
-        <v>27.6</v>
+        <v>77.475</v>
       </c>
       <c r="AO93" s="114">
         <f t="shared" si="14"/>
-        <v>56.5577319587629</v>
+        <v>81.4952319587629</v>
       </c>
       <c r="AP93" s="115">
         <f t="shared" si="15"/>
-        <v>84.6968962289061</v>
+        <v>89.3421109484145</v>
       </c>
       <c r="AQ93" s="116">
-        <v>84.6968962289061</v>
+        <v>89.3421109484145</v>
       </c>
       <c r="AR93" s="122" t="s">
         <v>1012</v>
@@ -34834,7 +34840,7 @@
       </c>
       <c r="AO95" s="114">
         <f t="shared" si="14"/>
-        <v>78.2335051546392</v>
+        <v>78.2335051546391</v>
       </c>
       <c r="AP95" s="115">
         <f t="shared" si="15"/>
@@ -35693,7 +35699,7 @@
       </c>
       <c r="AO102" s="114">
         <f t="shared" si="14"/>
-        <v>69.3802835051546</v>
+        <v>69.3802835051547</v>
       </c>
       <c r="AP102" s="115">
         <f t="shared" si="15"/>
@@ -36066,7 +36072,7 @@
       </c>
       <c r="AO105" s="114">
         <f t="shared" si="14"/>
-        <v>83.4684278350515</v>
+        <v>83.4684278350516</v>
       </c>
       <c r="AP105" s="115">
         <f t="shared" si="15"/>
@@ -37627,7 +37633,7 @@
       </c>
       <c r="AO118" s="114">
         <f t="shared" si="14"/>
-        <v>58.5565721649485</v>
+        <v>58.5565721649484</v>
       </c>
       <c r="AP118" s="115">
         <f t="shared" si="15"/>
@@ -37951,7 +37957,7 @@
       </c>
       <c r="AO121" s="114">
         <f t="shared" si="14"/>
-        <v>80.4684278350515</v>
+        <v>80.4684278350516</v>
       </c>
       <c r="AP121" s="115">
         <f t="shared" si="15"/>
@@ -38282,7 +38288,7 @@
       </c>
       <c r="AO124" s="114">
         <f t="shared" si="14"/>
-        <v>80.5844072164948</v>
+        <v>80.5844072164949</v>
       </c>
       <c r="AP124" s="115">
         <f t="shared" si="15"/>
@@ -38397,7 +38403,7 @@
       </c>
       <c r="AO125" s="114">
         <f t="shared" si="14"/>
-        <v>84.2538659793814</v>
+        <v>84.2538659793815</v>
       </c>
       <c r="AP125" s="115">
         <f t="shared" si="15"/>
@@ -38571,11 +38577,11 @@
       <c r="AF128" s="139"/>
       <c r="AG128" s="67">
         <f>COUNTIF(AG79:AG126,100)</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AH128" s="67">
         <f>COUNTIF(AH79:AH126,100)</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AO128" s="68">
         <f>MAX(AO79:AO126)</f>
@@ -38599,11 +38605,11 @@
       </c>
       <c r="AG129" s="144">
         <f>AG128/AG127</f>
-        <v>0.8125</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="AH129" s="145">
         <f>AH128/AH127</f>
-        <v>0.625</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="AO129" s="68">
         <f>MIN(AO79:AO126)</f>

--- a/Rekap Absen dan Nilai 2025-2026.xlsx
+++ b/Rekap Absen dan Nilai 2025-2026.xlsx
@@ -6776,9 +6776,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>12600</xdr:colOff>
+      <xdr:colOff>12960</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>106920</xdr:rowOff>
+      <xdr:rowOff>107280</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6788,9 +6788,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="1170000"/>
-          <a:ext cx="24086520" cy="41760"/>
+          <a:ext cx="24086880" cy="42120"/>
           <a:chOff x="35280" y="1170000"/>
-          <a:chExt cx="24086520" cy="41760"/>
+          <a:chExt cx="24086880" cy="42120"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -6801,7 +6801,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="36360" y="1188000"/>
-            <a:ext cx="24085800" cy="24120"/>
+            <a:ext cx="24086160" cy="24480"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -6822,7 +6822,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="1170000"/>
-            <a:ext cx="24079320" cy="24120"/>
+            <a:ext cx="24079680" cy="24480"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -6847,9 +6847,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>725400</xdr:colOff>
+      <xdr:colOff>725040</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>100440</xdr:rowOff>
+      <xdr:rowOff>100080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6864,7 +6864,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="57240"/>
-          <a:ext cx="1088640" cy="805320"/>
+          <a:ext cx="1088280" cy="804960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6886,9 +6886,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>725400</xdr:colOff>
+      <xdr:colOff>725040</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>119520</xdr:rowOff>
+      <xdr:rowOff>119160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6903,7 +6903,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="8798040"/>
-          <a:ext cx="1088640" cy="805320"/>
+          <a:ext cx="1088280" cy="804960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6925,9 +6925,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>725400</xdr:colOff>
+      <xdr:colOff>725040</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>119520</xdr:rowOff>
+      <xdr:rowOff>119160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6942,7 +6942,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="8798040"/>
-          <a:ext cx="1088640" cy="805320"/>
+          <a:ext cx="1088280" cy="804960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6964,9 +6964,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>12600</xdr:colOff>
+      <xdr:colOff>12960</xdr:colOff>
       <xdr:row>55</xdr:row>
-      <xdr:rowOff>106920</xdr:rowOff>
+      <xdr:rowOff>107280</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6976,9 +6976,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="10130040"/>
-          <a:ext cx="24086520" cy="41760"/>
+          <a:ext cx="24086880" cy="42120"/>
           <a:chOff x="35280" y="10130040"/>
-          <a:chExt cx="24086520" cy="41760"/>
+          <a:chExt cx="24086880" cy="42120"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -6989,7 +6989,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="36360" y="10148040"/>
-            <a:ext cx="24085800" cy="24120"/>
+            <a:ext cx="24086160" cy="24480"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7010,7 +7010,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="10130040"/>
-            <a:ext cx="24079320" cy="24120"/>
+            <a:ext cx="24079680" cy="24480"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7035,9 +7035,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>725400</xdr:colOff>
+      <xdr:colOff>725040</xdr:colOff>
       <xdr:row>53</xdr:row>
-      <xdr:rowOff>113400</xdr:rowOff>
+      <xdr:rowOff>113040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7052,7 +7052,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="9026640"/>
-          <a:ext cx="1088640" cy="808560"/>
+          <a:ext cx="1088280" cy="808200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7074,9 +7074,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>12600</xdr:colOff>
+      <xdr:colOff>12960</xdr:colOff>
       <xdr:row>114</xdr:row>
-      <xdr:rowOff>106920</xdr:rowOff>
+      <xdr:rowOff>107280</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -7086,9 +7086,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="20822040"/>
-          <a:ext cx="24086520" cy="41760"/>
+          <a:ext cx="24086880" cy="42120"/>
           <a:chOff x="35280" y="20822040"/>
-          <a:chExt cx="24086520" cy="41760"/>
+          <a:chExt cx="24086880" cy="42120"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -7099,7 +7099,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="36360" y="20840040"/>
-            <a:ext cx="24085800" cy="24120"/>
+            <a:ext cx="24086160" cy="24480"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7120,7 +7120,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="20822040"/>
-            <a:ext cx="24079320" cy="24120"/>
+            <a:ext cx="24079680" cy="24480"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7145,9 +7145,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>729000</xdr:colOff>
+      <xdr:colOff>728640</xdr:colOff>
       <xdr:row>112</xdr:row>
-      <xdr:rowOff>94320</xdr:rowOff>
+      <xdr:rowOff>93960</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7157,7 +7157,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4320" y="19703520"/>
-          <a:ext cx="1088640" cy="804960"/>
+          <a:ext cx="1088280" cy="804600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7223,9 +7223,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>13320</xdr:colOff>
+      <xdr:colOff>13680</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>106920</xdr:rowOff>
+      <xdr:rowOff>107280</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -7235,9 +7235,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="1112760"/>
-          <a:ext cx="3128400" cy="41760"/>
+          <a:ext cx="3128760" cy="42120"/>
           <a:chOff x="35280" y="1112760"/>
-          <a:chExt cx="3128400" cy="41760"/>
+          <a:chExt cx="3128760" cy="42120"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -7248,7 +7248,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="36360" y="1130760"/>
-            <a:ext cx="3127680" cy="24120"/>
+            <a:ext cx="3128040" cy="24480"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7269,7 +7269,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="1112760"/>
-            <a:ext cx="3127320" cy="24120"/>
+            <a:ext cx="3127680" cy="24480"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7294,9 +7294,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>738720</xdr:colOff>
+      <xdr:colOff>738360</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>11520</xdr:rowOff>
+      <xdr:rowOff>11160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7311,7 +7311,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="57240"/>
-          <a:ext cx="1087920" cy="811440"/>
+          <a:ext cx="1087560" cy="811080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7333,9 +7333,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>13320</xdr:colOff>
+      <xdr:colOff>13680</xdr:colOff>
       <xdr:row>73</xdr:row>
-      <xdr:rowOff>106920</xdr:rowOff>
+      <xdr:rowOff>107280</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -7345,9 +7345,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="12190320"/>
-          <a:ext cx="3128400" cy="41760"/>
+          <a:ext cx="3128760" cy="42120"/>
           <a:chOff x="35280" y="12190320"/>
-          <a:chExt cx="3128400" cy="41760"/>
+          <a:chExt cx="3128760" cy="42120"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -7358,7 +7358,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="36360" y="12208320"/>
-            <a:ext cx="3127680" cy="24120"/>
+            <a:ext cx="3128040" cy="24480"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7379,7 +7379,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="12190320"/>
-            <a:ext cx="3127320" cy="24120"/>
+            <a:ext cx="3127680" cy="24480"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7404,9 +7404,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>738720</xdr:colOff>
+      <xdr:colOff>738360</xdr:colOff>
       <xdr:row>72</xdr:row>
-      <xdr:rowOff>11520</xdr:rowOff>
+      <xdr:rowOff>11160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7421,7 +7421,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="11134800"/>
-          <a:ext cx="1087920" cy="811440"/>
+          <a:ext cx="1087560" cy="811080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7443,9 +7443,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>13320</xdr:colOff>
+      <xdr:colOff>13680</xdr:colOff>
       <xdr:row>140</xdr:row>
-      <xdr:rowOff>106920</xdr:rowOff>
+      <xdr:rowOff>107280</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -7455,9 +7455,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="23296680"/>
-          <a:ext cx="3128400" cy="41760"/>
+          <a:ext cx="3128760" cy="42120"/>
           <a:chOff x="35280" y="23296680"/>
-          <a:chExt cx="3128400" cy="41760"/>
+          <a:chExt cx="3128760" cy="42120"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -7468,7 +7468,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="36360" y="23314680"/>
-            <a:ext cx="3127680" cy="24120"/>
+            <a:ext cx="3128040" cy="24480"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7489,7 +7489,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="23296680"/>
-            <a:ext cx="3127320" cy="24120"/>
+            <a:ext cx="3127680" cy="24480"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7514,9 +7514,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>738720</xdr:colOff>
+      <xdr:colOff>738360</xdr:colOff>
       <xdr:row>139</xdr:row>
-      <xdr:rowOff>11520</xdr:rowOff>
+      <xdr:rowOff>11160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7531,7 +7531,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="22240800"/>
-          <a:ext cx="1087920" cy="811800"/>
+          <a:ext cx="1087560" cy="811440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7558,9 +7558,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>12600</xdr:colOff>
+      <xdr:colOff>12960</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>106920</xdr:rowOff>
+      <xdr:rowOff>107280</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -7570,9 +7570,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="1170000"/>
-          <a:ext cx="5641560" cy="41760"/>
+          <a:ext cx="5641920" cy="42120"/>
           <a:chOff x="35280" y="1170000"/>
-          <a:chExt cx="5641560" cy="41760"/>
+          <a:chExt cx="5641920" cy="42120"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -7583,7 +7583,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="1188000"/>
-            <a:ext cx="5641920" cy="24120"/>
+            <a:ext cx="5642280" cy="24480"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7604,7 +7604,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="1170000"/>
-            <a:ext cx="5640120" cy="24120"/>
+            <a:ext cx="5640480" cy="24480"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7629,9 +7629,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>725400</xdr:colOff>
+      <xdr:colOff>725040</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>100440</xdr:rowOff>
+      <xdr:rowOff>100080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7646,7 +7646,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="57240"/>
-          <a:ext cx="1088640" cy="805320"/>
+          <a:ext cx="1088280" cy="804960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7668,9 +7668,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>725400</xdr:colOff>
+      <xdr:colOff>725040</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>119520</xdr:rowOff>
+      <xdr:rowOff>119160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7685,7 +7685,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="8439840"/>
-          <a:ext cx="1088640" cy="805320"/>
+          <a:ext cx="1088280" cy="804960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7707,9 +7707,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>725400</xdr:colOff>
+      <xdr:colOff>725040</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>119520</xdr:rowOff>
+      <xdr:rowOff>119160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7724,7 +7724,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="8439840"/>
-          <a:ext cx="1088640" cy="805320"/>
+          <a:ext cx="1088280" cy="804960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7746,9 +7746,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>12600</xdr:colOff>
+      <xdr:colOff>12960</xdr:colOff>
       <xdr:row>55</xdr:row>
-      <xdr:rowOff>106920</xdr:rowOff>
+      <xdr:rowOff>107280</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -7758,9 +7758,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="9771840"/>
-          <a:ext cx="5641560" cy="41760"/>
+          <a:ext cx="5641920" cy="42120"/>
           <a:chOff x="35280" y="9771840"/>
-          <a:chExt cx="5641560" cy="41760"/>
+          <a:chExt cx="5641920" cy="42120"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -7771,7 +7771,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="9789840"/>
-            <a:ext cx="5641920" cy="24120"/>
+            <a:ext cx="5642280" cy="24480"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7792,7 +7792,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="9771840"/>
-            <a:ext cx="5640120" cy="24120"/>
+            <a:ext cx="5640480" cy="24480"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7817,9 +7817,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>725400</xdr:colOff>
+      <xdr:colOff>725040</xdr:colOff>
       <xdr:row>53</xdr:row>
-      <xdr:rowOff>113400</xdr:rowOff>
+      <xdr:rowOff>113040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7834,7 +7834,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="8668440"/>
-          <a:ext cx="1088640" cy="808560"/>
+          <a:ext cx="1088280" cy="808200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7856,9 +7856,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>12600</xdr:colOff>
+      <xdr:colOff>12960</xdr:colOff>
       <xdr:row>114</xdr:row>
-      <xdr:rowOff>106920</xdr:rowOff>
+      <xdr:rowOff>107280</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -7868,9 +7868,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="20097000"/>
-          <a:ext cx="5641560" cy="41760"/>
+          <a:ext cx="5641920" cy="42120"/>
           <a:chOff x="35280" y="20097000"/>
-          <a:chExt cx="5641560" cy="41760"/>
+          <a:chExt cx="5641920" cy="42120"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -7881,7 +7881,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="20115000"/>
-            <a:ext cx="5641920" cy="24120"/>
+            <a:ext cx="5642280" cy="24480"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7902,7 +7902,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="20097000"/>
-            <a:ext cx="5640120" cy="24120"/>
+            <a:ext cx="5640480" cy="24480"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7927,9 +7927,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>729000</xdr:colOff>
+      <xdr:colOff>728640</xdr:colOff>
       <xdr:row>112</xdr:row>
-      <xdr:rowOff>94320</xdr:rowOff>
+      <xdr:rowOff>93960</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7939,7 +7939,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4320" y="18978120"/>
-          <a:ext cx="1088640" cy="804960"/>
+          <a:ext cx="1088280" cy="804600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8005,9 +8005,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>13320</xdr:colOff>
+      <xdr:colOff>13680</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>106920</xdr:rowOff>
+      <xdr:rowOff>107280</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -8017,9 +8017,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="1112760"/>
-          <a:ext cx="3128400" cy="41760"/>
+          <a:ext cx="3128760" cy="42120"/>
           <a:chOff x="35280" y="1112760"/>
-          <a:chExt cx="3128400" cy="41760"/>
+          <a:chExt cx="3128760" cy="42120"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -8030,7 +8030,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="36360" y="1130760"/>
-            <a:ext cx="3127680" cy="24120"/>
+            <a:ext cx="3128040" cy="24480"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -8051,7 +8051,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="1112760"/>
-            <a:ext cx="3127320" cy="24120"/>
+            <a:ext cx="3127680" cy="24480"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -8076,9 +8076,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>738720</xdr:colOff>
+      <xdr:colOff>738360</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>11520</xdr:rowOff>
+      <xdr:rowOff>11160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -8093,7 +8093,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="57240"/>
-          <a:ext cx="1087920" cy="811440"/>
+          <a:ext cx="1087560" cy="811080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8115,9 +8115,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>13320</xdr:colOff>
+      <xdr:colOff>13680</xdr:colOff>
       <xdr:row>73</xdr:row>
-      <xdr:rowOff>106920</xdr:rowOff>
+      <xdr:rowOff>107280</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -8127,9 +8127,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="12190320"/>
-          <a:ext cx="3128400" cy="41760"/>
+          <a:ext cx="3128760" cy="42120"/>
           <a:chOff x="35280" y="12190320"/>
-          <a:chExt cx="3128400" cy="41760"/>
+          <a:chExt cx="3128760" cy="42120"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -8140,7 +8140,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="36360" y="12208320"/>
-            <a:ext cx="3127680" cy="24120"/>
+            <a:ext cx="3128040" cy="24480"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -8161,7 +8161,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="12190320"/>
-            <a:ext cx="3127320" cy="24120"/>
+            <a:ext cx="3127680" cy="24480"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -8186,9 +8186,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>738720</xdr:colOff>
+      <xdr:colOff>738360</xdr:colOff>
       <xdr:row>72</xdr:row>
-      <xdr:rowOff>11520</xdr:rowOff>
+      <xdr:rowOff>11160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -8203,7 +8203,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="11134800"/>
-          <a:ext cx="1087920" cy="811440"/>
+          <a:ext cx="1087560" cy="811080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8225,9 +8225,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>13320</xdr:colOff>
+      <xdr:colOff>13680</xdr:colOff>
       <xdr:row>140</xdr:row>
-      <xdr:rowOff>106920</xdr:rowOff>
+      <xdr:rowOff>107280</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -8237,9 +8237,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="23296680"/>
-          <a:ext cx="3128400" cy="41760"/>
+          <a:ext cx="3128760" cy="42120"/>
           <a:chOff x="35280" y="23296680"/>
-          <a:chExt cx="3128400" cy="41760"/>
+          <a:chExt cx="3128760" cy="42120"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -8250,7 +8250,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="36360" y="23314680"/>
-            <a:ext cx="3127680" cy="24120"/>
+            <a:ext cx="3128040" cy="24480"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -8271,7 +8271,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="23296680"/>
-            <a:ext cx="3127320" cy="24120"/>
+            <a:ext cx="3127680" cy="24480"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -8296,9 +8296,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>738720</xdr:colOff>
+      <xdr:colOff>738360</xdr:colOff>
       <xdr:row>139</xdr:row>
-      <xdr:rowOff>11520</xdr:rowOff>
+      <xdr:rowOff>11160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -8313,7 +8313,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="22240800"/>
-          <a:ext cx="1087920" cy="811800"/>
+          <a:ext cx="1087560" cy="811440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8340,9 +8340,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>33120</xdr:colOff>
+      <xdr:colOff>32760</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>136440</xdr:rowOff>
+      <xdr:rowOff>136080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -8356,7 +8356,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="389520" y="238320"/>
-          <a:ext cx="862200" cy="907920"/>
+          <a:ext cx="861840" cy="907560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8858,7 +8858,7 @@
         <v>26</v>
       </c>
       <c r="K16" s="23" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="L16" s="6" t="n">
         <v>100</v>
@@ -8895,7 +8895,9 @@
       <c r="J17" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="K17" s="23"/>
+      <c r="K17" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="L17" s="6" t="n">
         <v>100</v>
       </c>
@@ -9007,7 +9009,9 @@
       <c r="J20" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="K20" s="23"/>
+      <c r="K20" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="L20" s="6" t="n">
         <v>100</v>
       </c>
@@ -9082,7 +9086,7 @@
         <v>26</v>
       </c>
       <c r="K22" s="23" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="L22" s="6" t="n">
         <v>100</v>
@@ -9119,7 +9123,9 @@
       <c r="J23" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="K23" s="23"/>
+      <c r="K23" s="23" t="n">
+        <v>100</v>
+      </c>
       <c r="L23" s="6" t="n">
         <v>100</v>
       </c>
@@ -9644,7 +9650,7 @@
         <v>26</v>
       </c>
       <c r="K37" s="23" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="L37" s="6" t="n">
         <v>100</v>
@@ -9719,7 +9725,9 @@
       <c r="J39" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="K39" s="23"/>
+      <c r="K39" s="23" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="18" t="n">

--- a/Rekap Absen dan Nilai 2025-2026.xlsx
+++ b/Rekap Absen dan Nilai 2025-2026.xlsx
@@ -6776,9 +6776,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>12960</xdr:colOff>
+      <xdr:colOff>13320</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>107280</xdr:rowOff>
+      <xdr:rowOff>107640</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6788,9 +6788,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="1170000"/>
-          <a:ext cx="24086880" cy="42120"/>
+          <a:ext cx="24087240" cy="42480"/>
           <a:chOff x="35280" y="1170000"/>
-          <a:chExt cx="24086880" cy="42120"/>
+          <a:chExt cx="24087240" cy="42480"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -6801,7 +6801,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="36360" y="1188000"/>
-            <a:ext cx="24086160" cy="24480"/>
+            <a:ext cx="24086520" cy="24840"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -6822,7 +6822,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="1170000"/>
-            <a:ext cx="24079680" cy="24480"/>
+            <a:ext cx="24080040" cy="24840"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -6847,9 +6847,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>725040</xdr:colOff>
+      <xdr:colOff>724680</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>100080</xdr:rowOff>
+      <xdr:rowOff>99720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6864,7 +6864,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="57240"/>
-          <a:ext cx="1088280" cy="804960"/>
+          <a:ext cx="1087920" cy="804600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6886,9 +6886,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>725040</xdr:colOff>
+      <xdr:colOff>724680</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>119160</xdr:rowOff>
+      <xdr:rowOff>118800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6903,7 +6903,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="8798040"/>
-          <a:ext cx="1088280" cy="804960"/>
+          <a:ext cx="1087920" cy="804600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6925,9 +6925,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>725040</xdr:colOff>
+      <xdr:colOff>724680</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>119160</xdr:rowOff>
+      <xdr:rowOff>118800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6942,7 +6942,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="8798040"/>
-          <a:ext cx="1088280" cy="804960"/>
+          <a:ext cx="1087920" cy="804600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6964,9 +6964,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>12960</xdr:colOff>
+      <xdr:colOff>13320</xdr:colOff>
       <xdr:row>55</xdr:row>
-      <xdr:rowOff>107280</xdr:rowOff>
+      <xdr:rowOff>107640</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6976,9 +6976,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="10130040"/>
-          <a:ext cx="24086880" cy="42120"/>
+          <a:ext cx="24087240" cy="42480"/>
           <a:chOff x="35280" y="10130040"/>
-          <a:chExt cx="24086880" cy="42120"/>
+          <a:chExt cx="24087240" cy="42480"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -6989,7 +6989,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="36360" y="10148040"/>
-            <a:ext cx="24086160" cy="24480"/>
+            <a:ext cx="24086520" cy="24840"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7010,7 +7010,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="10130040"/>
-            <a:ext cx="24079680" cy="24480"/>
+            <a:ext cx="24080040" cy="24840"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7035,9 +7035,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>725040</xdr:colOff>
+      <xdr:colOff>724680</xdr:colOff>
       <xdr:row>53</xdr:row>
-      <xdr:rowOff>113040</xdr:rowOff>
+      <xdr:rowOff>112680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7052,7 +7052,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="9026640"/>
-          <a:ext cx="1088280" cy="808200"/>
+          <a:ext cx="1087920" cy="807840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7074,9 +7074,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>12960</xdr:colOff>
+      <xdr:colOff>13320</xdr:colOff>
       <xdr:row>114</xdr:row>
-      <xdr:rowOff>107280</xdr:rowOff>
+      <xdr:rowOff>107640</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -7086,9 +7086,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="20822040"/>
-          <a:ext cx="24086880" cy="42120"/>
+          <a:ext cx="24087240" cy="42480"/>
           <a:chOff x="35280" y="20822040"/>
-          <a:chExt cx="24086880" cy="42120"/>
+          <a:chExt cx="24087240" cy="42480"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -7099,7 +7099,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="36360" y="20840040"/>
-            <a:ext cx="24086160" cy="24480"/>
+            <a:ext cx="24086520" cy="24840"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7120,7 +7120,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="20822040"/>
-            <a:ext cx="24079680" cy="24480"/>
+            <a:ext cx="24080040" cy="24840"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7145,9 +7145,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>728640</xdr:colOff>
+      <xdr:colOff>728280</xdr:colOff>
       <xdr:row>112</xdr:row>
-      <xdr:rowOff>93960</xdr:rowOff>
+      <xdr:rowOff>93600</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7157,7 +7157,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4320" y="19703520"/>
-          <a:ext cx="1088280" cy="804600"/>
+          <a:ext cx="1087920" cy="804240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7223,9 +7223,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>13680</xdr:colOff>
+      <xdr:colOff>14040</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>107280</xdr:rowOff>
+      <xdr:rowOff>107640</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -7235,9 +7235,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="1112760"/>
-          <a:ext cx="3128760" cy="42120"/>
+          <a:ext cx="3129120" cy="42480"/>
           <a:chOff x="35280" y="1112760"/>
-          <a:chExt cx="3128760" cy="42120"/>
+          <a:chExt cx="3129120" cy="42480"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -7248,7 +7248,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="36360" y="1130760"/>
-            <a:ext cx="3128040" cy="24480"/>
+            <a:ext cx="3128400" cy="24840"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7269,7 +7269,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="1112760"/>
-            <a:ext cx="3127680" cy="24480"/>
+            <a:ext cx="3128040" cy="24840"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7294,9 +7294,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>738360</xdr:colOff>
+      <xdr:colOff>738000</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>11160</xdr:rowOff>
+      <xdr:rowOff>10800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7311,7 +7311,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="57240"/>
-          <a:ext cx="1087560" cy="811080"/>
+          <a:ext cx="1087200" cy="810720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7333,9 +7333,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>13680</xdr:colOff>
+      <xdr:colOff>14040</xdr:colOff>
       <xdr:row>73</xdr:row>
-      <xdr:rowOff>107280</xdr:rowOff>
+      <xdr:rowOff>107640</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -7345,9 +7345,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="12190320"/>
-          <a:ext cx="3128760" cy="42120"/>
+          <a:ext cx="3129120" cy="42480"/>
           <a:chOff x="35280" y="12190320"/>
-          <a:chExt cx="3128760" cy="42120"/>
+          <a:chExt cx="3129120" cy="42480"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -7358,7 +7358,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="36360" y="12208320"/>
-            <a:ext cx="3128040" cy="24480"/>
+            <a:ext cx="3128400" cy="24840"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7379,7 +7379,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="12190320"/>
-            <a:ext cx="3127680" cy="24480"/>
+            <a:ext cx="3128040" cy="24840"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7404,9 +7404,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>738360</xdr:colOff>
+      <xdr:colOff>738000</xdr:colOff>
       <xdr:row>72</xdr:row>
-      <xdr:rowOff>11160</xdr:rowOff>
+      <xdr:rowOff>10800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7421,7 +7421,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="11134800"/>
-          <a:ext cx="1087560" cy="811080"/>
+          <a:ext cx="1087200" cy="810720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7443,9 +7443,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>13680</xdr:colOff>
+      <xdr:colOff>14040</xdr:colOff>
       <xdr:row>140</xdr:row>
-      <xdr:rowOff>107280</xdr:rowOff>
+      <xdr:rowOff>107640</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -7455,9 +7455,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="23296680"/>
-          <a:ext cx="3128760" cy="42120"/>
+          <a:ext cx="3129120" cy="42480"/>
           <a:chOff x="35280" y="23296680"/>
-          <a:chExt cx="3128760" cy="42120"/>
+          <a:chExt cx="3129120" cy="42480"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -7468,7 +7468,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="36360" y="23314680"/>
-            <a:ext cx="3128040" cy="24480"/>
+            <a:ext cx="3128400" cy="24840"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7489,7 +7489,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="23296680"/>
-            <a:ext cx="3127680" cy="24480"/>
+            <a:ext cx="3128040" cy="24840"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7514,9 +7514,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>738360</xdr:colOff>
+      <xdr:colOff>738000</xdr:colOff>
       <xdr:row>139</xdr:row>
-      <xdr:rowOff>11160</xdr:rowOff>
+      <xdr:rowOff>10800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7531,7 +7531,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="22240800"/>
-          <a:ext cx="1087560" cy="811440"/>
+          <a:ext cx="1087200" cy="811080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7558,9 +7558,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>12960</xdr:colOff>
+      <xdr:colOff>13320</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>107280</xdr:rowOff>
+      <xdr:rowOff>107640</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -7570,9 +7570,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="1170000"/>
-          <a:ext cx="5641920" cy="42120"/>
+          <a:ext cx="5642280" cy="42480"/>
           <a:chOff x="35280" y="1170000"/>
-          <a:chExt cx="5641920" cy="42120"/>
+          <a:chExt cx="5642280" cy="42480"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -7583,7 +7583,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="1188000"/>
-            <a:ext cx="5642280" cy="24480"/>
+            <a:ext cx="5642640" cy="24840"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7604,7 +7604,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="1170000"/>
-            <a:ext cx="5640480" cy="24480"/>
+            <a:ext cx="5640840" cy="24840"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7629,9 +7629,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>725040</xdr:colOff>
+      <xdr:colOff>724680</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>100080</xdr:rowOff>
+      <xdr:rowOff>99720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7646,7 +7646,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="57240"/>
-          <a:ext cx="1088280" cy="804960"/>
+          <a:ext cx="1087920" cy="804600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7668,9 +7668,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>725040</xdr:colOff>
+      <xdr:colOff>724680</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>119160</xdr:rowOff>
+      <xdr:rowOff>118800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7685,7 +7685,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="8439840"/>
-          <a:ext cx="1088280" cy="804960"/>
+          <a:ext cx="1087920" cy="804600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7707,9 +7707,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>725040</xdr:colOff>
+      <xdr:colOff>724680</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>119160</xdr:rowOff>
+      <xdr:rowOff>118800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7724,7 +7724,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="8439840"/>
-          <a:ext cx="1088280" cy="804960"/>
+          <a:ext cx="1087920" cy="804600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7746,9 +7746,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>12960</xdr:colOff>
+      <xdr:colOff>13320</xdr:colOff>
       <xdr:row>55</xdr:row>
-      <xdr:rowOff>107280</xdr:rowOff>
+      <xdr:rowOff>107640</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -7758,9 +7758,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="9771840"/>
-          <a:ext cx="5641920" cy="42120"/>
+          <a:ext cx="5642280" cy="42480"/>
           <a:chOff x="35280" y="9771840"/>
-          <a:chExt cx="5641920" cy="42120"/>
+          <a:chExt cx="5642280" cy="42480"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -7771,7 +7771,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="9789840"/>
-            <a:ext cx="5642280" cy="24480"/>
+            <a:ext cx="5642640" cy="24840"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7792,7 +7792,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="9771840"/>
-            <a:ext cx="5640480" cy="24480"/>
+            <a:ext cx="5640840" cy="24840"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7817,9 +7817,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>725040</xdr:colOff>
+      <xdr:colOff>724680</xdr:colOff>
       <xdr:row>53</xdr:row>
-      <xdr:rowOff>113040</xdr:rowOff>
+      <xdr:rowOff>112680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7834,7 +7834,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="8668440"/>
-          <a:ext cx="1088280" cy="808200"/>
+          <a:ext cx="1087920" cy="807840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7856,9 +7856,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>12960</xdr:colOff>
+      <xdr:colOff>13320</xdr:colOff>
       <xdr:row>114</xdr:row>
-      <xdr:rowOff>107280</xdr:rowOff>
+      <xdr:rowOff>107640</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -7868,9 +7868,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="20097000"/>
-          <a:ext cx="5641920" cy="42120"/>
+          <a:ext cx="5642280" cy="42480"/>
           <a:chOff x="35280" y="20097000"/>
-          <a:chExt cx="5641920" cy="42120"/>
+          <a:chExt cx="5642280" cy="42480"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -7881,7 +7881,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="20115000"/>
-            <a:ext cx="5642280" cy="24480"/>
+            <a:ext cx="5642640" cy="24840"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7902,7 +7902,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="20097000"/>
-            <a:ext cx="5640480" cy="24480"/>
+            <a:ext cx="5640840" cy="24840"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -7927,9 +7927,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>728640</xdr:colOff>
+      <xdr:colOff>728280</xdr:colOff>
       <xdr:row>112</xdr:row>
-      <xdr:rowOff>93960</xdr:rowOff>
+      <xdr:rowOff>93600</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7939,7 +7939,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4320" y="18978120"/>
-          <a:ext cx="1088280" cy="804600"/>
+          <a:ext cx="1087920" cy="804240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8005,9 +8005,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>13680</xdr:colOff>
+      <xdr:colOff>14040</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>107280</xdr:rowOff>
+      <xdr:rowOff>107640</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -8017,9 +8017,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="1112760"/>
-          <a:ext cx="3128760" cy="42120"/>
+          <a:ext cx="3129120" cy="42480"/>
           <a:chOff x="35280" y="1112760"/>
-          <a:chExt cx="3128760" cy="42120"/>
+          <a:chExt cx="3129120" cy="42480"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -8030,7 +8030,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="36360" y="1130760"/>
-            <a:ext cx="3128040" cy="24480"/>
+            <a:ext cx="3128400" cy="24840"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -8051,7 +8051,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="1112760"/>
-            <a:ext cx="3127680" cy="24480"/>
+            <a:ext cx="3128040" cy="24840"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -8076,9 +8076,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>738360</xdr:colOff>
+      <xdr:colOff>738000</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>11160</xdr:rowOff>
+      <xdr:rowOff>10800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -8093,7 +8093,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="57240"/>
-          <a:ext cx="1087560" cy="811080"/>
+          <a:ext cx="1087200" cy="810720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8115,9 +8115,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>13680</xdr:colOff>
+      <xdr:colOff>14040</xdr:colOff>
       <xdr:row>73</xdr:row>
-      <xdr:rowOff>107280</xdr:rowOff>
+      <xdr:rowOff>107640</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -8127,9 +8127,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="12190320"/>
-          <a:ext cx="3128760" cy="42120"/>
+          <a:ext cx="3129120" cy="42480"/>
           <a:chOff x="35280" y="12190320"/>
-          <a:chExt cx="3128760" cy="42120"/>
+          <a:chExt cx="3129120" cy="42480"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -8140,7 +8140,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="36360" y="12208320"/>
-            <a:ext cx="3128040" cy="24480"/>
+            <a:ext cx="3128400" cy="24840"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -8161,7 +8161,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="12190320"/>
-            <a:ext cx="3127680" cy="24480"/>
+            <a:ext cx="3128040" cy="24840"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -8186,9 +8186,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>738360</xdr:colOff>
+      <xdr:colOff>738000</xdr:colOff>
       <xdr:row>72</xdr:row>
-      <xdr:rowOff>11160</xdr:rowOff>
+      <xdr:rowOff>10800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -8203,7 +8203,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="11134800"/>
-          <a:ext cx="1087560" cy="811080"/>
+          <a:ext cx="1087200" cy="810720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8225,9 +8225,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>13680</xdr:colOff>
+      <xdr:colOff>14040</xdr:colOff>
       <xdr:row>140</xdr:row>
-      <xdr:rowOff>107280</xdr:rowOff>
+      <xdr:rowOff>107640</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -8237,9 +8237,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="35280" y="23296680"/>
-          <a:ext cx="3128760" cy="42120"/>
+          <a:ext cx="3129120" cy="42480"/>
           <a:chOff x="35280" y="23296680"/>
-          <a:chExt cx="3128760" cy="42120"/>
+          <a:chExt cx="3129120" cy="42480"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -8250,7 +8250,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="36360" y="23314680"/>
-            <a:ext cx="3128040" cy="24480"/>
+            <a:ext cx="3128400" cy="24840"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -8271,7 +8271,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="35280" y="23296680"/>
-            <a:ext cx="3127680" cy="24480"/>
+            <a:ext cx="3128040" cy="24840"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -8296,9 +8296,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>738360</xdr:colOff>
+      <xdr:colOff>738000</xdr:colOff>
       <xdr:row>139</xdr:row>
-      <xdr:rowOff>11160</xdr:rowOff>
+      <xdr:rowOff>10800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -8313,7 +8313,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720" y="22240800"/>
-          <a:ext cx="1087560" cy="811440"/>
+          <a:ext cx="1087200" cy="811080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8340,9 +8340,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>32760</xdr:colOff>
+      <xdr:colOff>32400</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>136080</xdr:rowOff>
+      <xdr:rowOff>135720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -8356,7 +8356,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="389520" y="238320"/>
-          <a:ext cx="861840" cy="907560"/>
+          <a:ext cx="861480" cy="907200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10237,6 +10237,9 @@
         <v>101</v>
       </c>
       <c r="M62" s="32"/>
+      <c r="N62" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="18" t="n">
@@ -10278,6 +10281,9 @@
       <c r="M63" s="32" t="n">
         <v>1</v>
       </c>
+      <c r="N63" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="18" t="n">
@@ -10358,6 +10364,9 @@
       <c r="M65" s="32" t="n">
         <v>1</v>
       </c>
+      <c r="N65" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="18" t="n">
@@ -10397,6 +10406,9 @@
         <v>100</v>
       </c>
       <c r="M66" s="32"/>
+      <c r="N66" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="18" t="n">
@@ -10516,6 +10528,9 @@
       <c r="M69" s="32" t="n">
         <v>1</v>
       </c>
+      <c r="N69" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="18" t="n">
@@ -10555,6 +10570,9 @@
         <v>101</v>
       </c>
       <c r="M70" s="32"/>
+      <c r="N70" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="18" t="n">
@@ -10754,6 +10772,9 @@
       <c r="M75" s="32" t="n">
         <v>1</v>
       </c>
+      <c r="N75" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="18" t="n">
@@ -10951,6 +10972,9 @@
         <v>100</v>
       </c>
       <c r="M80" s="32"/>
+      <c r="N80" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="18" t="n">
@@ -10990,6 +11014,9 @@
         <v>100</v>
       </c>
       <c r="M81" s="32"/>
+      <c r="N81" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="18" t="n">
@@ -11228,6 +11255,9 @@
       <c r="M87" s="32" t="n">
         <v>1</v>
       </c>
+      <c r="N87" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="18" t="n">
@@ -11345,6 +11375,9 @@
         <v>100</v>
       </c>
       <c r="M90" s="32"/>
+      <c r="N90" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="18" t="n">
@@ -11499,6 +11532,9 @@
         <v>100</v>
       </c>
       <c r="M94" s="32"/>
+      <c r="N94" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="18" t="n">
@@ -11577,6 +11613,9 @@
         <v>100</v>
       </c>
       <c r="M96" s="32"/>
+      <c r="N96" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="18" t="n">
@@ -11616,6 +11655,9 @@
         <v>101</v>
       </c>
       <c r="M97" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="N97" s="6" t="n">
         <v>1</v>
       </c>
     </row>
